--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -7,11 +7,16 @@
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion1">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mh0BYxXpfOKDAPGiv5MkKBYToYp4w=="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -110,6 +115,30 @@
   </si>
   <si>
     <t>You have failed to purchase this product.</t>
+  </si>
+  <si>
+    <t>RESTORE_P_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>복원 성공 팝업 메세지</t>
+  </si>
+  <si>
+    <t>상품을 복원했습니다.</t>
+  </si>
+  <si>
+    <t>The product has been restored.</t>
+  </si>
+  <si>
+    <t>RESTORE_P_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>복원 실패 팝업 메세지</t>
+  </si>
+  <si>
+    <t>상품 복원에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Failed to restore the product.</t>
   </si>
   <si>
     <t>START_SM_LOADING_TEXT</t>
@@ -206,7 +235,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -214,6 +243,9 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -231,7 +263,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
@@ -247,22 +279,23 @@
       </top>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -277,49 +310,30 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -531,15 +545,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="32.86"/>
+    <col customWidth="1" min="2" max="2" width="14.43"/>
     <col customWidth="1" min="3" max="3" width="29.57"/>
     <col customWidth="1" min="4" max="4" width="59.14"/>
     <col customWidth="1" min="5" max="5" width="72.57"/>
+    <col customWidth="1" min="6" max="6" width="14.43"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,7 +572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -572,636 +588,1677 @@
       <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="5"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>0.0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="9"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>0.0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="9"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>0.0</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="9"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="9"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>0.0</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="9"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>0.0</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="9"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="7">
         <v>0.0</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="9"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="8"/>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="7">
         <v>0.0</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="9"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="8"/>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.0</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="9"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>0.0</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="9"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>0.0</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="9"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="7">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="5">
         <v>0.0</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="9"/>
+      <c r="E19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="7">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="10">
         <v>0.0</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="9"/>
+      <c r="C20" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="9"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="9"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="13"/>
-    </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -7,11 +7,6 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mh0BYxXpfOKDAPGiv5MkKBYToYp4w=="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -235,7 +230,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -243,9 +238,6 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -263,7 +255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -287,20 +279,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -314,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -323,17 +301,14 @@
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -867,7 +842,6 @@
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
-      <c r="Z9" s="8"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
@@ -905,7 +879,6 @@
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
-      <c r="Z10" s="8"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
@@ -1241,41 +1214,41 @@
       <c r="Y19" s="5"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>0.0</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -2257,8 +2230,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -7,11 +7,16 @@
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion1">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7miaSHn9FPVfJahlpw53wmsvdTcRRQ=="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
   <si>
     <t>ID</t>
   </si>
@@ -224,6 +229,72 @@
   </si>
   <si>
     <t>약관 동의 팝업 확인 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>DESC_P_TITLE</t>
+  </si>
+  <si>
+    <t>설명 팝업 제목</t>
+  </si>
+  <si>
+    <t>DESC_P_MSG</t>
+  </si>
+  <si>
+    <t>설명 팝업 메세지</t>
+  </si>
+  <si>
+    <t>추적 승인 허용</t>
+  </si>
+  <si>
+    <t>Allow tracking on the\nnext screen for</t>
+  </si>
+  <si>
+    <t>DESC_P_DESC_MSG_01</t>
+  </si>
+  <si>
+    <t>설명 팝업 설명 메세지 1</t>
+  </si>
+  <si>
+    <t>∙ 특별한 프로모션을 제공해\n드립니다.</t>
+  </si>
+  <si>
+    <t>∙ Special offers and promotions\njust for you</t>
+  </si>
+  <si>
+    <t>DESC_P_DESC_MSG_02</t>
+  </si>
+  <si>
+    <t>설명 팝업 설명 메세지 2</t>
+  </si>
+  <si>
+    <t>∙ 관심사에 맞는 광고를 보여\n드립니다.</t>
+  </si>
+  <si>
+    <t>∙ Advertisements that match\nyour interests</t>
+  </si>
+  <si>
+    <t>DESC_P_DESC_MSG_03</t>
+  </si>
+  <si>
+    <t>설명 팝업 설명 메세지 3</t>
+  </si>
+  <si>
+    <t>∙ 개인화 된 경험이 향상 시켜\n드립니다.</t>
+  </si>
+  <si>
+    <t>∙ An improved personalized\nexperience over time</t>
+  </si>
+  <si>
+    <t>DESC_P_NEXT_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>설명 팝업 다음 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>다음</t>
+  </si>
+  <si>
+    <t>Next</t>
   </si>
 </sst>
 </file>
@@ -255,7 +326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -271,9 +342,22 @@
       </top>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -288,27 +372,52 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -522,11 +631,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.86"/>
+    <col customWidth="1" min="1" max="1" width="31.57"/>
     <col customWidth="1" min="2" max="2" width="14.43"/>
     <col customWidth="1" min="3" max="3" width="29.57"/>
     <col customWidth="1" min="4" max="4" width="59.14"/>
-    <col customWidth="1" min="5" max="5" width="72.57"/>
+    <col customWidth="1" min="5" max="5" width="54.71"/>
     <col customWidth="1" min="6" max="6" width="14.43"/>
   </cols>
   <sheetData>
@@ -583,679 +692,920 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
+      <c r="Z2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>0.0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="7"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>0.0</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="7"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>0.0</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="7"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>0.0</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="7"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>0.0</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="7"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <v>0.0</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="7"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>0.0</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="7"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>0.0</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="7"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>0.0</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="7"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <v>0.0</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="7"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="6">
         <v>0.0</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="7"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="6">
         <v>0.0</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="7"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="6">
         <v>0.0</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="7"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="6">
         <v>0.0</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="7"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="6">
         <v>0.0</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="7"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="6">
         <v>0.0</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="7"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="6">
         <v>0.0</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="7"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="6">
         <v>0.0</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="7"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="7"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="7"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="7"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="7"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="7"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="16"/>
+    </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -2230,6 +2580,13 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -7,11 +7,6 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7miaSHn9FPVfJahlpw53wmsvdTcRRQ=="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -326,7 +321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -342,22 +337,9 @@
       </top>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
     </border>
     <border>
       <left style="thin">
@@ -372,30 +354,20 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -404,20 +376,8 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -692,919 +652,894 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0.0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="7"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>0.0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="7"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.0</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="7"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="7"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>0.0</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="7"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>0.0</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="7"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>0.0</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>0.0</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>0.0</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="7"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>0.0</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="7"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>0.0</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="7"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>0.0</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="7"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>0.0</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="7"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>0.0</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="7"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>0.0</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="7"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>0.0</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="7"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>0.0</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="7"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>0.0</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="7"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="5">
         <v>0.0</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="7"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="5">
         <v>0.0</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="7"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="5">
         <v>0.0</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="7"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="5">
         <v>0.0</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="7"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="5">
         <v>0.0</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="7"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="10">
         <v>0.0</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="16"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -2580,13 +2515,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
-    <row r="1005" ht="15.75" customHeight="1"/>
-    <row r="1006" ht="15.75" customHeight="1"/>
-    <row r="1007" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -74,6 +74,18 @@
   </si>
   <si>
     <t>Are you sure you want to quit the game?</t>
+  </si>
+  <si>
+    <t>EDITOR_QUIT_P_MSG</t>
+  </si>
+  <si>
+    <t>에디터 종료 팝업 메세지</t>
+  </si>
+  <si>
+    <t>에디터를 종료하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to quit the editor?</t>
   </si>
   <si>
     <t>UPDATE_P_MSG</t>
@@ -358,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -367,6 +379,12 @@
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -765,19 +783,19 @@
       <c r="Y5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="5"/>
@@ -876,115 +894,115 @@
       <c r="Y8" s="5"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.0</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>0.0</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="9">
         <v>0.0</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
@@ -1108,10 +1126,10 @@
         <v>58</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -1136,19 +1154,19 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="5">
         <v>0.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1173,19 +1191,19 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="5">
         <v>0.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1210,19 +1228,19 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="5">
         <v>0.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -1247,13 +1265,13 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="5">
         <v>0.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>52</v>
@@ -1284,19 +1302,19 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="5">
         <v>0.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -1321,19 +1339,19 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="5">
         <v>0.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -1358,19 +1376,19 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" s="5">
         <v>0.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -1505,43 +1523,79 @@
       <c r="Y25" s="5"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="5">
         <v>0.0</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+    </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
@@ -2515,6 +2569,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -617,7 +617,7 @@
     <col customWidth="1" min="6" max="6" width="14.43"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,7 +634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -671,7 +671,7 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -708,7 +708,7 @@
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -782,7 +782,7 @@
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -819,7 +819,7 @@
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
@@ -856,7 +856,7 @@
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>29</v>
       </c>
@@ -893,7 +893,7 @@
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
@@ -930,7 +930,7 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
@@ -967,7 +967,7 @@
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -1004,7 +1004,7 @@
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -1041,7 +1041,7 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>49</v>
       </c>
@@ -1078,7 +1078,7 @@
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
@@ -1115,7 +1115,7 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
@@ -1152,7 +1152,7 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>61</v>
       </c>
@@ -1189,7 +1189,7 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>66</v>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>69</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>71</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>73</v>
       </c>
@@ -1374,7 +1374,7 @@
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>75</v>
       </c>
@@ -1411,7 +1411,7 @@
       <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>77</v>
       </c>
@@ -1448,7 +1448,7 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>81</v>
       </c>
@@ -1485,7 +1485,7 @@
       <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>85</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>89</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="X26" s="5"/>
       <c r="Y26" s="5"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="11" t="s">
         <v>93</v>
       </c>
@@ -1596,980 +1596,980 @@
       <c r="X27" s="12"/>
       <c r="Y27" s="12"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.0" customHeight="1"/>
+    <row r="29" ht="15.0" customHeight="1"/>
+    <row r="30" ht="15.0" customHeight="1"/>
+    <row r="31" ht="15.0" customHeight="1"/>
+    <row r="32" ht="15.0" customHeight="1"/>
+    <row r="33" ht="15.0" customHeight="1"/>
+    <row r="34" ht="15.0" customHeight="1"/>
+    <row r="35" ht="15.0" customHeight="1"/>
+    <row r="36" ht="15.0" customHeight="1"/>
+    <row r="37" ht="15.0" customHeight="1"/>
+    <row r="38" ht="15.0" customHeight="1"/>
+    <row r="39" ht="15.0" customHeight="1"/>
+    <row r="40" ht="15.0" customHeight="1"/>
+    <row r="41" ht="15.0" customHeight="1"/>
+    <row r="42" ht="15.0" customHeight="1"/>
+    <row r="43" ht="15.0" customHeight="1"/>
+    <row r="44" ht="15.0" customHeight="1"/>
+    <row r="45" ht="15.0" customHeight="1"/>
+    <row r="46" ht="15.0" customHeight="1"/>
+    <row r="47" ht="15.0" customHeight="1"/>
+    <row r="48" ht="15.0" customHeight="1"/>
+    <row r="49" ht="15.0" customHeight="1"/>
+    <row r="50" ht="15.0" customHeight="1"/>
+    <row r="51" ht="15.0" customHeight="1"/>
+    <row r="52" ht="15.0" customHeight="1"/>
+    <row r="53" ht="15.0" customHeight="1"/>
+    <row r="54" ht="15.0" customHeight="1"/>
+    <row r="55" ht="15.0" customHeight="1"/>
+    <row r="56" ht="15.0" customHeight="1"/>
+    <row r="57" ht="15.0" customHeight="1"/>
+    <row r="58" ht="15.0" customHeight="1"/>
+    <row r="59" ht="15.0" customHeight="1"/>
+    <row r="60" ht="15.0" customHeight="1"/>
+    <row r="61" ht="15.0" customHeight="1"/>
+    <row r="62" ht="15.0" customHeight="1"/>
+    <row r="63" ht="15.0" customHeight="1"/>
+    <row r="64" ht="15.0" customHeight="1"/>
+    <row r="65" ht="15.0" customHeight="1"/>
+    <row r="66" ht="15.0" customHeight="1"/>
+    <row r="67" ht="15.0" customHeight="1"/>
+    <row r="68" ht="15.0" customHeight="1"/>
+    <row r="69" ht="15.0" customHeight="1"/>
+    <row r="70" ht="15.0" customHeight="1"/>
+    <row r="71" ht="15.0" customHeight="1"/>
+    <row r="72" ht="15.0" customHeight="1"/>
+    <row r="73" ht="15.0" customHeight="1"/>
+    <row r="74" ht="15.0" customHeight="1"/>
+    <row r="75" ht="15.0" customHeight="1"/>
+    <row r="76" ht="15.0" customHeight="1"/>
+    <row r="77" ht="15.0" customHeight="1"/>
+    <row r="78" ht="15.0" customHeight="1"/>
+    <row r="79" ht="15.0" customHeight="1"/>
+    <row r="80" ht="15.0" customHeight="1"/>
+    <row r="81" ht="15.0" customHeight="1"/>
+    <row r="82" ht="15.0" customHeight="1"/>
+    <row r="83" ht="15.0" customHeight="1"/>
+    <row r="84" ht="15.0" customHeight="1"/>
+    <row r="85" ht="15.0" customHeight="1"/>
+    <row r="86" ht="15.0" customHeight="1"/>
+    <row r="87" ht="15.0" customHeight="1"/>
+    <row r="88" ht="15.0" customHeight="1"/>
+    <row r="89" ht="15.0" customHeight="1"/>
+    <row r="90" ht="15.0" customHeight="1"/>
+    <row r="91" ht="15.0" customHeight="1"/>
+    <row r="92" ht="15.0" customHeight="1"/>
+    <row r="93" ht="15.0" customHeight="1"/>
+    <row r="94" ht="15.0" customHeight="1"/>
+    <row r="95" ht="15.0" customHeight="1"/>
+    <row r="96" ht="15.0" customHeight="1"/>
+    <row r="97" ht="15.0" customHeight="1"/>
+    <row r="98" ht="15.0" customHeight="1"/>
+    <row r="99" ht="15.0" customHeight="1"/>
+    <row r="100" ht="15.0" customHeight="1"/>
+    <row r="101" ht="15.0" customHeight="1"/>
+    <row r="102" ht="15.0" customHeight="1"/>
+    <row r="103" ht="15.0" customHeight="1"/>
+    <row r="104" ht="15.0" customHeight="1"/>
+    <row r="105" ht="15.0" customHeight="1"/>
+    <row r="106" ht="15.0" customHeight="1"/>
+    <row r="107" ht="15.0" customHeight="1"/>
+    <row r="108" ht="15.0" customHeight="1"/>
+    <row r="109" ht="15.0" customHeight="1"/>
+    <row r="110" ht="15.0" customHeight="1"/>
+    <row r="111" ht="15.0" customHeight="1"/>
+    <row r="112" ht="15.0" customHeight="1"/>
+    <row r="113" ht="15.0" customHeight="1"/>
+    <row r="114" ht="15.0" customHeight="1"/>
+    <row r="115" ht="15.0" customHeight="1"/>
+    <row r="116" ht="15.0" customHeight="1"/>
+    <row r="117" ht="15.0" customHeight="1"/>
+    <row r="118" ht="15.0" customHeight="1"/>
+    <row r="119" ht="15.0" customHeight="1"/>
+    <row r="120" ht="15.0" customHeight="1"/>
+    <row r="121" ht="15.0" customHeight="1"/>
+    <row r="122" ht="15.0" customHeight="1"/>
+    <row r="123" ht="15.0" customHeight="1"/>
+    <row r="124" ht="15.0" customHeight="1"/>
+    <row r="125" ht="15.0" customHeight="1"/>
+    <row r="126" ht="15.0" customHeight="1"/>
+    <row r="127" ht="15.0" customHeight="1"/>
+    <row r="128" ht="15.0" customHeight="1"/>
+    <row r="129" ht="15.0" customHeight="1"/>
+    <row r="130" ht="15.0" customHeight="1"/>
+    <row r="131" ht="15.0" customHeight="1"/>
+    <row r="132" ht="15.0" customHeight="1"/>
+    <row r="133" ht="15.0" customHeight="1"/>
+    <row r="134" ht="15.0" customHeight="1"/>
+    <row r="135" ht="15.0" customHeight="1"/>
+    <row r="136" ht="15.0" customHeight="1"/>
+    <row r="137" ht="15.0" customHeight="1"/>
+    <row r="138" ht="15.0" customHeight="1"/>
+    <row r="139" ht="15.0" customHeight="1"/>
+    <row r="140" ht="15.0" customHeight="1"/>
+    <row r="141" ht="15.0" customHeight="1"/>
+    <row r="142" ht="15.0" customHeight="1"/>
+    <row r="143" ht="15.0" customHeight="1"/>
+    <row r="144" ht="15.0" customHeight="1"/>
+    <row r="145" ht="15.0" customHeight="1"/>
+    <row r="146" ht="15.0" customHeight="1"/>
+    <row r="147" ht="15.0" customHeight="1"/>
+    <row r="148" ht="15.0" customHeight="1"/>
+    <row r="149" ht="15.0" customHeight="1"/>
+    <row r="150" ht="15.0" customHeight="1"/>
+    <row r="151" ht="15.0" customHeight="1"/>
+    <row r="152" ht="15.0" customHeight="1"/>
+    <row r="153" ht="15.0" customHeight="1"/>
+    <row r="154" ht="15.0" customHeight="1"/>
+    <row r="155" ht="15.0" customHeight="1"/>
+    <row r="156" ht="15.0" customHeight="1"/>
+    <row r="157" ht="15.0" customHeight="1"/>
+    <row r="158" ht="15.0" customHeight="1"/>
+    <row r="159" ht="15.0" customHeight="1"/>
+    <row r="160" ht="15.0" customHeight="1"/>
+    <row r="161" ht="15.0" customHeight="1"/>
+    <row r="162" ht="15.0" customHeight="1"/>
+    <row r="163" ht="15.0" customHeight="1"/>
+    <row r="164" ht="15.0" customHeight="1"/>
+    <row r="165" ht="15.0" customHeight="1"/>
+    <row r="166" ht="15.0" customHeight="1"/>
+    <row r="167" ht="15.0" customHeight="1"/>
+    <row r="168" ht="15.0" customHeight="1"/>
+    <row r="169" ht="15.0" customHeight="1"/>
+    <row r="170" ht="15.0" customHeight="1"/>
+    <row r="171" ht="15.0" customHeight="1"/>
+    <row r="172" ht="15.0" customHeight="1"/>
+    <row r="173" ht="15.0" customHeight="1"/>
+    <row r="174" ht="15.0" customHeight="1"/>
+    <row r="175" ht="15.0" customHeight="1"/>
+    <row r="176" ht="15.0" customHeight="1"/>
+    <row r="177" ht="15.0" customHeight="1"/>
+    <row r="178" ht="15.0" customHeight="1"/>
+    <row r="179" ht="15.0" customHeight="1"/>
+    <row r="180" ht="15.0" customHeight="1"/>
+    <row r="181" ht="15.0" customHeight="1"/>
+    <row r="182" ht="15.0" customHeight="1"/>
+    <row r="183" ht="15.0" customHeight="1"/>
+    <row r="184" ht="15.0" customHeight="1"/>
+    <row r="185" ht="15.0" customHeight="1"/>
+    <row r="186" ht="15.0" customHeight="1"/>
+    <row r="187" ht="15.0" customHeight="1"/>
+    <row r="188" ht="15.0" customHeight="1"/>
+    <row r="189" ht="15.0" customHeight="1"/>
+    <row r="190" ht="15.0" customHeight="1"/>
+    <row r="191" ht="15.0" customHeight="1"/>
+    <row r="192" ht="15.0" customHeight="1"/>
+    <row r="193" ht="15.0" customHeight="1"/>
+    <row r="194" ht="15.0" customHeight="1"/>
+    <row r="195" ht="15.0" customHeight="1"/>
+    <row r="196" ht="15.0" customHeight="1"/>
+    <row r="197" ht="15.0" customHeight="1"/>
+    <row r="198" ht="15.0" customHeight="1"/>
+    <row r="199" ht="15.0" customHeight="1"/>
+    <row r="200" ht="15.0" customHeight="1"/>
+    <row r="201" ht="15.0" customHeight="1"/>
+    <row r="202" ht="15.0" customHeight="1"/>
+    <row r="203" ht="15.0" customHeight="1"/>
+    <row r="204" ht="15.0" customHeight="1"/>
+    <row r="205" ht="15.0" customHeight="1"/>
+    <row r="206" ht="15.0" customHeight="1"/>
+    <row r="207" ht="15.0" customHeight="1"/>
+    <row r="208" ht="15.0" customHeight="1"/>
+    <row r="209" ht="15.0" customHeight="1"/>
+    <row r="210" ht="15.0" customHeight="1"/>
+    <row r="211" ht="15.0" customHeight="1"/>
+    <row r="212" ht="15.0" customHeight="1"/>
+    <row r="213" ht="15.0" customHeight="1"/>
+    <row r="214" ht="15.0" customHeight="1"/>
+    <row r="215" ht="15.0" customHeight="1"/>
+    <row r="216" ht="15.0" customHeight="1"/>
+    <row r="217" ht="15.0" customHeight="1"/>
+    <row r="218" ht="15.0" customHeight="1"/>
+    <row r="219" ht="15.0" customHeight="1"/>
+    <row r="220" ht="15.0" customHeight="1"/>
+    <row r="221" ht="15.0" customHeight="1"/>
+    <row r="222" ht="15.0" customHeight="1"/>
+    <row r="223" ht="15.0" customHeight="1"/>
+    <row r="224" ht="15.0" customHeight="1"/>
+    <row r="225" ht="15.0" customHeight="1"/>
+    <row r="226" ht="15.0" customHeight="1"/>
+    <row r="227" ht="15.0" customHeight="1"/>
+    <row r="228" ht="15.0" customHeight="1"/>
+    <row r="229" ht="15.0" customHeight="1"/>
+    <row r="230" ht="15.0" customHeight="1"/>
+    <row r="231" ht="15.0" customHeight="1"/>
+    <row r="232" ht="15.0" customHeight="1"/>
+    <row r="233" ht="15.0" customHeight="1"/>
+    <row r="234" ht="15.0" customHeight="1"/>
+    <row r="235" ht="15.0" customHeight="1"/>
+    <row r="236" ht="15.0" customHeight="1"/>
+    <row r="237" ht="15.0" customHeight="1"/>
+    <row r="238" ht="15.0" customHeight="1"/>
+    <row r="239" ht="15.0" customHeight="1"/>
+    <row r="240" ht="15.0" customHeight="1"/>
+    <row r="241" ht="15.0" customHeight="1"/>
+    <row r="242" ht="15.0" customHeight="1"/>
+    <row r="243" ht="15.0" customHeight="1"/>
+    <row r="244" ht="15.0" customHeight="1"/>
+    <row r="245" ht="15.0" customHeight="1"/>
+    <row r="246" ht="15.0" customHeight="1"/>
+    <row r="247" ht="15.0" customHeight="1"/>
+    <row r="248" ht="15.0" customHeight="1"/>
+    <row r="249" ht="15.0" customHeight="1"/>
+    <row r="250" ht="15.0" customHeight="1"/>
+    <row r="251" ht="15.0" customHeight="1"/>
+    <row r="252" ht="15.0" customHeight="1"/>
+    <row r="253" ht="15.0" customHeight="1"/>
+    <row r="254" ht="15.0" customHeight="1"/>
+    <row r="255" ht="15.0" customHeight="1"/>
+    <row r="256" ht="15.0" customHeight="1"/>
+    <row r="257" ht="15.0" customHeight="1"/>
+    <row r="258" ht="15.0" customHeight="1"/>
+    <row r="259" ht="15.0" customHeight="1"/>
+    <row r="260" ht="15.0" customHeight="1"/>
+    <row r="261" ht="15.0" customHeight="1"/>
+    <row r="262" ht="15.0" customHeight="1"/>
+    <row r="263" ht="15.0" customHeight="1"/>
+    <row r="264" ht="15.0" customHeight="1"/>
+    <row r="265" ht="15.0" customHeight="1"/>
+    <row r="266" ht="15.0" customHeight="1"/>
+    <row r="267" ht="15.0" customHeight="1"/>
+    <row r="268" ht="15.0" customHeight="1"/>
+    <row r="269" ht="15.0" customHeight="1"/>
+    <row r="270" ht="15.0" customHeight="1"/>
+    <row r="271" ht="15.0" customHeight="1"/>
+    <row r="272" ht="15.0" customHeight="1"/>
+    <row r="273" ht="15.0" customHeight="1"/>
+    <row r="274" ht="15.0" customHeight="1"/>
+    <row r="275" ht="15.0" customHeight="1"/>
+    <row r="276" ht="15.0" customHeight="1"/>
+    <row r="277" ht="15.0" customHeight="1"/>
+    <row r="278" ht="15.0" customHeight="1"/>
+    <row r="279" ht="15.0" customHeight="1"/>
+    <row r="280" ht="15.0" customHeight="1"/>
+    <row r="281" ht="15.0" customHeight="1"/>
+    <row r="282" ht="15.0" customHeight="1"/>
+    <row r="283" ht="15.0" customHeight="1"/>
+    <row r="284" ht="15.0" customHeight="1"/>
+    <row r="285" ht="15.0" customHeight="1"/>
+    <row r="286" ht="15.0" customHeight="1"/>
+    <row r="287" ht="15.0" customHeight="1"/>
+    <row r="288" ht="15.0" customHeight="1"/>
+    <row r="289" ht="15.0" customHeight="1"/>
+    <row r="290" ht="15.0" customHeight="1"/>
+    <row r="291" ht="15.0" customHeight="1"/>
+    <row r="292" ht="15.0" customHeight="1"/>
+    <row r="293" ht="15.0" customHeight="1"/>
+    <row r="294" ht="15.0" customHeight="1"/>
+    <row r="295" ht="15.0" customHeight="1"/>
+    <row r="296" ht="15.0" customHeight="1"/>
+    <row r="297" ht="15.0" customHeight="1"/>
+    <row r="298" ht="15.0" customHeight="1"/>
+    <row r="299" ht="15.0" customHeight="1"/>
+    <row r="300" ht="15.0" customHeight="1"/>
+    <row r="301" ht="15.0" customHeight="1"/>
+    <row r="302" ht="15.0" customHeight="1"/>
+    <row r="303" ht="15.0" customHeight="1"/>
+    <row r="304" ht="15.0" customHeight="1"/>
+    <row r="305" ht="15.0" customHeight="1"/>
+    <row r="306" ht="15.0" customHeight="1"/>
+    <row r="307" ht="15.0" customHeight="1"/>
+    <row r="308" ht="15.0" customHeight="1"/>
+    <row r="309" ht="15.0" customHeight="1"/>
+    <row r="310" ht="15.0" customHeight="1"/>
+    <row r="311" ht="15.0" customHeight="1"/>
+    <row r="312" ht="15.0" customHeight="1"/>
+    <row r="313" ht="15.0" customHeight="1"/>
+    <row r="314" ht="15.0" customHeight="1"/>
+    <row r="315" ht="15.0" customHeight="1"/>
+    <row r="316" ht="15.0" customHeight="1"/>
+    <row r="317" ht="15.0" customHeight="1"/>
+    <row r="318" ht="15.0" customHeight="1"/>
+    <row r="319" ht="15.0" customHeight="1"/>
+    <row r="320" ht="15.0" customHeight="1"/>
+    <row r="321" ht="15.0" customHeight="1"/>
+    <row r="322" ht="15.0" customHeight="1"/>
+    <row r="323" ht="15.0" customHeight="1"/>
+    <row r="324" ht="15.0" customHeight="1"/>
+    <row r="325" ht="15.0" customHeight="1"/>
+    <row r="326" ht="15.0" customHeight="1"/>
+    <row r="327" ht="15.0" customHeight="1"/>
+    <row r="328" ht="15.0" customHeight="1"/>
+    <row r="329" ht="15.0" customHeight="1"/>
+    <row r="330" ht="15.0" customHeight="1"/>
+    <row r="331" ht="15.0" customHeight="1"/>
+    <row r="332" ht="15.0" customHeight="1"/>
+    <row r="333" ht="15.0" customHeight="1"/>
+    <row r="334" ht="15.0" customHeight="1"/>
+    <row r="335" ht="15.0" customHeight="1"/>
+    <row r="336" ht="15.0" customHeight="1"/>
+    <row r="337" ht="15.0" customHeight="1"/>
+    <row r="338" ht="15.0" customHeight="1"/>
+    <row r="339" ht="15.0" customHeight="1"/>
+    <row r="340" ht="15.0" customHeight="1"/>
+    <row r="341" ht="15.0" customHeight="1"/>
+    <row r="342" ht="15.0" customHeight="1"/>
+    <row r="343" ht="15.0" customHeight="1"/>
+    <row r="344" ht="15.0" customHeight="1"/>
+    <row r="345" ht="15.0" customHeight="1"/>
+    <row r="346" ht="15.0" customHeight="1"/>
+    <row r="347" ht="15.0" customHeight="1"/>
+    <row r="348" ht="15.0" customHeight="1"/>
+    <row r="349" ht="15.0" customHeight="1"/>
+    <row r="350" ht="15.0" customHeight="1"/>
+    <row r="351" ht="15.0" customHeight="1"/>
+    <row r="352" ht="15.0" customHeight="1"/>
+    <row r="353" ht="15.0" customHeight="1"/>
+    <row r="354" ht="15.0" customHeight="1"/>
+    <row r="355" ht="15.0" customHeight="1"/>
+    <row r="356" ht="15.0" customHeight="1"/>
+    <row r="357" ht="15.0" customHeight="1"/>
+    <row r="358" ht="15.0" customHeight="1"/>
+    <row r="359" ht="15.0" customHeight="1"/>
+    <row r="360" ht="15.0" customHeight="1"/>
+    <row r="361" ht="15.0" customHeight="1"/>
+    <row r="362" ht="15.0" customHeight="1"/>
+    <row r="363" ht="15.0" customHeight="1"/>
+    <row r="364" ht="15.0" customHeight="1"/>
+    <row r="365" ht="15.0" customHeight="1"/>
+    <row r="366" ht="15.0" customHeight="1"/>
+    <row r="367" ht="15.0" customHeight="1"/>
+    <row r="368" ht="15.0" customHeight="1"/>
+    <row r="369" ht="15.0" customHeight="1"/>
+    <row r="370" ht="15.0" customHeight="1"/>
+    <row r="371" ht="15.0" customHeight="1"/>
+    <row r="372" ht="15.0" customHeight="1"/>
+    <row r="373" ht="15.0" customHeight="1"/>
+    <row r="374" ht="15.0" customHeight="1"/>
+    <row r="375" ht="15.0" customHeight="1"/>
+    <row r="376" ht="15.0" customHeight="1"/>
+    <row r="377" ht="15.0" customHeight="1"/>
+    <row r="378" ht="15.0" customHeight="1"/>
+    <row r="379" ht="15.0" customHeight="1"/>
+    <row r="380" ht="15.0" customHeight="1"/>
+    <row r="381" ht="15.0" customHeight="1"/>
+    <row r="382" ht="15.0" customHeight="1"/>
+    <row r="383" ht="15.0" customHeight="1"/>
+    <row r="384" ht="15.0" customHeight="1"/>
+    <row r="385" ht="15.0" customHeight="1"/>
+    <row r="386" ht="15.0" customHeight="1"/>
+    <row r="387" ht="15.0" customHeight="1"/>
+    <row r="388" ht="15.0" customHeight="1"/>
+    <row r="389" ht="15.0" customHeight="1"/>
+    <row r="390" ht="15.0" customHeight="1"/>
+    <row r="391" ht="15.0" customHeight="1"/>
+    <row r="392" ht="15.0" customHeight="1"/>
+    <row r="393" ht="15.0" customHeight="1"/>
+    <row r="394" ht="15.0" customHeight="1"/>
+    <row r="395" ht="15.0" customHeight="1"/>
+    <row r="396" ht="15.0" customHeight="1"/>
+    <row r="397" ht="15.0" customHeight="1"/>
+    <row r="398" ht="15.0" customHeight="1"/>
+    <row r="399" ht="15.0" customHeight="1"/>
+    <row r="400" ht="15.0" customHeight="1"/>
+    <row r="401" ht="15.0" customHeight="1"/>
+    <row r="402" ht="15.0" customHeight="1"/>
+    <row r="403" ht="15.0" customHeight="1"/>
+    <row r="404" ht="15.0" customHeight="1"/>
+    <row r="405" ht="15.0" customHeight="1"/>
+    <row r="406" ht="15.0" customHeight="1"/>
+    <row r="407" ht="15.0" customHeight="1"/>
+    <row r="408" ht="15.0" customHeight="1"/>
+    <row r="409" ht="15.0" customHeight="1"/>
+    <row r="410" ht="15.0" customHeight="1"/>
+    <row r="411" ht="15.0" customHeight="1"/>
+    <row r="412" ht="15.0" customHeight="1"/>
+    <row r="413" ht="15.0" customHeight="1"/>
+    <row r="414" ht="15.0" customHeight="1"/>
+    <row r="415" ht="15.0" customHeight="1"/>
+    <row r="416" ht="15.0" customHeight="1"/>
+    <row r="417" ht="15.0" customHeight="1"/>
+    <row r="418" ht="15.0" customHeight="1"/>
+    <row r="419" ht="15.0" customHeight="1"/>
+    <row r="420" ht="15.0" customHeight="1"/>
+    <row r="421" ht="15.0" customHeight="1"/>
+    <row r="422" ht="15.0" customHeight="1"/>
+    <row r="423" ht="15.0" customHeight="1"/>
+    <row r="424" ht="15.0" customHeight="1"/>
+    <row r="425" ht="15.0" customHeight="1"/>
+    <row r="426" ht="15.0" customHeight="1"/>
+    <row r="427" ht="15.0" customHeight="1"/>
+    <row r="428" ht="15.0" customHeight="1"/>
+    <row r="429" ht="15.0" customHeight="1"/>
+    <row r="430" ht="15.0" customHeight="1"/>
+    <row r="431" ht="15.0" customHeight="1"/>
+    <row r="432" ht="15.0" customHeight="1"/>
+    <row r="433" ht="15.0" customHeight="1"/>
+    <row r="434" ht="15.0" customHeight="1"/>
+    <row r="435" ht="15.0" customHeight="1"/>
+    <row r="436" ht="15.0" customHeight="1"/>
+    <row r="437" ht="15.0" customHeight="1"/>
+    <row r="438" ht="15.0" customHeight="1"/>
+    <row r="439" ht="15.0" customHeight="1"/>
+    <row r="440" ht="15.0" customHeight="1"/>
+    <row r="441" ht="15.0" customHeight="1"/>
+    <row r="442" ht="15.0" customHeight="1"/>
+    <row r="443" ht="15.0" customHeight="1"/>
+    <row r="444" ht="15.0" customHeight="1"/>
+    <row r="445" ht="15.0" customHeight="1"/>
+    <row r="446" ht="15.0" customHeight="1"/>
+    <row r="447" ht="15.0" customHeight="1"/>
+    <row r="448" ht="15.0" customHeight="1"/>
+    <row r="449" ht="15.0" customHeight="1"/>
+    <row r="450" ht="15.0" customHeight="1"/>
+    <row r="451" ht="15.0" customHeight="1"/>
+    <row r="452" ht="15.0" customHeight="1"/>
+    <row r="453" ht="15.0" customHeight="1"/>
+    <row r="454" ht="15.0" customHeight="1"/>
+    <row r="455" ht="15.0" customHeight="1"/>
+    <row r="456" ht="15.0" customHeight="1"/>
+    <row r="457" ht="15.0" customHeight="1"/>
+    <row r="458" ht="15.0" customHeight="1"/>
+    <row r="459" ht="15.0" customHeight="1"/>
+    <row r="460" ht="15.0" customHeight="1"/>
+    <row r="461" ht="15.0" customHeight="1"/>
+    <row r="462" ht="15.0" customHeight="1"/>
+    <row r="463" ht="15.0" customHeight="1"/>
+    <row r="464" ht="15.0" customHeight="1"/>
+    <row r="465" ht="15.0" customHeight="1"/>
+    <row r="466" ht="15.0" customHeight="1"/>
+    <row r="467" ht="15.0" customHeight="1"/>
+    <row r="468" ht="15.0" customHeight="1"/>
+    <row r="469" ht="15.0" customHeight="1"/>
+    <row r="470" ht="15.0" customHeight="1"/>
+    <row r="471" ht="15.0" customHeight="1"/>
+    <row r="472" ht="15.0" customHeight="1"/>
+    <row r="473" ht="15.0" customHeight="1"/>
+    <row r="474" ht="15.0" customHeight="1"/>
+    <row r="475" ht="15.0" customHeight="1"/>
+    <row r="476" ht="15.0" customHeight="1"/>
+    <row r="477" ht="15.0" customHeight="1"/>
+    <row r="478" ht="15.0" customHeight="1"/>
+    <row r="479" ht="15.0" customHeight="1"/>
+    <row r="480" ht="15.0" customHeight="1"/>
+    <row r="481" ht="15.0" customHeight="1"/>
+    <row r="482" ht="15.0" customHeight="1"/>
+    <row r="483" ht="15.0" customHeight="1"/>
+    <row r="484" ht="15.0" customHeight="1"/>
+    <row r="485" ht="15.0" customHeight="1"/>
+    <row r="486" ht="15.0" customHeight="1"/>
+    <row r="487" ht="15.0" customHeight="1"/>
+    <row r="488" ht="15.0" customHeight="1"/>
+    <row r="489" ht="15.0" customHeight="1"/>
+    <row r="490" ht="15.0" customHeight="1"/>
+    <row r="491" ht="15.0" customHeight="1"/>
+    <row r="492" ht="15.0" customHeight="1"/>
+    <row r="493" ht="15.0" customHeight="1"/>
+    <row r="494" ht="15.0" customHeight="1"/>
+    <row r="495" ht="15.0" customHeight="1"/>
+    <row r="496" ht="15.0" customHeight="1"/>
+    <row r="497" ht="15.0" customHeight="1"/>
+    <row r="498" ht="15.0" customHeight="1"/>
+    <row r="499" ht="15.0" customHeight="1"/>
+    <row r="500" ht="15.0" customHeight="1"/>
+    <row r="501" ht="15.0" customHeight="1"/>
+    <row r="502" ht="15.0" customHeight="1"/>
+    <row r="503" ht="15.0" customHeight="1"/>
+    <row r="504" ht="15.0" customHeight="1"/>
+    <row r="505" ht="15.0" customHeight="1"/>
+    <row r="506" ht="15.0" customHeight="1"/>
+    <row r="507" ht="15.0" customHeight="1"/>
+    <row r="508" ht="15.0" customHeight="1"/>
+    <row r="509" ht="15.0" customHeight="1"/>
+    <row r="510" ht="15.0" customHeight="1"/>
+    <row r="511" ht="15.0" customHeight="1"/>
+    <row r="512" ht="15.0" customHeight="1"/>
+    <row r="513" ht="15.0" customHeight="1"/>
+    <row r="514" ht="15.0" customHeight="1"/>
+    <row r="515" ht="15.0" customHeight="1"/>
+    <row r="516" ht="15.0" customHeight="1"/>
+    <row r="517" ht="15.0" customHeight="1"/>
+    <row r="518" ht="15.0" customHeight="1"/>
+    <row r="519" ht="15.0" customHeight="1"/>
+    <row r="520" ht="15.0" customHeight="1"/>
+    <row r="521" ht="15.0" customHeight="1"/>
+    <row r="522" ht="15.0" customHeight="1"/>
+    <row r="523" ht="15.0" customHeight="1"/>
+    <row r="524" ht="15.0" customHeight="1"/>
+    <row r="525" ht="15.0" customHeight="1"/>
+    <row r="526" ht="15.0" customHeight="1"/>
+    <row r="527" ht="15.0" customHeight="1"/>
+    <row r="528" ht="15.0" customHeight="1"/>
+    <row r="529" ht="15.0" customHeight="1"/>
+    <row r="530" ht="15.0" customHeight="1"/>
+    <row r="531" ht="15.0" customHeight="1"/>
+    <row r="532" ht="15.0" customHeight="1"/>
+    <row r="533" ht="15.0" customHeight="1"/>
+    <row r="534" ht="15.0" customHeight="1"/>
+    <row r="535" ht="15.0" customHeight="1"/>
+    <row r="536" ht="15.0" customHeight="1"/>
+    <row r="537" ht="15.0" customHeight="1"/>
+    <row r="538" ht="15.0" customHeight="1"/>
+    <row r="539" ht="15.0" customHeight="1"/>
+    <row r="540" ht="15.0" customHeight="1"/>
+    <row r="541" ht="15.0" customHeight="1"/>
+    <row r="542" ht="15.0" customHeight="1"/>
+    <row r="543" ht="15.0" customHeight="1"/>
+    <row r="544" ht="15.0" customHeight="1"/>
+    <row r="545" ht="15.0" customHeight="1"/>
+    <row r="546" ht="15.0" customHeight="1"/>
+    <row r="547" ht="15.0" customHeight="1"/>
+    <row r="548" ht="15.0" customHeight="1"/>
+    <row r="549" ht="15.0" customHeight="1"/>
+    <row r="550" ht="15.0" customHeight="1"/>
+    <row r="551" ht="15.0" customHeight="1"/>
+    <row r="552" ht="15.0" customHeight="1"/>
+    <row r="553" ht="15.0" customHeight="1"/>
+    <row r="554" ht="15.0" customHeight="1"/>
+    <row r="555" ht="15.0" customHeight="1"/>
+    <row r="556" ht="15.0" customHeight="1"/>
+    <row r="557" ht="15.0" customHeight="1"/>
+    <row r="558" ht="15.0" customHeight="1"/>
+    <row r="559" ht="15.0" customHeight="1"/>
+    <row r="560" ht="15.0" customHeight="1"/>
+    <row r="561" ht="15.0" customHeight="1"/>
+    <row r="562" ht="15.0" customHeight="1"/>
+    <row r="563" ht="15.0" customHeight="1"/>
+    <row r="564" ht="15.0" customHeight="1"/>
+    <row r="565" ht="15.0" customHeight="1"/>
+    <row r="566" ht="15.0" customHeight="1"/>
+    <row r="567" ht="15.0" customHeight="1"/>
+    <row r="568" ht="15.0" customHeight="1"/>
+    <row r="569" ht="15.0" customHeight="1"/>
+    <row r="570" ht="15.0" customHeight="1"/>
+    <row r="571" ht="15.0" customHeight="1"/>
+    <row r="572" ht="15.0" customHeight="1"/>
+    <row r="573" ht="15.0" customHeight="1"/>
+    <row r="574" ht="15.0" customHeight="1"/>
+    <row r="575" ht="15.0" customHeight="1"/>
+    <row r="576" ht="15.0" customHeight="1"/>
+    <row r="577" ht="15.0" customHeight="1"/>
+    <row r="578" ht="15.0" customHeight="1"/>
+    <row r="579" ht="15.0" customHeight="1"/>
+    <row r="580" ht="15.0" customHeight="1"/>
+    <row r="581" ht="15.0" customHeight="1"/>
+    <row r="582" ht="15.0" customHeight="1"/>
+    <row r="583" ht="15.0" customHeight="1"/>
+    <row r="584" ht="15.0" customHeight="1"/>
+    <row r="585" ht="15.0" customHeight="1"/>
+    <row r="586" ht="15.0" customHeight="1"/>
+    <row r="587" ht="15.0" customHeight="1"/>
+    <row r="588" ht="15.0" customHeight="1"/>
+    <row r="589" ht="15.0" customHeight="1"/>
+    <row r="590" ht="15.0" customHeight="1"/>
+    <row r="591" ht="15.0" customHeight="1"/>
+    <row r="592" ht="15.0" customHeight="1"/>
+    <row r="593" ht="15.0" customHeight="1"/>
+    <row r="594" ht="15.0" customHeight="1"/>
+    <row r="595" ht="15.0" customHeight="1"/>
+    <row r="596" ht="15.0" customHeight="1"/>
+    <row r="597" ht="15.0" customHeight="1"/>
+    <row r="598" ht="15.0" customHeight="1"/>
+    <row r="599" ht="15.0" customHeight="1"/>
+    <row r="600" ht="15.0" customHeight="1"/>
+    <row r="601" ht="15.0" customHeight="1"/>
+    <row r="602" ht="15.0" customHeight="1"/>
+    <row r="603" ht="15.0" customHeight="1"/>
+    <row r="604" ht="15.0" customHeight="1"/>
+    <row r="605" ht="15.0" customHeight="1"/>
+    <row r="606" ht="15.0" customHeight="1"/>
+    <row r="607" ht="15.0" customHeight="1"/>
+    <row r="608" ht="15.0" customHeight="1"/>
+    <row r="609" ht="15.0" customHeight="1"/>
+    <row r="610" ht="15.0" customHeight="1"/>
+    <row r="611" ht="15.0" customHeight="1"/>
+    <row r="612" ht="15.0" customHeight="1"/>
+    <row r="613" ht="15.0" customHeight="1"/>
+    <row r="614" ht="15.0" customHeight="1"/>
+    <row r="615" ht="15.0" customHeight="1"/>
+    <row r="616" ht="15.0" customHeight="1"/>
+    <row r="617" ht="15.0" customHeight="1"/>
+    <row r="618" ht="15.0" customHeight="1"/>
+    <row r="619" ht="15.0" customHeight="1"/>
+    <row r="620" ht="15.0" customHeight="1"/>
+    <row r="621" ht="15.0" customHeight="1"/>
+    <row r="622" ht="15.0" customHeight="1"/>
+    <row r="623" ht="15.0" customHeight="1"/>
+    <row r="624" ht="15.0" customHeight="1"/>
+    <row r="625" ht="15.0" customHeight="1"/>
+    <row r="626" ht="15.0" customHeight="1"/>
+    <row r="627" ht="15.0" customHeight="1"/>
+    <row r="628" ht="15.0" customHeight="1"/>
+    <row r="629" ht="15.0" customHeight="1"/>
+    <row r="630" ht="15.0" customHeight="1"/>
+    <row r="631" ht="15.0" customHeight="1"/>
+    <row r="632" ht="15.0" customHeight="1"/>
+    <row r="633" ht="15.0" customHeight="1"/>
+    <row r="634" ht="15.0" customHeight="1"/>
+    <row r="635" ht="15.0" customHeight="1"/>
+    <row r="636" ht="15.0" customHeight="1"/>
+    <row r="637" ht="15.0" customHeight="1"/>
+    <row r="638" ht="15.0" customHeight="1"/>
+    <row r="639" ht="15.0" customHeight="1"/>
+    <row r="640" ht="15.0" customHeight="1"/>
+    <row r="641" ht="15.0" customHeight="1"/>
+    <row r="642" ht="15.0" customHeight="1"/>
+    <row r="643" ht="15.0" customHeight="1"/>
+    <row r="644" ht="15.0" customHeight="1"/>
+    <row r="645" ht="15.0" customHeight="1"/>
+    <row r="646" ht="15.0" customHeight="1"/>
+    <row r="647" ht="15.0" customHeight="1"/>
+    <row r="648" ht="15.0" customHeight="1"/>
+    <row r="649" ht="15.0" customHeight="1"/>
+    <row r="650" ht="15.0" customHeight="1"/>
+    <row r="651" ht="15.0" customHeight="1"/>
+    <row r="652" ht="15.0" customHeight="1"/>
+    <row r="653" ht="15.0" customHeight="1"/>
+    <row r="654" ht="15.0" customHeight="1"/>
+    <row r="655" ht="15.0" customHeight="1"/>
+    <row r="656" ht="15.0" customHeight="1"/>
+    <row r="657" ht="15.0" customHeight="1"/>
+    <row r="658" ht="15.0" customHeight="1"/>
+    <row r="659" ht="15.0" customHeight="1"/>
+    <row r="660" ht="15.0" customHeight="1"/>
+    <row r="661" ht="15.0" customHeight="1"/>
+    <row r="662" ht="15.0" customHeight="1"/>
+    <row r="663" ht="15.0" customHeight="1"/>
+    <row r="664" ht="15.0" customHeight="1"/>
+    <row r="665" ht="15.0" customHeight="1"/>
+    <row r="666" ht="15.0" customHeight="1"/>
+    <row r="667" ht="15.0" customHeight="1"/>
+    <row r="668" ht="15.0" customHeight="1"/>
+    <row r="669" ht="15.0" customHeight="1"/>
+    <row r="670" ht="15.0" customHeight="1"/>
+    <row r="671" ht="15.0" customHeight="1"/>
+    <row r="672" ht="15.0" customHeight="1"/>
+    <row r="673" ht="15.0" customHeight="1"/>
+    <row r="674" ht="15.0" customHeight="1"/>
+    <row r="675" ht="15.0" customHeight="1"/>
+    <row r="676" ht="15.0" customHeight="1"/>
+    <row r="677" ht="15.0" customHeight="1"/>
+    <row r="678" ht="15.0" customHeight="1"/>
+    <row r="679" ht="15.0" customHeight="1"/>
+    <row r="680" ht="15.0" customHeight="1"/>
+    <row r="681" ht="15.0" customHeight="1"/>
+    <row r="682" ht="15.0" customHeight="1"/>
+    <row r="683" ht="15.0" customHeight="1"/>
+    <row r="684" ht="15.0" customHeight="1"/>
+    <row r="685" ht="15.0" customHeight="1"/>
+    <row r="686" ht="15.0" customHeight="1"/>
+    <row r="687" ht="15.0" customHeight="1"/>
+    <row r="688" ht="15.0" customHeight="1"/>
+    <row r="689" ht="15.0" customHeight="1"/>
+    <row r="690" ht="15.0" customHeight="1"/>
+    <row r="691" ht="15.0" customHeight="1"/>
+    <row r="692" ht="15.0" customHeight="1"/>
+    <row r="693" ht="15.0" customHeight="1"/>
+    <row r="694" ht="15.0" customHeight="1"/>
+    <row r="695" ht="15.0" customHeight="1"/>
+    <row r="696" ht="15.0" customHeight="1"/>
+    <row r="697" ht="15.0" customHeight="1"/>
+    <row r="698" ht="15.0" customHeight="1"/>
+    <row r="699" ht="15.0" customHeight="1"/>
+    <row r="700" ht="15.0" customHeight="1"/>
+    <row r="701" ht="15.0" customHeight="1"/>
+    <row r="702" ht="15.0" customHeight="1"/>
+    <row r="703" ht="15.0" customHeight="1"/>
+    <row r="704" ht="15.0" customHeight="1"/>
+    <row r="705" ht="15.0" customHeight="1"/>
+    <row r="706" ht="15.0" customHeight="1"/>
+    <row r="707" ht="15.0" customHeight="1"/>
+    <row r="708" ht="15.0" customHeight="1"/>
+    <row r="709" ht="15.0" customHeight="1"/>
+    <row r="710" ht="15.0" customHeight="1"/>
+    <row r="711" ht="15.0" customHeight="1"/>
+    <row r="712" ht="15.0" customHeight="1"/>
+    <row r="713" ht="15.0" customHeight="1"/>
+    <row r="714" ht="15.0" customHeight="1"/>
+    <row r="715" ht="15.0" customHeight="1"/>
+    <row r="716" ht="15.0" customHeight="1"/>
+    <row r="717" ht="15.0" customHeight="1"/>
+    <row r="718" ht="15.0" customHeight="1"/>
+    <row r="719" ht="15.0" customHeight="1"/>
+    <row r="720" ht="15.0" customHeight="1"/>
+    <row r="721" ht="15.0" customHeight="1"/>
+    <row r="722" ht="15.0" customHeight="1"/>
+    <row r="723" ht="15.0" customHeight="1"/>
+    <row r="724" ht="15.0" customHeight="1"/>
+    <row r="725" ht="15.0" customHeight="1"/>
+    <row r="726" ht="15.0" customHeight="1"/>
+    <row r="727" ht="15.0" customHeight="1"/>
+    <row r="728" ht="15.0" customHeight="1"/>
+    <row r="729" ht="15.0" customHeight="1"/>
+    <row r="730" ht="15.0" customHeight="1"/>
+    <row r="731" ht="15.0" customHeight="1"/>
+    <row r="732" ht="15.0" customHeight="1"/>
+    <row r="733" ht="15.0" customHeight="1"/>
+    <row r="734" ht="15.0" customHeight="1"/>
+    <row r="735" ht="15.0" customHeight="1"/>
+    <row r="736" ht="15.0" customHeight="1"/>
+    <row r="737" ht="15.0" customHeight="1"/>
+    <row r="738" ht="15.0" customHeight="1"/>
+    <row r="739" ht="15.0" customHeight="1"/>
+    <row r="740" ht="15.0" customHeight="1"/>
+    <row r="741" ht="15.0" customHeight="1"/>
+    <row r="742" ht="15.0" customHeight="1"/>
+    <row r="743" ht="15.0" customHeight="1"/>
+    <row r="744" ht="15.0" customHeight="1"/>
+    <row r="745" ht="15.0" customHeight="1"/>
+    <row r="746" ht="15.0" customHeight="1"/>
+    <row r="747" ht="15.0" customHeight="1"/>
+    <row r="748" ht="15.0" customHeight="1"/>
+    <row r="749" ht="15.0" customHeight="1"/>
+    <row r="750" ht="15.0" customHeight="1"/>
+    <row r="751" ht="15.0" customHeight="1"/>
+    <row r="752" ht="15.0" customHeight="1"/>
+    <row r="753" ht="15.0" customHeight="1"/>
+    <row r="754" ht="15.0" customHeight="1"/>
+    <row r="755" ht="15.0" customHeight="1"/>
+    <row r="756" ht="15.0" customHeight="1"/>
+    <row r="757" ht="15.0" customHeight="1"/>
+    <row r="758" ht="15.0" customHeight="1"/>
+    <row r="759" ht="15.0" customHeight="1"/>
+    <row r="760" ht="15.0" customHeight="1"/>
+    <row r="761" ht="15.0" customHeight="1"/>
+    <row r="762" ht="15.0" customHeight="1"/>
+    <row r="763" ht="15.0" customHeight="1"/>
+    <row r="764" ht="15.0" customHeight="1"/>
+    <row r="765" ht="15.0" customHeight="1"/>
+    <row r="766" ht="15.0" customHeight="1"/>
+    <row r="767" ht="15.0" customHeight="1"/>
+    <row r="768" ht="15.0" customHeight="1"/>
+    <row r="769" ht="15.0" customHeight="1"/>
+    <row r="770" ht="15.0" customHeight="1"/>
+    <row r="771" ht="15.0" customHeight="1"/>
+    <row r="772" ht="15.0" customHeight="1"/>
+    <row r="773" ht="15.0" customHeight="1"/>
+    <row r="774" ht="15.0" customHeight="1"/>
+    <row r="775" ht="15.0" customHeight="1"/>
+    <row r="776" ht="15.0" customHeight="1"/>
+    <row r="777" ht="15.0" customHeight="1"/>
+    <row r="778" ht="15.0" customHeight="1"/>
+    <row r="779" ht="15.0" customHeight="1"/>
+    <row r="780" ht="15.0" customHeight="1"/>
+    <row r="781" ht="15.0" customHeight="1"/>
+    <row r="782" ht="15.0" customHeight="1"/>
+    <row r="783" ht="15.0" customHeight="1"/>
+    <row r="784" ht="15.0" customHeight="1"/>
+    <row r="785" ht="15.0" customHeight="1"/>
+    <row r="786" ht="15.0" customHeight="1"/>
+    <row r="787" ht="15.0" customHeight="1"/>
+    <row r="788" ht="15.0" customHeight="1"/>
+    <row r="789" ht="15.0" customHeight="1"/>
+    <row r="790" ht="15.0" customHeight="1"/>
+    <row r="791" ht="15.0" customHeight="1"/>
+    <row r="792" ht="15.0" customHeight="1"/>
+    <row r="793" ht="15.0" customHeight="1"/>
+    <row r="794" ht="15.0" customHeight="1"/>
+    <row r="795" ht="15.0" customHeight="1"/>
+    <row r="796" ht="15.0" customHeight="1"/>
+    <row r="797" ht="15.0" customHeight="1"/>
+    <row r="798" ht="15.0" customHeight="1"/>
+    <row r="799" ht="15.0" customHeight="1"/>
+    <row r="800" ht="15.0" customHeight="1"/>
+    <row r="801" ht="15.0" customHeight="1"/>
+    <row r="802" ht="15.0" customHeight="1"/>
+    <row r="803" ht="15.0" customHeight="1"/>
+    <row r="804" ht="15.0" customHeight="1"/>
+    <row r="805" ht="15.0" customHeight="1"/>
+    <row r="806" ht="15.0" customHeight="1"/>
+    <row r="807" ht="15.0" customHeight="1"/>
+    <row r="808" ht="15.0" customHeight="1"/>
+    <row r="809" ht="15.0" customHeight="1"/>
+    <row r="810" ht="15.0" customHeight="1"/>
+    <row r="811" ht="15.0" customHeight="1"/>
+    <row r="812" ht="15.0" customHeight="1"/>
+    <row r="813" ht="15.0" customHeight="1"/>
+    <row r="814" ht="15.0" customHeight="1"/>
+    <row r="815" ht="15.0" customHeight="1"/>
+    <row r="816" ht="15.0" customHeight="1"/>
+    <row r="817" ht="15.0" customHeight="1"/>
+    <row r="818" ht="15.0" customHeight="1"/>
+    <row r="819" ht="15.0" customHeight="1"/>
+    <row r="820" ht="15.0" customHeight="1"/>
+    <row r="821" ht="15.0" customHeight="1"/>
+    <row r="822" ht="15.0" customHeight="1"/>
+    <row r="823" ht="15.0" customHeight="1"/>
+    <row r="824" ht="15.0" customHeight="1"/>
+    <row r="825" ht="15.0" customHeight="1"/>
+    <row r="826" ht="15.0" customHeight="1"/>
+    <row r="827" ht="15.0" customHeight="1"/>
+    <row r="828" ht="15.0" customHeight="1"/>
+    <row r="829" ht="15.0" customHeight="1"/>
+    <row r="830" ht="15.0" customHeight="1"/>
+    <row r="831" ht="15.0" customHeight="1"/>
+    <row r="832" ht="15.0" customHeight="1"/>
+    <row r="833" ht="15.0" customHeight="1"/>
+    <row r="834" ht="15.0" customHeight="1"/>
+    <row r="835" ht="15.0" customHeight="1"/>
+    <row r="836" ht="15.0" customHeight="1"/>
+    <row r="837" ht="15.0" customHeight="1"/>
+    <row r="838" ht="15.0" customHeight="1"/>
+    <row r="839" ht="15.0" customHeight="1"/>
+    <row r="840" ht="15.0" customHeight="1"/>
+    <row r="841" ht="15.0" customHeight="1"/>
+    <row r="842" ht="15.0" customHeight="1"/>
+    <row r="843" ht="15.0" customHeight="1"/>
+    <row r="844" ht="15.0" customHeight="1"/>
+    <row r="845" ht="15.0" customHeight="1"/>
+    <row r="846" ht="15.0" customHeight="1"/>
+    <row r="847" ht="15.0" customHeight="1"/>
+    <row r="848" ht="15.0" customHeight="1"/>
+    <row r="849" ht="15.0" customHeight="1"/>
+    <row r="850" ht="15.0" customHeight="1"/>
+    <row r="851" ht="15.0" customHeight="1"/>
+    <row r="852" ht="15.0" customHeight="1"/>
+    <row r="853" ht="15.0" customHeight="1"/>
+    <row r="854" ht="15.0" customHeight="1"/>
+    <row r="855" ht="15.0" customHeight="1"/>
+    <row r="856" ht="15.0" customHeight="1"/>
+    <row r="857" ht="15.0" customHeight="1"/>
+    <row r="858" ht="15.0" customHeight="1"/>
+    <row r="859" ht="15.0" customHeight="1"/>
+    <row r="860" ht="15.0" customHeight="1"/>
+    <row r="861" ht="15.0" customHeight="1"/>
+    <row r="862" ht="15.0" customHeight="1"/>
+    <row r="863" ht="15.0" customHeight="1"/>
+    <row r="864" ht="15.0" customHeight="1"/>
+    <row r="865" ht="15.0" customHeight="1"/>
+    <row r="866" ht="15.0" customHeight="1"/>
+    <row r="867" ht="15.0" customHeight="1"/>
+    <row r="868" ht="15.0" customHeight="1"/>
+    <row r="869" ht="15.0" customHeight="1"/>
+    <row r="870" ht="15.0" customHeight="1"/>
+    <row r="871" ht="15.0" customHeight="1"/>
+    <row r="872" ht="15.0" customHeight="1"/>
+    <row r="873" ht="15.0" customHeight="1"/>
+    <row r="874" ht="15.0" customHeight="1"/>
+    <row r="875" ht="15.0" customHeight="1"/>
+    <row r="876" ht="15.0" customHeight="1"/>
+    <row r="877" ht="15.0" customHeight="1"/>
+    <row r="878" ht="15.0" customHeight="1"/>
+    <row r="879" ht="15.0" customHeight="1"/>
+    <row r="880" ht="15.0" customHeight="1"/>
+    <row r="881" ht="15.0" customHeight="1"/>
+    <row r="882" ht="15.0" customHeight="1"/>
+    <row r="883" ht="15.0" customHeight="1"/>
+    <row r="884" ht="15.0" customHeight="1"/>
+    <row r="885" ht="15.0" customHeight="1"/>
+    <row r="886" ht="15.0" customHeight="1"/>
+    <row r="887" ht="15.0" customHeight="1"/>
+    <row r="888" ht="15.0" customHeight="1"/>
+    <row r="889" ht="15.0" customHeight="1"/>
+    <row r="890" ht="15.0" customHeight="1"/>
+    <row r="891" ht="15.0" customHeight="1"/>
+    <row r="892" ht="15.0" customHeight="1"/>
+    <row r="893" ht="15.0" customHeight="1"/>
+    <row r="894" ht="15.0" customHeight="1"/>
+    <row r="895" ht="15.0" customHeight="1"/>
+    <row r="896" ht="15.0" customHeight="1"/>
+    <row r="897" ht="15.0" customHeight="1"/>
+    <row r="898" ht="15.0" customHeight="1"/>
+    <row r="899" ht="15.0" customHeight="1"/>
+    <row r="900" ht="15.0" customHeight="1"/>
+    <row r="901" ht="15.0" customHeight="1"/>
+    <row r="902" ht="15.0" customHeight="1"/>
+    <row r="903" ht="15.0" customHeight="1"/>
+    <row r="904" ht="15.0" customHeight="1"/>
+    <row r="905" ht="15.0" customHeight="1"/>
+    <row r="906" ht="15.0" customHeight="1"/>
+    <row r="907" ht="15.0" customHeight="1"/>
+    <row r="908" ht="15.0" customHeight="1"/>
+    <row r="909" ht="15.0" customHeight="1"/>
+    <row r="910" ht="15.0" customHeight="1"/>
+    <row r="911" ht="15.0" customHeight="1"/>
+    <row r="912" ht="15.0" customHeight="1"/>
+    <row r="913" ht="15.0" customHeight="1"/>
+    <row r="914" ht="15.0" customHeight="1"/>
+    <row r="915" ht="15.0" customHeight="1"/>
+    <row r="916" ht="15.0" customHeight="1"/>
+    <row r="917" ht="15.0" customHeight="1"/>
+    <row r="918" ht="15.0" customHeight="1"/>
+    <row r="919" ht="15.0" customHeight="1"/>
+    <row r="920" ht="15.0" customHeight="1"/>
+    <row r="921" ht="15.0" customHeight="1"/>
+    <row r="922" ht="15.0" customHeight="1"/>
+    <row r="923" ht="15.0" customHeight="1"/>
+    <row r="924" ht="15.0" customHeight="1"/>
+    <row r="925" ht="15.0" customHeight="1"/>
+    <row r="926" ht="15.0" customHeight="1"/>
+    <row r="927" ht="15.0" customHeight="1"/>
+    <row r="928" ht="15.0" customHeight="1"/>
+    <row r="929" ht="15.0" customHeight="1"/>
+    <row r="930" ht="15.0" customHeight="1"/>
+    <row r="931" ht="15.0" customHeight="1"/>
+    <row r="932" ht="15.0" customHeight="1"/>
+    <row r="933" ht="15.0" customHeight="1"/>
+    <row r="934" ht="15.0" customHeight="1"/>
+    <row r="935" ht="15.0" customHeight="1"/>
+    <row r="936" ht="15.0" customHeight="1"/>
+    <row r="937" ht="15.0" customHeight="1"/>
+    <row r="938" ht="15.0" customHeight="1"/>
+    <row r="939" ht="15.0" customHeight="1"/>
+    <row r="940" ht="15.0" customHeight="1"/>
+    <row r="941" ht="15.0" customHeight="1"/>
+    <row r="942" ht="15.0" customHeight="1"/>
+    <row r="943" ht="15.0" customHeight="1"/>
+    <row r="944" ht="15.0" customHeight="1"/>
+    <row r="945" ht="15.0" customHeight="1"/>
+    <row r="946" ht="15.0" customHeight="1"/>
+    <row r="947" ht="15.0" customHeight="1"/>
+    <row r="948" ht="15.0" customHeight="1"/>
+    <row r="949" ht="15.0" customHeight="1"/>
+    <row r="950" ht="15.0" customHeight="1"/>
+    <row r="951" ht="15.0" customHeight="1"/>
+    <row r="952" ht="15.0" customHeight="1"/>
+    <row r="953" ht="15.0" customHeight="1"/>
+    <row r="954" ht="15.0" customHeight="1"/>
+    <row r="955" ht="15.0" customHeight="1"/>
+    <row r="956" ht="15.0" customHeight="1"/>
+    <row r="957" ht="15.0" customHeight="1"/>
+    <row r="958" ht="15.0" customHeight="1"/>
+    <row r="959" ht="15.0" customHeight="1"/>
+    <row r="960" ht="15.0" customHeight="1"/>
+    <row r="961" ht="15.0" customHeight="1"/>
+    <row r="962" ht="15.0" customHeight="1"/>
+    <row r="963" ht="15.0" customHeight="1"/>
+    <row r="964" ht="15.0" customHeight="1"/>
+    <row r="965" ht="15.0" customHeight="1"/>
+    <row r="966" ht="15.0" customHeight="1"/>
+    <row r="967" ht="15.0" customHeight="1"/>
+    <row r="968" ht="15.0" customHeight="1"/>
+    <row r="969" ht="15.0" customHeight="1"/>
+    <row r="970" ht="15.0" customHeight="1"/>
+    <row r="971" ht="15.0" customHeight="1"/>
+    <row r="972" ht="15.0" customHeight="1"/>
+    <row r="973" ht="15.0" customHeight="1"/>
+    <row r="974" ht="15.0" customHeight="1"/>
+    <row r="975" ht="15.0" customHeight="1"/>
+    <row r="976" ht="15.0" customHeight="1"/>
+    <row r="977" ht="15.0" customHeight="1"/>
+    <row r="978" ht="15.0" customHeight="1"/>
+    <row r="979" ht="15.0" customHeight="1"/>
+    <row r="980" ht="15.0" customHeight="1"/>
+    <row r="981" ht="15.0" customHeight="1"/>
+    <row r="982" ht="15.0" customHeight="1"/>
+    <row r="983" ht="15.0" customHeight="1"/>
+    <row r="984" ht="15.0" customHeight="1"/>
+    <row r="985" ht="15.0" customHeight="1"/>
+    <row r="986" ht="15.0" customHeight="1"/>
+    <row r="987" ht="15.0" customHeight="1"/>
+    <row r="988" ht="15.0" customHeight="1"/>
+    <row r="989" ht="15.0" customHeight="1"/>
+    <row r="990" ht="15.0" customHeight="1"/>
+    <row r="991" ht="15.0" customHeight="1"/>
+    <row r="992" ht="15.0" customHeight="1"/>
+    <row r="993" ht="15.0" customHeight="1"/>
+    <row r="994" ht="15.0" customHeight="1"/>
+    <row r="995" ht="15.0" customHeight="1"/>
+    <row r="996" ht="15.0" customHeight="1"/>
+    <row r="997" ht="15.0" customHeight="1"/>
+    <row r="998" ht="15.0" customHeight="1"/>
+    <row r="999" ht="15.0" customHeight="1"/>
+    <row r="1000" ht="15.0" customHeight="1"/>
+    <row r="1001" ht="15.0" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
   <si>
     <t>ID</t>
   </si>
@@ -86,6 +86,42 @@
   </si>
   <si>
     <t>Are you sure you want to quit the editor?</t>
+  </si>
+  <si>
+    <t>EDITOR_REMOVE_LP_MSG</t>
+  </si>
+  <si>
+    <t>에디터 레벨 제거 팝업 메세지</t>
+  </si>
+  <si>
+    <t>레벨을 제거하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove the level?</t>
+  </si>
+  <si>
+    <t>EDITOR_REMOVE_SP_MSG</t>
+  </si>
+  <si>
+    <t>에디터 스테이지 제거 팝업 메세지</t>
+  </si>
+  <si>
+    <t>스테이지를 제거하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove the stage?</t>
+  </si>
+  <si>
+    <t>EDITOR_REMOVE_CP_MSG</t>
+  </si>
+  <si>
+    <t>에디터 챕터 제거 팝업 메세지</t>
+  </si>
+  <si>
+    <t>챕터를 제거하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove the chapter?</t>
   </si>
   <si>
     <t>UPDATE_P_MSG</t>
@@ -783,19 +819,19 @@
       <c r="Y5" s="5"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="5"/>
@@ -820,19 +856,19 @@
       <c r="Y6" s="5"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="5"/>
@@ -857,19 +893,19 @@
       <c r="Y7" s="5"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F8" s="5"/>
@@ -894,19 +930,19 @@
       <c r="Y8" s="5"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F9" s="5"/>
@@ -931,78 +967,78 @@
       <c r="Y9" s="5"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="4" t="s">
@@ -1042,78 +1078,78 @@
       <c r="Y12" s="5"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
@@ -1163,10 +1199,10 @@
         <v>62</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1191,19 +1227,19 @@
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17" s="5">
         <v>0.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1228,19 +1264,19 @@
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5">
         <v>0.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -1265,19 +1301,19 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5">
         <v>0.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -1302,19 +1338,19 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B20" s="5">
         <v>0.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -1339,19 +1375,19 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B21" s="5">
         <v>0.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -1376,19 +1412,19 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B22" s="5">
         <v>0.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -1413,19 +1449,19 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B23" s="5">
         <v>0.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -1450,19 +1486,19 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B24" s="5">
         <v>0.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -1487,19 +1523,19 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" s="5">
         <v>0.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -1560,45 +1596,153 @@
       <c r="Y26" s="5"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="C27" s="12" t="s">
+      <c r="B27" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-    </row>
-    <row r="28" ht="15.0" customHeight="1"/>
-    <row r="29" ht="15.0" customHeight="1"/>
-    <row r="30" ht="15.0" customHeight="1"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+    </row>
+    <row r="28" ht="15.0" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+    </row>
+    <row r="29" ht="15.0" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+    </row>
+    <row r="30" ht="15.0" customHeight="1">
+      <c r="A30" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+    </row>
     <row r="31" ht="15.0" customHeight="1"/>
     <row r="32" ht="15.0" customHeight="1"/>
     <row r="33" ht="15.0" customHeight="1"/>
@@ -1799,777 +1943,779 @@
     <row r="228" ht="15.0" customHeight="1"/>
     <row r="229" ht="15.0" customHeight="1"/>
     <row r="230" ht="15.0" customHeight="1"/>
-    <row r="231" ht="15.0" customHeight="1"/>
-    <row r="232" ht="15.0" customHeight="1"/>
-    <row r="233" ht="15.0" customHeight="1"/>
-    <row r="234" ht="15.0" customHeight="1"/>
-    <row r="235" ht="15.0" customHeight="1"/>
-    <row r="236" ht="15.0" customHeight="1"/>
-    <row r="237" ht="15.0" customHeight="1"/>
-    <row r="238" ht="15.0" customHeight="1"/>
-    <row r="239" ht="15.0" customHeight="1"/>
-    <row r="240" ht="15.0" customHeight="1"/>
-    <row r="241" ht="15.0" customHeight="1"/>
-    <row r="242" ht="15.0" customHeight="1"/>
-    <row r="243" ht="15.0" customHeight="1"/>
-    <row r="244" ht="15.0" customHeight="1"/>
-    <row r="245" ht="15.0" customHeight="1"/>
-    <row r="246" ht="15.0" customHeight="1"/>
-    <row r="247" ht="15.0" customHeight="1"/>
-    <row r="248" ht="15.0" customHeight="1"/>
-    <row r="249" ht="15.0" customHeight="1"/>
-    <row r="250" ht="15.0" customHeight="1"/>
-    <row r="251" ht="15.0" customHeight="1"/>
-    <row r="252" ht="15.0" customHeight="1"/>
-    <row r="253" ht="15.0" customHeight="1"/>
-    <row r="254" ht="15.0" customHeight="1"/>
-    <row r="255" ht="15.0" customHeight="1"/>
-    <row r="256" ht="15.0" customHeight="1"/>
-    <row r="257" ht="15.0" customHeight="1"/>
-    <row r="258" ht="15.0" customHeight="1"/>
-    <row r="259" ht="15.0" customHeight="1"/>
-    <row r="260" ht="15.0" customHeight="1"/>
-    <row r="261" ht="15.0" customHeight="1"/>
-    <row r="262" ht="15.0" customHeight="1"/>
-    <row r="263" ht="15.0" customHeight="1"/>
-    <row r="264" ht="15.0" customHeight="1"/>
-    <row r="265" ht="15.0" customHeight="1"/>
-    <row r="266" ht="15.0" customHeight="1"/>
-    <row r="267" ht="15.0" customHeight="1"/>
-    <row r="268" ht="15.0" customHeight="1"/>
-    <row r="269" ht="15.0" customHeight="1"/>
-    <row r="270" ht="15.0" customHeight="1"/>
-    <row r="271" ht="15.0" customHeight="1"/>
-    <row r="272" ht="15.0" customHeight="1"/>
-    <row r="273" ht="15.0" customHeight="1"/>
-    <row r="274" ht="15.0" customHeight="1"/>
-    <row r="275" ht="15.0" customHeight="1"/>
-    <row r="276" ht="15.0" customHeight="1"/>
-    <row r="277" ht="15.0" customHeight="1"/>
-    <row r="278" ht="15.0" customHeight="1"/>
-    <row r="279" ht="15.0" customHeight="1"/>
-    <row r="280" ht="15.0" customHeight="1"/>
-    <row r="281" ht="15.0" customHeight="1"/>
-    <row r="282" ht="15.0" customHeight="1"/>
-    <row r="283" ht="15.0" customHeight="1"/>
-    <row r="284" ht="15.0" customHeight="1"/>
-    <row r="285" ht="15.0" customHeight="1"/>
-    <row r="286" ht="15.0" customHeight="1"/>
-    <row r="287" ht="15.0" customHeight="1"/>
-    <row r="288" ht="15.0" customHeight="1"/>
-    <row r="289" ht="15.0" customHeight="1"/>
-    <row r="290" ht="15.0" customHeight="1"/>
-    <row r="291" ht="15.0" customHeight="1"/>
-    <row r="292" ht="15.0" customHeight="1"/>
-    <row r="293" ht="15.0" customHeight="1"/>
-    <row r="294" ht="15.0" customHeight="1"/>
-    <row r="295" ht="15.0" customHeight="1"/>
-    <row r="296" ht="15.0" customHeight="1"/>
-    <row r="297" ht="15.0" customHeight="1"/>
-    <row r="298" ht="15.0" customHeight="1"/>
-    <row r="299" ht="15.0" customHeight="1"/>
-    <row r="300" ht="15.0" customHeight="1"/>
-    <row r="301" ht="15.0" customHeight="1"/>
-    <row r="302" ht="15.0" customHeight="1"/>
-    <row r="303" ht="15.0" customHeight="1"/>
-    <row r="304" ht="15.0" customHeight="1"/>
-    <row r="305" ht="15.0" customHeight="1"/>
-    <row r="306" ht="15.0" customHeight="1"/>
-    <row r="307" ht="15.0" customHeight="1"/>
-    <row r="308" ht="15.0" customHeight="1"/>
-    <row r="309" ht="15.0" customHeight="1"/>
-    <row r="310" ht="15.0" customHeight="1"/>
-    <row r="311" ht="15.0" customHeight="1"/>
-    <row r="312" ht="15.0" customHeight="1"/>
-    <row r="313" ht="15.0" customHeight="1"/>
-    <row r="314" ht="15.0" customHeight="1"/>
-    <row r="315" ht="15.0" customHeight="1"/>
-    <row r="316" ht="15.0" customHeight="1"/>
-    <row r="317" ht="15.0" customHeight="1"/>
-    <row r="318" ht="15.0" customHeight="1"/>
-    <row r="319" ht="15.0" customHeight="1"/>
-    <row r="320" ht="15.0" customHeight="1"/>
-    <row r="321" ht="15.0" customHeight="1"/>
-    <row r="322" ht="15.0" customHeight="1"/>
-    <row r="323" ht="15.0" customHeight="1"/>
-    <row r="324" ht="15.0" customHeight="1"/>
-    <row r="325" ht="15.0" customHeight="1"/>
-    <row r="326" ht="15.0" customHeight="1"/>
-    <row r="327" ht="15.0" customHeight="1"/>
-    <row r="328" ht="15.0" customHeight="1"/>
-    <row r="329" ht="15.0" customHeight="1"/>
-    <row r="330" ht="15.0" customHeight="1"/>
-    <row r="331" ht="15.0" customHeight="1"/>
-    <row r="332" ht="15.0" customHeight="1"/>
-    <row r="333" ht="15.0" customHeight="1"/>
-    <row r="334" ht="15.0" customHeight="1"/>
-    <row r="335" ht="15.0" customHeight="1"/>
-    <row r="336" ht="15.0" customHeight="1"/>
-    <row r="337" ht="15.0" customHeight="1"/>
-    <row r="338" ht="15.0" customHeight="1"/>
-    <row r="339" ht="15.0" customHeight="1"/>
-    <row r="340" ht="15.0" customHeight="1"/>
-    <row r="341" ht="15.0" customHeight="1"/>
-    <row r="342" ht="15.0" customHeight="1"/>
-    <row r="343" ht="15.0" customHeight="1"/>
-    <row r="344" ht="15.0" customHeight="1"/>
-    <row r="345" ht="15.0" customHeight="1"/>
-    <row r="346" ht="15.0" customHeight="1"/>
-    <row r="347" ht="15.0" customHeight="1"/>
-    <row r="348" ht="15.0" customHeight="1"/>
-    <row r="349" ht="15.0" customHeight="1"/>
-    <row r="350" ht="15.0" customHeight="1"/>
-    <row r="351" ht="15.0" customHeight="1"/>
-    <row r="352" ht="15.0" customHeight="1"/>
-    <row r="353" ht="15.0" customHeight="1"/>
-    <row r="354" ht="15.0" customHeight="1"/>
-    <row r="355" ht="15.0" customHeight="1"/>
-    <row r="356" ht="15.0" customHeight="1"/>
-    <row r="357" ht="15.0" customHeight="1"/>
-    <row r="358" ht="15.0" customHeight="1"/>
-    <row r="359" ht="15.0" customHeight="1"/>
-    <row r="360" ht="15.0" customHeight="1"/>
-    <row r="361" ht="15.0" customHeight="1"/>
-    <row r="362" ht="15.0" customHeight="1"/>
-    <row r="363" ht="15.0" customHeight="1"/>
-    <row r="364" ht="15.0" customHeight="1"/>
-    <row r="365" ht="15.0" customHeight="1"/>
-    <row r="366" ht="15.0" customHeight="1"/>
-    <row r="367" ht="15.0" customHeight="1"/>
-    <row r="368" ht="15.0" customHeight="1"/>
-    <row r="369" ht="15.0" customHeight="1"/>
-    <row r="370" ht="15.0" customHeight="1"/>
-    <row r="371" ht="15.0" customHeight="1"/>
-    <row r="372" ht="15.0" customHeight="1"/>
-    <row r="373" ht="15.0" customHeight="1"/>
-    <row r="374" ht="15.0" customHeight="1"/>
-    <row r="375" ht="15.0" customHeight="1"/>
-    <row r="376" ht="15.0" customHeight="1"/>
-    <row r="377" ht="15.0" customHeight="1"/>
-    <row r="378" ht="15.0" customHeight="1"/>
-    <row r="379" ht="15.0" customHeight="1"/>
-    <row r="380" ht="15.0" customHeight="1"/>
-    <row r="381" ht="15.0" customHeight="1"/>
-    <row r="382" ht="15.0" customHeight="1"/>
-    <row r="383" ht="15.0" customHeight="1"/>
-    <row r="384" ht="15.0" customHeight="1"/>
-    <row r="385" ht="15.0" customHeight="1"/>
-    <row r="386" ht="15.0" customHeight="1"/>
-    <row r="387" ht="15.0" customHeight="1"/>
-    <row r="388" ht="15.0" customHeight="1"/>
-    <row r="389" ht="15.0" customHeight="1"/>
-    <row r="390" ht="15.0" customHeight="1"/>
-    <row r="391" ht="15.0" customHeight="1"/>
-    <row r="392" ht="15.0" customHeight="1"/>
-    <row r="393" ht="15.0" customHeight="1"/>
-    <row r="394" ht="15.0" customHeight="1"/>
-    <row r="395" ht="15.0" customHeight="1"/>
-    <row r="396" ht="15.0" customHeight="1"/>
-    <row r="397" ht="15.0" customHeight="1"/>
-    <row r="398" ht="15.0" customHeight="1"/>
-    <row r="399" ht="15.0" customHeight="1"/>
-    <row r="400" ht="15.0" customHeight="1"/>
-    <row r="401" ht="15.0" customHeight="1"/>
-    <row r="402" ht="15.0" customHeight="1"/>
-    <row r="403" ht="15.0" customHeight="1"/>
-    <row r="404" ht="15.0" customHeight="1"/>
-    <row r="405" ht="15.0" customHeight="1"/>
-    <row r="406" ht="15.0" customHeight="1"/>
-    <row r="407" ht="15.0" customHeight="1"/>
-    <row r="408" ht="15.0" customHeight="1"/>
-    <row r="409" ht="15.0" customHeight="1"/>
-    <row r="410" ht="15.0" customHeight="1"/>
-    <row r="411" ht="15.0" customHeight="1"/>
-    <row r="412" ht="15.0" customHeight="1"/>
-    <row r="413" ht="15.0" customHeight="1"/>
-    <row r="414" ht="15.0" customHeight="1"/>
-    <row r="415" ht="15.0" customHeight="1"/>
-    <row r="416" ht="15.0" customHeight="1"/>
-    <row r="417" ht="15.0" customHeight="1"/>
-    <row r="418" ht="15.0" customHeight="1"/>
-    <row r="419" ht="15.0" customHeight="1"/>
-    <row r="420" ht="15.0" customHeight="1"/>
-    <row r="421" ht="15.0" customHeight="1"/>
-    <row r="422" ht="15.0" customHeight="1"/>
-    <row r="423" ht="15.0" customHeight="1"/>
-    <row r="424" ht="15.0" customHeight="1"/>
-    <row r="425" ht="15.0" customHeight="1"/>
-    <row r="426" ht="15.0" customHeight="1"/>
-    <row r="427" ht="15.0" customHeight="1"/>
-    <row r="428" ht="15.0" customHeight="1"/>
-    <row r="429" ht="15.0" customHeight="1"/>
-    <row r="430" ht="15.0" customHeight="1"/>
-    <row r="431" ht="15.0" customHeight="1"/>
-    <row r="432" ht="15.0" customHeight="1"/>
-    <row r="433" ht="15.0" customHeight="1"/>
-    <row r="434" ht="15.0" customHeight="1"/>
-    <row r="435" ht="15.0" customHeight="1"/>
-    <row r="436" ht="15.0" customHeight="1"/>
-    <row r="437" ht="15.0" customHeight="1"/>
-    <row r="438" ht="15.0" customHeight="1"/>
-    <row r="439" ht="15.0" customHeight="1"/>
-    <row r="440" ht="15.0" customHeight="1"/>
-    <row r="441" ht="15.0" customHeight="1"/>
-    <row r="442" ht="15.0" customHeight="1"/>
-    <row r="443" ht="15.0" customHeight="1"/>
-    <row r="444" ht="15.0" customHeight="1"/>
-    <row r="445" ht="15.0" customHeight="1"/>
-    <row r="446" ht="15.0" customHeight="1"/>
-    <row r="447" ht="15.0" customHeight="1"/>
-    <row r="448" ht="15.0" customHeight="1"/>
-    <row r="449" ht="15.0" customHeight="1"/>
-    <row r="450" ht="15.0" customHeight="1"/>
-    <row r="451" ht="15.0" customHeight="1"/>
-    <row r="452" ht="15.0" customHeight="1"/>
-    <row r="453" ht="15.0" customHeight="1"/>
-    <row r="454" ht="15.0" customHeight="1"/>
-    <row r="455" ht="15.0" customHeight="1"/>
-    <row r="456" ht="15.0" customHeight="1"/>
-    <row r="457" ht="15.0" customHeight="1"/>
-    <row r="458" ht="15.0" customHeight="1"/>
-    <row r="459" ht="15.0" customHeight="1"/>
-    <row r="460" ht="15.0" customHeight="1"/>
-    <row r="461" ht="15.0" customHeight="1"/>
-    <row r="462" ht="15.0" customHeight="1"/>
-    <row r="463" ht="15.0" customHeight="1"/>
-    <row r="464" ht="15.0" customHeight="1"/>
-    <row r="465" ht="15.0" customHeight="1"/>
-    <row r="466" ht="15.0" customHeight="1"/>
-    <row r="467" ht="15.0" customHeight="1"/>
-    <row r="468" ht="15.0" customHeight="1"/>
-    <row r="469" ht="15.0" customHeight="1"/>
-    <row r="470" ht="15.0" customHeight="1"/>
-    <row r="471" ht="15.0" customHeight="1"/>
-    <row r="472" ht="15.0" customHeight="1"/>
-    <row r="473" ht="15.0" customHeight="1"/>
-    <row r="474" ht="15.0" customHeight="1"/>
-    <row r="475" ht="15.0" customHeight="1"/>
-    <row r="476" ht="15.0" customHeight="1"/>
-    <row r="477" ht="15.0" customHeight="1"/>
-    <row r="478" ht="15.0" customHeight="1"/>
-    <row r="479" ht="15.0" customHeight="1"/>
-    <row r="480" ht="15.0" customHeight="1"/>
-    <row r="481" ht="15.0" customHeight="1"/>
-    <row r="482" ht="15.0" customHeight="1"/>
-    <row r="483" ht="15.0" customHeight="1"/>
-    <row r="484" ht="15.0" customHeight="1"/>
-    <row r="485" ht="15.0" customHeight="1"/>
-    <row r="486" ht="15.0" customHeight="1"/>
-    <row r="487" ht="15.0" customHeight="1"/>
-    <row r="488" ht="15.0" customHeight="1"/>
-    <row r="489" ht="15.0" customHeight="1"/>
-    <row r="490" ht="15.0" customHeight="1"/>
-    <row r="491" ht="15.0" customHeight="1"/>
-    <row r="492" ht="15.0" customHeight="1"/>
-    <row r="493" ht="15.0" customHeight="1"/>
-    <row r="494" ht="15.0" customHeight="1"/>
-    <row r="495" ht="15.0" customHeight="1"/>
-    <row r="496" ht="15.0" customHeight="1"/>
-    <row r="497" ht="15.0" customHeight="1"/>
-    <row r="498" ht="15.0" customHeight="1"/>
-    <row r="499" ht="15.0" customHeight="1"/>
-    <row r="500" ht="15.0" customHeight="1"/>
-    <row r="501" ht="15.0" customHeight="1"/>
-    <row r="502" ht="15.0" customHeight="1"/>
-    <row r="503" ht="15.0" customHeight="1"/>
-    <row r="504" ht="15.0" customHeight="1"/>
-    <row r="505" ht="15.0" customHeight="1"/>
-    <row r="506" ht="15.0" customHeight="1"/>
-    <row r="507" ht="15.0" customHeight="1"/>
-    <row r="508" ht="15.0" customHeight="1"/>
-    <row r="509" ht="15.0" customHeight="1"/>
-    <row r="510" ht="15.0" customHeight="1"/>
-    <row r="511" ht="15.0" customHeight="1"/>
-    <row r="512" ht="15.0" customHeight="1"/>
-    <row r="513" ht="15.0" customHeight="1"/>
-    <row r="514" ht="15.0" customHeight="1"/>
-    <row r="515" ht="15.0" customHeight="1"/>
-    <row r="516" ht="15.0" customHeight="1"/>
-    <row r="517" ht="15.0" customHeight="1"/>
-    <row r="518" ht="15.0" customHeight="1"/>
-    <row r="519" ht="15.0" customHeight="1"/>
-    <row r="520" ht="15.0" customHeight="1"/>
-    <row r="521" ht="15.0" customHeight="1"/>
-    <row r="522" ht="15.0" customHeight="1"/>
-    <row r="523" ht="15.0" customHeight="1"/>
-    <row r="524" ht="15.0" customHeight="1"/>
-    <row r="525" ht="15.0" customHeight="1"/>
-    <row r="526" ht="15.0" customHeight="1"/>
-    <row r="527" ht="15.0" customHeight="1"/>
-    <row r="528" ht="15.0" customHeight="1"/>
-    <row r="529" ht="15.0" customHeight="1"/>
-    <row r="530" ht="15.0" customHeight="1"/>
-    <row r="531" ht="15.0" customHeight="1"/>
-    <row r="532" ht="15.0" customHeight="1"/>
-    <row r="533" ht="15.0" customHeight="1"/>
-    <row r="534" ht="15.0" customHeight="1"/>
-    <row r="535" ht="15.0" customHeight="1"/>
-    <row r="536" ht="15.0" customHeight="1"/>
-    <row r="537" ht="15.0" customHeight="1"/>
-    <row r="538" ht="15.0" customHeight="1"/>
-    <row r="539" ht="15.0" customHeight="1"/>
-    <row r="540" ht="15.0" customHeight="1"/>
-    <row r="541" ht="15.0" customHeight="1"/>
-    <row r="542" ht="15.0" customHeight="1"/>
-    <row r="543" ht="15.0" customHeight="1"/>
-    <row r="544" ht="15.0" customHeight="1"/>
-    <row r="545" ht="15.0" customHeight="1"/>
-    <row r="546" ht="15.0" customHeight="1"/>
-    <row r="547" ht="15.0" customHeight="1"/>
-    <row r="548" ht="15.0" customHeight="1"/>
-    <row r="549" ht="15.0" customHeight="1"/>
-    <row r="550" ht="15.0" customHeight="1"/>
-    <row r="551" ht="15.0" customHeight="1"/>
-    <row r="552" ht="15.0" customHeight="1"/>
-    <row r="553" ht="15.0" customHeight="1"/>
-    <row r="554" ht="15.0" customHeight="1"/>
-    <row r="555" ht="15.0" customHeight="1"/>
-    <row r="556" ht="15.0" customHeight="1"/>
-    <row r="557" ht="15.0" customHeight="1"/>
-    <row r="558" ht="15.0" customHeight="1"/>
-    <row r="559" ht="15.0" customHeight="1"/>
-    <row r="560" ht="15.0" customHeight="1"/>
-    <row r="561" ht="15.0" customHeight="1"/>
-    <row r="562" ht="15.0" customHeight="1"/>
-    <row r="563" ht="15.0" customHeight="1"/>
-    <row r="564" ht="15.0" customHeight="1"/>
-    <row r="565" ht="15.0" customHeight="1"/>
-    <row r="566" ht="15.0" customHeight="1"/>
-    <row r="567" ht="15.0" customHeight="1"/>
-    <row r="568" ht="15.0" customHeight="1"/>
-    <row r="569" ht="15.0" customHeight="1"/>
-    <row r="570" ht="15.0" customHeight="1"/>
-    <row r="571" ht="15.0" customHeight="1"/>
-    <row r="572" ht="15.0" customHeight="1"/>
-    <row r="573" ht="15.0" customHeight="1"/>
-    <row r="574" ht="15.0" customHeight="1"/>
-    <row r="575" ht="15.0" customHeight="1"/>
-    <row r="576" ht="15.0" customHeight="1"/>
-    <row r="577" ht="15.0" customHeight="1"/>
-    <row r="578" ht="15.0" customHeight="1"/>
-    <row r="579" ht="15.0" customHeight="1"/>
-    <row r="580" ht="15.0" customHeight="1"/>
-    <row r="581" ht="15.0" customHeight="1"/>
-    <row r="582" ht="15.0" customHeight="1"/>
-    <row r="583" ht="15.0" customHeight="1"/>
-    <row r="584" ht="15.0" customHeight="1"/>
-    <row r="585" ht="15.0" customHeight="1"/>
-    <row r="586" ht="15.0" customHeight="1"/>
-    <row r="587" ht="15.0" customHeight="1"/>
-    <row r="588" ht="15.0" customHeight="1"/>
-    <row r="589" ht="15.0" customHeight="1"/>
-    <row r="590" ht="15.0" customHeight="1"/>
-    <row r="591" ht="15.0" customHeight="1"/>
-    <row r="592" ht="15.0" customHeight="1"/>
-    <row r="593" ht="15.0" customHeight="1"/>
-    <row r="594" ht="15.0" customHeight="1"/>
-    <row r="595" ht="15.0" customHeight="1"/>
-    <row r="596" ht="15.0" customHeight="1"/>
-    <row r="597" ht="15.0" customHeight="1"/>
-    <row r="598" ht="15.0" customHeight="1"/>
-    <row r="599" ht="15.0" customHeight="1"/>
-    <row r="600" ht="15.0" customHeight="1"/>
-    <row r="601" ht="15.0" customHeight="1"/>
-    <row r="602" ht="15.0" customHeight="1"/>
-    <row r="603" ht="15.0" customHeight="1"/>
-    <row r="604" ht="15.0" customHeight="1"/>
-    <row r="605" ht="15.0" customHeight="1"/>
-    <row r="606" ht="15.0" customHeight="1"/>
-    <row r="607" ht="15.0" customHeight="1"/>
-    <row r="608" ht="15.0" customHeight="1"/>
-    <row r="609" ht="15.0" customHeight="1"/>
-    <row r="610" ht="15.0" customHeight="1"/>
-    <row r="611" ht="15.0" customHeight="1"/>
-    <row r="612" ht="15.0" customHeight="1"/>
-    <row r="613" ht="15.0" customHeight="1"/>
-    <row r="614" ht="15.0" customHeight="1"/>
-    <row r="615" ht="15.0" customHeight="1"/>
-    <row r="616" ht="15.0" customHeight="1"/>
-    <row r="617" ht="15.0" customHeight="1"/>
-    <row r="618" ht="15.0" customHeight="1"/>
-    <row r="619" ht="15.0" customHeight="1"/>
-    <row r="620" ht="15.0" customHeight="1"/>
-    <row r="621" ht="15.0" customHeight="1"/>
-    <row r="622" ht="15.0" customHeight="1"/>
-    <row r="623" ht="15.0" customHeight="1"/>
-    <row r="624" ht="15.0" customHeight="1"/>
-    <row r="625" ht="15.0" customHeight="1"/>
-    <row r="626" ht="15.0" customHeight="1"/>
-    <row r="627" ht="15.0" customHeight="1"/>
-    <row r="628" ht="15.0" customHeight="1"/>
-    <row r="629" ht="15.0" customHeight="1"/>
-    <row r="630" ht="15.0" customHeight="1"/>
-    <row r="631" ht="15.0" customHeight="1"/>
-    <row r="632" ht="15.0" customHeight="1"/>
-    <row r="633" ht="15.0" customHeight="1"/>
-    <row r="634" ht="15.0" customHeight="1"/>
-    <row r="635" ht="15.0" customHeight="1"/>
-    <row r="636" ht="15.0" customHeight="1"/>
-    <row r="637" ht="15.0" customHeight="1"/>
-    <row r="638" ht="15.0" customHeight="1"/>
-    <row r="639" ht="15.0" customHeight="1"/>
-    <row r="640" ht="15.0" customHeight="1"/>
-    <row r="641" ht="15.0" customHeight="1"/>
-    <row r="642" ht="15.0" customHeight="1"/>
-    <row r="643" ht="15.0" customHeight="1"/>
-    <row r="644" ht="15.0" customHeight="1"/>
-    <row r="645" ht="15.0" customHeight="1"/>
-    <row r="646" ht="15.0" customHeight="1"/>
-    <row r="647" ht="15.0" customHeight="1"/>
-    <row r="648" ht="15.0" customHeight="1"/>
-    <row r="649" ht="15.0" customHeight="1"/>
-    <row r="650" ht="15.0" customHeight="1"/>
-    <row r="651" ht="15.0" customHeight="1"/>
-    <row r="652" ht="15.0" customHeight="1"/>
-    <row r="653" ht="15.0" customHeight="1"/>
-    <row r="654" ht="15.0" customHeight="1"/>
-    <row r="655" ht="15.0" customHeight="1"/>
-    <row r="656" ht="15.0" customHeight="1"/>
-    <row r="657" ht="15.0" customHeight="1"/>
-    <row r="658" ht="15.0" customHeight="1"/>
-    <row r="659" ht="15.0" customHeight="1"/>
-    <row r="660" ht="15.0" customHeight="1"/>
-    <row r="661" ht="15.0" customHeight="1"/>
-    <row r="662" ht="15.0" customHeight="1"/>
-    <row r="663" ht="15.0" customHeight="1"/>
-    <row r="664" ht="15.0" customHeight="1"/>
-    <row r="665" ht="15.0" customHeight="1"/>
-    <row r="666" ht="15.0" customHeight="1"/>
-    <row r="667" ht="15.0" customHeight="1"/>
-    <row r="668" ht="15.0" customHeight="1"/>
-    <row r="669" ht="15.0" customHeight="1"/>
-    <row r="670" ht="15.0" customHeight="1"/>
-    <row r="671" ht="15.0" customHeight="1"/>
-    <row r="672" ht="15.0" customHeight="1"/>
-    <row r="673" ht="15.0" customHeight="1"/>
-    <row r="674" ht="15.0" customHeight="1"/>
-    <row r="675" ht="15.0" customHeight="1"/>
-    <row r="676" ht="15.0" customHeight="1"/>
-    <row r="677" ht="15.0" customHeight="1"/>
-    <row r="678" ht="15.0" customHeight="1"/>
-    <row r="679" ht="15.0" customHeight="1"/>
-    <row r="680" ht="15.0" customHeight="1"/>
-    <row r="681" ht="15.0" customHeight="1"/>
-    <row r="682" ht="15.0" customHeight="1"/>
-    <row r="683" ht="15.0" customHeight="1"/>
-    <row r="684" ht="15.0" customHeight="1"/>
-    <row r="685" ht="15.0" customHeight="1"/>
-    <row r="686" ht="15.0" customHeight="1"/>
-    <row r="687" ht="15.0" customHeight="1"/>
-    <row r="688" ht="15.0" customHeight="1"/>
-    <row r="689" ht="15.0" customHeight="1"/>
-    <row r="690" ht="15.0" customHeight="1"/>
-    <row r="691" ht="15.0" customHeight="1"/>
-    <row r="692" ht="15.0" customHeight="1"/>
-    <row r="693" ht="15.0" customHeight="1"/>
-    <row r="694" ht="15.0" customHeight="1"/>
-    <row r="695" ht="15.0" customHeight="1"/>
-    <row r="696" ht="15.0" customHeight="1"/>
-    <row r="697" ht="15.0" customHeight="1"/>
-    <row r="698" ht="15.0" customHeight="1"/>
-    <row r="699" ht="15.0" customHeight="1"/>
-    <row r="700" ht="15.0" customHeight="1"/>
-    <row r="701" ht="15.0" customHeight="1"/>
-    <row r="702" ht="15.0" customHeight="1"/>
-    <row r="703" ht="15.0" customHeight="1"/>
-    <row r="704" ht="15.0" customHeight="1"/>
-    <row r="705" ht="15.0" customHeight="1"/>
-    <row r="706" ht="15.0" customHeight="1"/>
-    <row r="707" ht="15.0" customHeight="1"/>
-    <row r="708" ht="15.0" customHeight="1"/>
-    <row r="709" ht="15.0" customHeight="1"/>
-    <row r="710" ht="15.0" customHeight="1"/>
-    <row r="711" ht="15.0" customHeight="1"/>
-    <row r="712" ht="15.0" customHeight="1"/>
-    <row r="713" ht="15.0" customHeight="1"/>
-    <row r="714" ht="15.0" customHeight="1"/>
-    <row r="715" ht="15.0" customHeight="1"/>
-    <row r="716" ht="15.0" customHeight="1"/>
-    <row r="717" ht="15.0" customHeight="1"/>
-    <row r="718" ht="15.0" customHeight="1"/>
-    <row r="719" ht="15.0" customHeight="1"/>
-    <row r="720" ht="15.0" customHeight="1"/>
-    <row r="721" ht="15.0" customHeight="1"/>
-    <row r="722" ht="15.0" customHeight="1"/>
-    <row r="723" ht="15.0" customHeight="1"/>
-    <row r="724" ht="15.0" customHeight="1"/>
-    <row r="725" ht="15.0" customHeight="1"/>
-    <row r="726" ht="15.0" customHeight="1"/>
-    <row r="727" ht="15.0" customHeight="1"/>
-    <row r="728" ht="15.0" customHeight="1"/>
-    <row r="729" ht="15.0" customHeight="1"/>
-    <row r="730" ht="15.0" customHeight="1"/>
-    <row r="731" ht="15.0" customHeight="1"/>
-    <row r="732" ht="15.0" customHeight="1"/>
-    <row r="733" ht="15.0" customHeight="1"/>
-    <row r="734" ht="15.0" customHeight="1"/>
-    <row r="735" ht="15.0" customHeight="1"/>
-    <row r="736" ht="15.0" customHeight="1"/>
-    <row r="737" ht="15.0" customHeight="1"/>
-    <row r="738" ht="15.0" customHeight="1"/>
-    <row r="739" ht="15.0" customHeight="1"/>
-    <row r="740" ht="15.0" customHeight="1"/>
-    <row r="741" ht="15.0" customHeight="1"/>
-    <row r="742" ht="15.0" customHeight="1"/>
-    <row r="743" ht="15.0" customHeight="1"/>
-    <row r="744" ht="15.0" customHeight="1"/>
-    <row r="745" ht="15.0" customHeight="1"/>
-    <row r="746" ht="15.0" customHeight="1"/>
-    <row r="747" ht="15.0" customHeight="1"/>
-    <row r="748" ht="15.0" customHeight="1"/>
-    <row r="749" ht="15.0" customHeight="1"/>
-    <row r="750" ht="15.0" customHeight="1"/>
-    <row r="751" ht="15.0" customHeight="1"/>
-    <row r="752" ht="15.0" customHeight="1"/>
-    <row r="753" ht="15.0" customHeight="1"/>
-    <row r="754" ht="15.0" customHeight="1"/>
-    <row r="755" ht="15.0" customHeight="1"/>
-    <row r="756" ht="15.0" customHeight="1"/>
-    <row r="757" ht="15.0" customHeight="1"/>
-    <row r="758" ht="15.0" customHeight="1"/>
-    <row r="759" ht="15.0" customHeight="1"/>
-    <row r="760" ht="15.0" customHeight="1"/>
-    <row r="761" ht="15.0" customHeight="1"/>
-    <row r="762" ht="15.0" customHeight="1"/>
-    <row r="763" ht="15.0" customHeight="1"/>
-    <row r="764" ht="15.0" customHeight="1"/>
-    <row r="765" ht="15.0" customHeight="1"/>
-    <row r="766" ht="15.0" customHeight="1"/>
-    <row r="767" ht="15.0" customHeight="1"/>
-    <row r="768" ht="15.0" customHeight="1"/>
-    <row r="769" ht="15.0" customHeight="1"/>
-    <row r="770" ht="15.0" customHeight="1"/>
-    <row r="771" ht="15.0" customHeight="1"/>
-    <row r="772" ht="15.0" customHeight="1"/>
-    <row r="773" ht="15.0" customHeight="1"/>
-    <row r="774" ht="15.0" customHeight="1"/>
-    <row r="775" ht="15.0" customHeight="1"/>
-    <row r="776" ht="15.0" customHeight="1"/>
-    <row r="777" ht="15.0" customHeight="1"/>
-    <row r="778" ht="15.0" customHeight="1"/>
-    <row r="779" ht="15.0" customHeight="1"/>
-    <row r="780" ht="15.0" customHeight="1"/>
-    <row r="781" ht="15.0" customHeight="1"/>
-    <row r="782" ht="15.0" customHeight="1"/>
-    <row r="783" ht="15.0" customHeight="1"/>
-    <row r="784" ht="15.0" customHeight="1"/>
-    <row r="785" ht="15.0" customHeight="1"/>
-    <row r="786" ht="15.0" customHeight="1"/>
-    <row r="787" ht="15.0" customHeight="1"/>
-    <row r="788" ht="15.0" customHeight="1"/>
-    <row r="789" ht="15.0" customHeight="1"/>
-    <row r="790" ht="15.0" customHeight="1"/>
-    <row r="791" ht="15.0" customHeight="1"/>
-    <row r="792" ht="15.0" customHeight="1"/>
-    <row r="793" ht="15.0" customHeight="1"/>
-    <row r="794" ht="15.0" customHeight="1"/>
-    <row r="795" ht="15.0" customHeight="1"/>
-    <row r="796" ht="15.0" customHeight="1"/>
-    <row r="797" ht="15.0" customHeight="1"/>
-    <row r="798" ht="15.0" customHeight="1"/>
-    <row r="799" ht="15.0" customHeight="1"/>
-    <row r="800" ht="15.0" customHeight="1"/>
-    <row r="801" ht="15.0" customHeight="1"/>
-    <row r="802" ht="15.0" customHeight="1"/>
-    <row r="803" ht="15.0" customHeight="1"/>
-    <row r="804" ht="15.0" customHeight="1"/>
-    <row r="805" ht="15.0" customHeight="1"/>
-    <row r="806" ht="15.0" customHeight="1"/>
-    <row r="807" ht="15.0" customHeight="1"/>
-    <row r="808" ht="15.0" customHeight="1"/>
-    <row r="809" ht="15.0" customHeight="1"/>
-    <row r="810" ht="15.0" customHeight="1"/>
-    <row r="811" ht="15.0" customHeight="1"/>
-    <row r="812" ht="15.0" customHeight="1"/>
-    <row r="813" ht="15.0" customHeight="1"/>
-    <row r="814" ht="15.0" customHeight="1"/>
-    <row r="815" ht="15.0" customHeight="1"/>
-    <row r="816" ht="15.0" customHeight="1"/>
-    <row r="817" ht="15.0" customHeight="1"/>
-    <row r="818" ht="15.0" customHeight="1"/>
-    <row r="819" ht="15.0" customHeight="1"/>
-    <row r="820" ht="15.0" customHeight="1"/>
-    <row r="821" ht="15.0" customHeight="1"/>
-    <row r="822" ht="15.0" customHeight="1"/>
-    <row r="823" ht="15.0" customHeight="1"/>
-    <row r="824" ht="15.0" customHeight="1"/>
-    <row r="825" ht="15.0" customHeight="1"/>
-    <row r="826" ht="15.0" customHeight="1"/>
-    <row r="827" ht="15.0" customHeight="1"/>
-    <row r="828" ht="15.0" customHeight="1"/>
-    <row r="829" ht="15.0" customHeight="1"/>
-    <row r="830" ht="15.0" customHeight="1"/>
-    <row r="831" ht="15.0" customHeight="1"/>
-    <row r="832" ht="15.0" customHeight="1"/>
-    <row r="833" ht="15.0" customHeight="1"/>
-    <row r="834" ht="15.0" customHeight="1"/>
-    <row r="835" ht="15.0" customHeight="1"/>
-    <row r="836" ht="15.0" customHeight="1"/>
-    <row r="837" ht="15.0" customHeight="1"/>
-    <row r="838" ht="15.0" customHeight="1"/>
-    <row r="839" ht="15.0" customHeight="1"/>
-    <row r="840" ht="15.0" customHeight="1"/>
-    <row r="841" ht="15.0" customHeight="1"/>
-    <row r="842" ht="15.0" customHeight="1"/>
-    <row r="843" ht="15.0" customHeight="1"/>
-    <row r="844" ht="15.0" customHeight="1"/>
-    <row r="845" ht="15.0" customHeight="1"/>
-    <row r="846" ht="15.0" customHeight="1"/>
-    <row r="847" ht="15.0" customHeight="1"/>
-    <row r="848" ht="15.0" customHeight="1"/>
-    <row r="849" ht="15.0" customHeight="1"/>
-    <row r="850" ht="15.0" customHeight="1"/>
-    <row r="851" ht="15.0" customHeight="1"/>
-    <row r="852" ht="15.0" customHeight="1"/>
-    <row r="853" ht="15.0" customHeight="1"/>
-    <row r="854" ht="15.0" customHeight="1"/>
-    <row r="855" ht="15.0" customHeight="1"/>
-    <row r="856" ht="15.0" customHeight="1"/>
-    <row r="857" ht="15.0" customHeight="1"/>
-    <row r="858" ht="15.0" customHeight="1"/>
-    <row r="859" ht="15.0" customHeight="1"/>
-    <row r="860" ht="15.0" customHeight="1"/>
-    <row r="861" ht="15.0" customHeight="1"/>
-    <row r="862" ht="15.0" customHeight="1"/>
-    <row r="863" ht="15.0" customHeight="1"/>
-    <row r="864" ht="15.0" customHeight="1"/>
-    <row r="865" ht="15.0" customHeight="1"/>
-    <row r="866" ht="15.0" customHeight="1"/>
-    <row r="867" ht="15.0" customHeight="1"/>
-    <row r="868" ht="15.0" customHeight="1"/>
-    <row r="869" ht="15.0" customHeight="1"/>
-    <row r="870" ht="15.0" customHeight="1"/>
-    <row r="871" ht="15.0" customHeight="1"/>
-    <row r="872" ht="15.0" customHeight="1"/>
-    <row r="873" ht="15.0" customHeight="1"/>
-    <row r="874" ht="15.0" customHeight="1"/>
-    <row r="875" ht="15.0" customHeight="1"/>
-    <row r="876" ht="15.0" customHeight="1"/>
-    <row r="877" ht="15.0" customHeight="1"/>
-    <row r="878" ht="15.0" customHeight="1"/>
-    <row r="879" ht="15.0" customHeight="1"/>
-    <row r="880" ht="15.0" customHeight="1"/>
-    <row r="881" ht="15.0" customHeight="1"/>
-    <row r="882" ht="15.0" customHeight="1"/>
-    <row r="883" ht="15.0" customHeight="1"/>
-    <row r="884" ht="15.0" customHeight="1"/>
-    <row r="885" ht="15.0" customHeight="1"/>
-    <row r="886" ht="15.0" customHeight="1"/>
-    <row r="887" ht="15.0" customHeight="1"/>
-    <row r="888" ht="15.0" customHeight="1"/>
-    <row r="889" ht="15.0" customHeight="1"/>
-    <row r="890" ht="15.0" customHeight="1"/>
-    <row r="891" ht="15.0" customHeight="1"/>
-    <row r="892" ht="15.0" customHeight="1"/>
-    <row r="893" ht="15.0" customHeight="1"/>
-    <row r="894" ht="15.0" customHeight="1"/>
-    <row r="895" ht="15.0" customHeight="1"/>
-    <row r="896" ht="15.0" customHeight="1"/>
-    <row r="897" ht="15.0" customHeight="1"/>
-    <row r="898" ht="15.0" customHeight="1"/>
-    <row r="899" ht="15.0" customHeight="1"/>
-    <row r="900" ht="15.0" customHeight="1"/>
-    <row r="901" ht="15.0" customHeight="1"/>
-    <row r="902" ht="15.0" customHeight="1"/>
-    <row r="903" ht="15.0" customHeight="1"/>
-    <row r="904" ht="15.0" customHeight="1"/>
-    <row r="905" ht="15.0" customHeight="1"/>
-    <row r="906" ht="15.0" customHeight="1"/>
-    <row r="907" ht="15.0" customHeight="1"/>
-    <row r="908" ht="15.0" customHeight="1"/>
-    <row r="909" ht="15.0" customHeight="1"/>
-    <row r="910" ht="15.0" customHeight="1"/>
-    <row r="911" ht="15.0" customHeight="1"/>
-    <row r="912" ht="15.0" customHeight="1"/>
-    <row r="913" ht="15.0" customHeight="1"/>
-    <row r="914" ht="15.0" customHeight="1"/>
-    <row r="915" ht="15.0" customHeight="1"/>
-    <row r="916" ht="15.0" customHeight="1"/>
-    <row r="917" ht="15.0" customHeight="1"/>
-    <row r="918" ht="15.0" customHeight="1"/>
-    <row r="919" ht="15.0" customHeight="1"/>
-    <row r="920" ht="15.0" customHeight="1"/>
-    <row r="921" ht="15.0" customHeight="1"/>
-    <row r="922" ht="15.0" customHeight="1"/>
-    <row r="923" ht="15.0" customHeight="1"/>
-    <row r="924" ht="15.0" customHeight="1"/>
-    <row r="925" ht="15.0" customHeight="1"/>
-    <row r="926" ht="15.0" customHeight="1"/>
-    <row r="927" ht="15.0" customHeight="1"/>
-    <row r="928" ht="15.0" customHeight="1"/>
-    <row r="929" ht="15.0" customHeight="1"/>
-    <row r="930" ht="15.0" customHeight="1"/>
-    <row r="931" ht="15.0" customHeight="1"/>
-    <row r="932" ht="15.0" customHeight="1"/>
-    <row r="933" ht="15.0" customHeight="1"/>
-    <row r="934" ht="15.0" customHeight="1"/>
-    <row r="935" ht="15.0" customHeight="1"/>
-    <row r="936" ht="15.0" customHeight="1"/>
-    <row r="937" ht="15.0" customHeight="1"/>
-    <row r="938" ht="15.0" customHeight="1"/>
-    <row r="939" ht="15.0" customHeight="1"/>
-    <row r="940" ht="15.0" customHeight="1"/>
-    <row r="941" ht="15.0" customHeight="1"/>
-    <row r="942" ht="15.0" customHeight="1"/>
-    <row r="943" ht="15.0" customHeight="1"/>
-    <row r="944" ht="15.0" customHeight="1"/>
-    <row r="945" ht="15.0" customHeight="1"/>
-    <row r="946" ht="15.0" customHeight="1"/>
-    <row r="947" ht="15.0" customHeight="1"/>
-    <row r="948" ht="15.0" customHeight="1"/>
-    <row r="949" ht="15.0" customHeight="1"/>
-    <row r="950" ht="15.0" customHeight="1"/>
-    <row r="951" ht="15.0" customHeight="1"/>
-    <row r="952" ht="15.0" customHeight="1"/>
-    <row r="953" ht="15.0" customHeight="1"/>
-    <row r="954" ht="15.0" customHeight="1"/>
-    <row r="955" ht="15.0" customHeight="1"/>
-    <row r="956" ht="15.0" customHeight="1"/>
-    <row r="957" ht="15.0" customHeight="1"/>
-    <row r="958" ht="15.0" customHeight="1"/>
-    <row r="959" ht="15.0" customHeight="1"/>
-    <row r="960" ht="15.0" customHeight="1"/>
-    <row r="961" ht="15.0" customHeight="1"/>
-    <row r="962" ht="15.0" customHeight="1"/>
-    <row r="963" ht="15.0" customHeight="1"/>
-    <row r="964" ht="15.0" customHeight="1"/>
-    <row r="965" ht="15.0" customHeight="1"/>
-    <row r="966" ht="15.0" customHeight="1"/>
-    <row r="967" ht="15.0" customHeight="1"/>
-    <row r="968" ht="15.0" customHeight="1"/>
-    <row r="969" ht="15.0" customHeight="1"/>
-    <row r="970" ht="15.0" customHeight="1"/>
-    <row r="971" ht="15.0" customHeight="1"/>
-    <row r="972" ht="15.0" customHeight="1"/>
-    <row r="973" ht="15.0" customHeight="1"/>
-    <row r="974" ht="15.0" customHeight="1"/>
-    <row r="975" ht="15.0" customHeight="1"/>
-    <row r="976" ht="15.0" customHeight="1"/>
-    <row r="977" ht="15.0" customHeight="1"/>
-    <row r="978" ht="15.0" customHeight="1"/>
-    <row r="979" ht="15.0" customHeight="1"/>
-    <row r="980" ht="15.0" customHeight="1"/>
-    <row r="981" ht="15.0" customHeight="1"/>
-    <row r="982" ht="15.0" customHeight="1"/>
-    <row r="983" ht="15.0" customHeight="1"/>
-    <row r="984" ht="15.0" customHeight="1"/>
-    <row r="985" ht="15.0" customHeight="1"/>
-    <row r="986" ht="15.0" customHeight="1"/>
-    <row r="987" ht="15.0" customHeight="1"/>
-    <row r="988" ht="15.0" customHeight="1"/>
-    <row r="989" ht="15.0" customHeight="1"/>
-    <row r="990" ht="15.0" customHeight="1"/>
-    <row r="991" ht="15.0" customHeight="1"/>
-    <row r="992" ht="15.0" customHeight="1"/>
-    <row r="993" ht="15.0" customHeight="1"/>
-    <row r="994" ht="15.0" customHeight="1"/>
-    <row r="995" ht="15.0" customHeight="1"/>
-    <row r="996" ht="15.0" customHeight="1"/>
-    <row r="997" ht="15.0" customHeight="1"/>
-    <row r="998" ht="15.0" customHeight="1"/>
-    <row r="999" ht="15.0" customHeight="1"/>
-    <row r="1000" ht="15.0" customHeight="1"/>
-    <row r="1001" ht="15.0" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -28,6 +28,54 @@
     <t>English</t>
   </si>
   <si>
+    <t>EDITOR_QUIT_P_MSG</t>
+  </si>
+  <si>
+    <t>에디터 종료 팝업 메세지</t>
+  </si>
+  <si>
+    <t>에디터를 종료하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to quit the editor?</t>
+  </si>
+  <si>
+    <t>EDITOR_REMOVE_LP_MSG</t>
+  </si>
+  <si>
+    <t>에디터 레벨 제거 팝업 메세지</t>
+  </si>
+  <si>
+    <t>레벨을 제거하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove the level?</t>
+  </si>
+  <si>
+    <t>EDITOR_REMOVE_SP_MSG</t>
+  </si>
+  <si>
+    <t>에디터 스테이지 제거 팝업 메세지</t>
+  </si>
+  <si>
+    <t>스테이지를 제거하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove the stage?</t>
+  </si>
+  <si>
+    <t>EDITOR_REMOVE_CP_MSG</t>
+  </si>
+  <si>
+    <t>에디터 챕터 제거 팝업 메세지</t>
+  </si>
+  <si>
+    <t>챕터를 제거하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove the chapter?</t>
+  </si>
+  <si>
     <t>ALERT_P_TITLE</t>
   </si>
   <si>
@@ -76,54 +124,6 @@
     <t>Are you sure you want to quit the game?</t>
   </si>
   <si>
-    <t>EDITOR_QUIT_P_MSG</t>
-  </si>
-  <si>
-    <t>에디터 종료 팝업 메세지</t>
-  </si>
-  <si>
-    <t>에디터를 종료하시겠습니까?</t>
-  </si>
-  <si>
-    <t>Are you sure you want to quit the editor?</t>
-  </si>
-  <si>
-    <t>EDITOR_REMOVE_LP_MSG</t>
-  </si>
-  <si>
-    <t>에디터 레벨 제거 팝업 메세지</t>
-  </si>
-  <si>
-    <t>레벨을 제거하시겠습니까?</t>
-  </si>
-  <si>
-    <t>Are you sure you want to remove the level?</t>
-  </si>
-  <si>
-    <t>EDITOR_REMOVE_SP_MSG</t>
-  </si>
-  <si>
-    <t>에디터 스테이지 제거 팝업 메세지</t>
-  </si>
-  <si>
-    <t>스테이지를 제거하시겠습니까?</t>
-  </si>
-  <si>
-    <t>Are you sure you want to remove the stage?</t>
-  </si>
-  <si>
-    <t>EDITOR_REMOVE_CP_MSG</t>
-  </si>
-  <si>
-    <t>에디터 챕터 제거 팝업 메세지</t>
-  </si>
-  <si>
-    <t>챕터를 제거하시겠습니까?</t>
-  </si>
-  <si>
-    <t>Are you sure you want to remove the chapter?</t>
-  </si>
-  <si>
     <t>UPDATE_P_MSG</t>
   </si>
   <si>
@@ -286,7 +286,7 @@
     <t>설명 팝업 메세지</t>
   </si>
   <si>
-    <t>추적 승인 허용</t>
+    <t>추적 허용</t>
   </si>
   <si>
     <t>Allow tracking on the\nnext screen for</t>
@@ -369,7 +369,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -385,9 +385,22 @@
       </top>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -402,26 +415,36 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -430,8 +453,9 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -706,157 +730,162 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
+      <c r="Z2" s="4"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="8"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="8"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="8"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="8"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="7">
@@ -871,29 +900,30 @@
       <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="8"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="7">
@@ -908,29 +938,30 @@
       <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="8"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="7">
@@ -945,803 +976,825 @@
       <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="8"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="8"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="8"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="8"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="8"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="8"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="8"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="8"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="8"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="8"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
+      <c r="D19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="8"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="8"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="8"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="8"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="8"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
+      <c r="D24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="8"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
+      <c r="D25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="8"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="8"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="8"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="8"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="5"/>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="8"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="15"/>
     </row>
     <row r="31" ht="15.0" customHeight="1"/>
     <row r="32" ht="15.0" customHeight="1"/>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="145">
   <si>
     <t>ID</t>
   </si>
@@ -338,13 +338,121 @@
   </si>
   <si>
     <t>Next</t>
+  </si>
+  <si>
+    <t>COMMON_LEVEL_TEXT</t>
+  </si>
+  <si>
+    <t>공용 레벨 텍스트</t>
+  </si>
+  <si>
+    <t>레벨</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>COMMON_STAGE_TEXT</t>
+  </si>
+  <si>
+    <t>공용 스테이지 텍스트</t>
+  </si>
+  <si>
+    <t>스테이지</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>COMMON_CHAPTER_TEXT</t>
+  </si>
+  <si>
+    <t>공용 챕터 텍스트</t>
+  </si>
+  <si>
+    <t>챕터</t>
+  </si>
+  <si>
+    <t>Chapter</t>
+  </si>
+  <si>
+    <t>COMMON_LEVEL_PAGE_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 레벨 페이지 텍스트 형식</t>
+  </si>
+  <si>
+    <t>레벨 {0}/{1}</t>
+  </si>
+  <si>
+    <t>Level {0}/{1}</t>
+  </si>
+  <si>
+    <t>COMMON_STAGE_PAGE_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 스테이지 페이지 텍스트 형식</t>
+  </si>
+  <si>
+    <t>스테이지 {0}/{1}</t>
+  </si>
+  <si>
+    <t>Stage {0}/{1}</t>
+  </si>
+  <si>
+    <t>COMMON_CHAPTER_PAGE_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 챕터 페이지 텍스트 형식</t>
+  </si>
+  <si>
+    <t>챕터 {0}/{1}</t>
+  </si>
+  <si>
+    <t>Chapter {0}/{1}</t>
+  </si>
+  <si>
+    <t>COMMON_NUM_LEVELS_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 레벨 개수 텍스트 형식</t>
+  </si>
+  <si>
+    <t>레벨 개수 : {0}</t>
+  </si>
+  <si>
+    <t>Levels : {0}</t>
+  </si>
+  <si>
+    <t>COMMON_NUM_STAGES_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 스테이지 개수 텍스트 형식</t>
+  </si>
+  <si>
+    <t>스테이지 개수 : {0}</t>
+  </si>
+  <si>
+    <t>Stages : {0}</t>
+  </si>
+  <si>
+    <t>COMMON_NUM_CHAPTERS_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 챕터 개수 텍스트 형식</t>
+  </si>
+  <si>
+    <t>챕터 개수 : {0}</t>
+  </si>
+  <si>
+    <t>Chapters : {0}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -354,8 +462,9 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,6 +475,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE6B8AF"/>
         <bgColor rgb="FFE6B8AF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -427,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -438,17 +553,14 @@
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -456,6 +568,14 @@
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -669,7 +789,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="31.57"/>
+    <col customWidth="1" min="1" max="1" width="37.71"/>
     <col customWidth="1" min="2" max="2" width="14.43"/>
     <col customWidth="1" min="3" max="3" width="29.57"/>
     <col customWidth="1" min="4" max="4" width="59.14"/>
@@ -739,35 +859,35 @@
       <c r="B3" s="6">
         <v>0.0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
       <c r="Z3" s="8"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
@@ -777,35 +897,35 @@
       <c r="B4" s="6">
         <v>0.0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
       <c r="Z4" s="8"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
@@ -815,996 +935,1203 @@
       <c r="B5" s="6">
         <v>0.0</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
       <c r="Z5" s="8"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
       <c r="Z6" s="8"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
       <c r="Z7" s="8"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
       <c r="Z8" s="8"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
       <c r="Z9" s="8"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
       <c r="Z10" s="8"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
       <c r="Z11" s="8"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
       <c r="Z12" s="8"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
       <c r="Z13" s="8"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
       <c r="Z14" s="8"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
       <c r="Z15" s="8"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
       <c r="Z16" s="8"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
       <c r="Z17" s="8"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
       <c r="Z18" s="8"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
       <c r="Z19" s="8"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
       <c r="Z20" s="8"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
       <c r="Z21" s="8"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
       <c r="Z22" s="8"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
       <c r="Z23" s="8"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
       <c r="Z24" s="8"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
       <c r="Z25" s="8"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="B26" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
       <c r="Z26" s="8"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="B27" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
       <c r="Z27" s="8"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="B28" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
       <c r="Z28" s="8"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="6"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
       <c r="Z29" s="8"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="B30" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="15"/>
-    </row>
-    <row r="31" ht="15.0" customHeight="1"/>
-    <row r="32" ht="15.0" customHeight="1"/>
-    <row r="33" ht="15.0" customHeight="1"/>
-    <row r="34" ht="15.0" customHeight="1"/>
-    <row r="35" ht="15.0" customHeight="1"/>
-    <row r="36" ht="15.0" customHeight="1"/>
-    <row r="37" ht="15.0" customHeight="1"/>
-    <row r="38" ht="15.0" customHeight="1"/>
-    <row r="39" ht="15.0" customHeight="1"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="14"/>
+    </row>
+    <row r="31" ht="15.0" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" ht="15.0" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" ht="15.0" customHeight="1">
+      <c r="A33" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" ht="15.0" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" ht="15.0" customHeight="1">
+      <c r="A36" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" ht="15.0" customHeight="1">
+      <c r="A37" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="18"/>
+    </row>
+    <row r="38" ht="15.0" customHeight="1">
+      <c r="A38" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="18"/>
+    </row>
+    <row r="39" ht="15.0" customHeight="1">
+      <c r="A39" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="18"/>
+    </row>
     <row r="40" ht="15.0" customHeight="1"/>
     <row r="41" ht="15.0" customHeight="1"/>
     <row r="42" ht="15.0" customHeight="1"/>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="177">
   <si>
     <t>ID</t>
   </si>
@@ -134,66 +134,6 @@
   </si>
   <si>
     <t>A new version has been released.\nWould you like to update it?</t>
-  </si>
-  <si>
-    <t>PURCHASE_P_SUCCESS_MSG</t>
-  </si>
-  <si>
-    <t>결제 성공 팝업 메세지</t>
-  </si>
-  <si>
-    <t>해당 상품을 구입했습니다.</t>
-  </si>
-  <si>
-    <t>You have successfully purchased this product.</t>
-  </si>
-  <si>
-    <t>PURCHASE_P_FAIL_MSG</t>
-  </si>
-  <si>
-    <t>결제 실패 팝업 메세지</t>
-  </si>
-  <si>
-    <t>해당 상품 구입에 실패했습니다.</t>
-  </si>
-  <si>
-    <t>You have failed to purchase this product.</t>
-  </si>
-  <si>
-    <t>RESTORE_P_SUCCESS_MSG</t>
-  </si>
-  <si>
-    <t>복원 성공 팝업 메세지</t>
-  </si>
-  <si>
-    <t>상품을 복원했습니다.</t>
-  </si>
-  <si>
-    <t>The product has been restored.</t>
-  </si>
-  <si>
-    <t>RESTORE_P_FAIL_MSG</t>
-  </si>
-  <si>
-    <t>복원 실패 팝업 메세지</t>
-  </si>
-  <si>
-    <t>상품 복원에 실패했습니다.</t>
-  </si>
-  <si>
-    <t>Failed to restore the product.</t>
-  </si>
-  <si>
-    <t>START_SM_LOADING_TEXT</t>
-  </si>
-  <si>
-    <t>시작 씬 관리자 로딩 텍스트</t>
-  </si>
-  <si>
-    <t>로딩 중</t>
-  </si>
-  <si>
-    <t>Loading</t>
   </si>
   <si>
     <t>AGREE_P_SERVICES_TITLE</t>
@@ -338,6 +278,162 @@
   </si>
   <si>
     <t>Next</t>
+  </si>
+  <si>
+    <t>START_SM_LOADING_TEXT</t>
+  </si>
+  <si>
+    <t>시작 씬 관리자 로딩 텍스트</t>
+  </si>
+  <si>
+    <t>로딩 중</t>
+  </si>
+  <si>
+    <t>Loading</t>
+  </si>
+  <si>
+    <t>COMMON_LOGIN_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 로그인 성공 메세지</t>
+  </si>
+  <si>
+    <t>로그인했습니다.</t>
+  </si>
+  <si>
+    <t>You have successfully login</t>
+  </si>
+  <si>
+    <t>COMMON_LOGIN_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 로그인 실패 메세지</t>
+  </si>
+  <si>
+    <t>로그인에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>You have failed to login</t>
+  </si>
+  <si>
+    <t>COMMON_LOGOUT_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 로그아웃 성공 메세지</t>
+  </si>
+  <si>
+    <t>로그아웃했습니다.</t>
+  </si>
+  <si>
+    <t>You have successfully logout</t>
+  </si>
+  <si>
+    <t>COMMON_LOGOUT_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 로그아웃 실패 메세지</t>
+  </si>
+  <si>
+    <t>로그아웃에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>You have failed to logout</t>
+  </si>
+  <si>
+    <t>COMMON_SAVE_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 저장 성공 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황을 저장했습니다.</t>
+  </si>
+  <si>
+    <t>You have successfully saved progress.</t>
+  </si>
+  <si>
+    <t>COMMON_SAVE_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 저장 실패 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황 저장에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>You have failed to save progress.</t>
+  </si>
+  <si>
+    <t>COMMON_LOAD_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 로드 성공 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황을 로드했습니다.</t>
+  </si>
+  <si>
+    <t>You have successfully loaded progress.</t>
+  </si>
+  <si>
+    <t>COMMON_LOAD_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 로드 실패 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황 로드에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>You have failed to load progress.</t>
+  </si>
+  <si>
+    <t>COMMON_PURCHASE_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 결제 성공 메세지</t>
+  </si>
+  <si>
+    <t>해당 상품을 구입했습니다.</t>
+  </si>
+  <si>
+    <t>You have successfully purchased this product.</t>
+  </si>
+  <si>
+    <t>COMMON_PURCHASE_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 결제 실패 메세지</t>
+  </si>
+  <si>
+    <t>해당 상품 구입에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>You have failed to purchase this product.</t>
+  </si>
+  <si>
+    <t>COMMON_RESTORE_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 복원 성공 메세지</t>
+  </si>
+  <si>
+    <t>상품을 복원했습니다.</t>
+  </si>
+  <si>
+    <t>The product has been restored.</t>
+  </si>
+  <si>
+    <t>COMMON_RESTORE_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 복원 실패 메세지</t>
+  </si>
+  <si>
+    <t>상품 복원에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Failed to restore the product.</t>
   </si>
   <si>
     <t>COMMON_LEVEL_TEXT</t>
@@ -553,7 +649,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -566,15 +662,6 @@
     </xf>
     <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -589,6 +676,8 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -597,6 +686,15 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1284,96 +1382,96 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="7">
         <v>0.0</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="9"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B14" s="7">
         <v>0.0</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>55</v>
+      <c r="D14" s="7" t="s">
+        <v>24</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>56</v>
+      <c r="E14" s="7" t="s">
+        <v>24</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
       <c r="Z14" s="9"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7">
         <v>0.0</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -1399,19 +1497,19 @@
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B16" s="7">
         <v>0.0</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1437,19 +1535,19 @@
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B17" s="7">
         <v>0.0</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -1475,19 +1573,19 @@
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B18" s="7">
         <v>0.0</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1513,19 +1611,19 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B19" s="7">
         <v>0.0</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -1551,19 +1649,19 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B20" s="7">
         <v>0.0</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1589,19 +1687,19 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B21" s="7">
         <v>0.0</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>80</v>
+      <c r="D21" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -1627,19 +1725,19 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B22" s="7">
         <v>0.0</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -1665,19 +1763,19 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B23" s="7">
         <v>0.0</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -1703,19 +1801,19 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B24" s="7">
         <v>0.0</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -1741,19 +1839,19 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" s="7">
         <v>0.0</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -1787,7 +1885,7 @@
       <c r="C26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -1815,324 +1913,324 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="9"/>
     </row>
-    <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="10" t="s">
+    <row r="27">
+      <c r="A27" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="12">
         <v>0.0</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="9"/>
-    </row>
-    <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="10" t="s">
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="14"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="16">
         <v>0.0</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="9"/>
-    </row>
-    <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="10" t="s">
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="18"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="16">
         <v>0.0</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="9"/>
-    </row>
-    <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="13" t="s">
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="18"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="16">
         <v>0.0</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="15"/>
-    </row>
-    <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="16" t="s">
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="16">
         <v>0.0</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="19"/>
-    </row>
-    <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="20" t="s">
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="16">
         <v>0.0</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="23"/>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="20" t="s">
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="16">
         <v>0.0</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="22"/>
-      <c r="X33" s="22"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="23"/>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="20" t="s">
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="16">
         <v>0.0</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="23"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="19"/>
+      <c r="Z34" s="20"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <v>0.0</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="22" t="s">
         <v>128</v>
       </c>
       <c r="F35" s="22"/>
@@ -2155,22 +2253,22 @@
       <c r="W35" s="22"/>
       <c r="X35" s="22"/>
       <c r="Y35" s="22"/>
-      <c r="Z35" s="23"/>
+      <c r="Z35" s="20"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <v>0.0</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="22" t="s">
         <v>132</v>
       </c>
       <c r="F36" s="22"/>
@@ -2193,16 +2291,16 @@
       <c r="W36" s="22"/>
       <c r="X36" s="22"/>
       <c r="Y36" s="22"/>
-      <c r="Z36" s="23"/>
+      <c r="Z36" s="20"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="22">
         <v>0.0</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="25" t="s">
         <v>134</v>
       </c>
       <c r="D37" s="26" t="s">
@@ -2211,36 +2309,36 @@
       <c r="E37" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="25"/>
-      <c r="S37" s="25"/>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-      <c r="V37" s="25"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="25"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="23"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="26"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="26"/>
+      <c r="W37" s="26"/>
+      <c r="X37" s="26"/>
+      <c r="Y37" s="26"/>
+      <c r="Z37" s="20"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="22">
         <v>0.0</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="25" t="s">
         <v>138</v>
       </c>
       <c r="D38" s="26" t="s">
@@ -2249,289 +2347,369 @@
       <c r="E38" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="25"/>
-      <c r="N38" s="25"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="25"/>
-      <c r="S38" s="25"/>
-      <c r="T38" s="25"/>
-      <c r="U38" s="25"/>
-      <c r="V38" s="25"/>
-      <c r="W38" s="25"/>
-      <c r="X38" s="25"/>
-      <c r="Y38" s="25"/>
-      <c r="Z38" s="23"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="26"/>
+      <c r="X38" s="26"/>
+      <c r="Y38" s="26"/>
+      <c r="Z38" s="20"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="16">
         <v>0.0</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="30"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="19"/>
+      <c r="U39" s="19"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19"/>
+      <c r="Z39" s="20"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="2"/>
-      <c r="W40" s="2"/>
-      <c r="X40" s="2"/>
-      <c r="Y40" s="2"/>
-      <c r="Z40" s="2"/>
+      <c r="A40" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="20"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
-      <c r="Z41" s="2"/>
+      <c r="A41" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="20"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="2"/>
-      <c r="W42" s="2"/>
-      <c r="X42" s="2"/>
-      <c r="Y42" s="2"/>
-      <c r="Z42" s="2"/>
+      <c r="A42" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="19"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="19"/>
+      <c r="W42" s="19"/>
+      <c r="X42" s="19"/>
+      <c r="Y42" s="19"/>
+      <c r="Z42" s="20"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="2"/>
-      <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="2"/>
-      <c r="W43" s="2"/>
-      <c r="X43" s="2"/>
-      <c r="Y43" s="2"/>
-      <c r="Z43" s="2"/>
+      <c r="A43" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="19"/>
+      <c r="U43" s="19"/>
+      <c r="V43" s="19"/>
+      <c r="W43" s="19"/>
+      <c r="X43" s="19"/>
+      <c r="Y43" s="19"/>
+      <c r="Z43" s="20"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="2"/>
-      <c r="T44" s="2"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="2"/>
-      <c r="W44" s="2"/>
-      <c r="X44" s="2"/>
-      <c r="Y44" s="2"/>
-      <c r="Z44" s="2"/>
+      <c r="A44" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="19"/>
+      <c r="U44" s="19"/>
+      <c r="V44" s="19"/>
+      <c r="W44" s="19"/>
+      <c r="X44" s="19"/>
+      <c r="Y44" s="19"/>
+      <c r="Z44" s="20"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="2"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="2"/>
-      <c r="X45" s="2"/>
-      <c r="Y45" s="2"/>
-      <c r="Z45" s="2"/>
+      <c r="A45" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22"/>
+      <c r="R45" s="22"/>
+      <c r="S45" s="22"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="22"/>
+      <c r="V45" s="22"/>
+      <c r="W45" s="22"/>
+      <c r="X45" s="22"/>
+      <c r="Y45" s="22"/>
+      <c r="Z45" s="20"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
+      <c r="A46" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="22"/>
+      <c r="T46" s="22"/>
+      <c r="U46" s="22"/>
+      <c r="V46" s="22"/>
+      <c r="W46" s="22"/>
+      <c r="X46" s="22"/>
+      <c r="Y46" s="22"/>
+      <c r="Z46" s="20"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="2"/>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="2"/>
+      <c r="A47" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
+      <c r="T47" s="28"/>
+      <c r="U47" s="28"/>
+      <c r="V47" s="28"/>
+      <c r="W47" s="28"/>
+      <c r="X47" s="28"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="30"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="2"/>
@@ -7657,7 +7835,7 @@
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" ht="15.0" customHeight="1">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -7685,7 +7863,7 @@
       <c r="Y231" s="2"/>
       <c r="Z231" s="2"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" ht="15.0" customHeight="1">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -7713,7 +7891,7 @@
       <c r="Y232" s="2"/>
       <c r="Z232" s="2"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" ht="15.0" customHeight="1">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -7741,7 +7919,7 @@
       <c r="Y233" s="2"/>
       <c r="Z233" s="2"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" ht="15.0" customHeight="1">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -7769,7 +7947,7 @@
       <c r="Y234" s="2"/>
       <c r="Z234" s="2"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" ht="15.0" customHeight="1">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -7797,7 +7975,7 @@
       <c r="Y235" s="2"/>
       <c r="Z235" s="2"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" ht="15.0" customHeight="1">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -7825,7 +8003,7 @@
       <c r="Y236" s="2"/>
       <c r="Z236" s="2"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" ht="15.0" customHeight="1">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -7853,7 +8031,7 @@
       <c r="Y237" s="2"/>
       <c r="Z237" s="2"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" ht="15.0" customHeight="1">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -29301,6 +29479,230 @@
       <c r="Y1003" s="2"/>
       <c r="Z1003" s="2"/>
     </row>
+    <row r="1004" ht="15.75" customHeight="1">
+      <c r="A1004" s="2"/>
+      <c r="B1004" s="2"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
+      <c r="E1004" s="2"/>
+      <c r="F1004" s="2"/>
+      <c r="G1004" s="2"/>
+      <c r="H1004" s="2"/>
+      <c r="I1004" s="2"/>
+      <c r="J1004" s="2"/>
+      <c r="K1004" s="2"/>
+      <c r="L1004" s="2"/>
+      <c r="M1004" s="2"/>
+      <c r="N1004" s="2"/>
+      <c r="O1004" s="2"/>
+      <c r="P1004" s="2"/>
+      <c r="Q1004" s="2"/>
+      <c r="R1004" s="2"/>
+      <c r="S1004" s="2"/>
+      <c r="T1004" s="2"/>
+      <c r="U1004" s="2"/>
+      <c r="V1004" s="2"/>
+      <c r="W1004" s="2"/>
+      <c r="X1004" s="2"/>
+      <c r="Y1004" s="2"/>
+      <c r="Z1004" s="2"/>
+    </row>
+    <row r="1005" ht="15.75" customHeight="1">
+      <c r="A1005" s="2"/>
+      <c r="B1005" s="2"/>
+      <c r="C1005" s="2"/>
+      <c r="D1005" s="2"/>
+      <c r="E1005" s="2"/>
+      <c r="F1005" s="2"/>
+      <c r="G1005" s="2"/>
+      <c r="H1005" s="2"/>
+      <c r="I1005" s="2"/>
+      <c r="J1005" s="2"/>
+      <c r="K1005" s="2"/>
+      <c r="L1005" s="2"/>
+      <c r="M1005" s="2"/>
+      <c r="N1005" s="2"/>
+      <c r="O1005" s="2"/>
+      <c r="P1005" s="2"/>
+      <c r="Q1005" s="2"/>
+      <c r="R1005" s="2"/>
+      <c r="S1005" s="2"/>
+      <c r="T1005" s="2"/>
+      <c r="U1005" s="2"/>
+      <c r="V1005" s="2"/>
+      <c r="W1005" s="2"/>
+      <c r="X1005" s="2"/>
+      <c r="Y1005" s="2"/>
+      <c r="Z1005" s="2"/>
+    </row>
+    <row r="1006" ht="15.75" customHeight="1">
+      <c r="A1006" s="2"/>
+      <c r="B1006" s="2"/>
+      <c r="C1006" s="2"/>
+      <c r="D1006" s="2"/>
+      <c r="E1006" s="2"/>
+      <c r="F1006" s="2"/>
+      <c r="G1006" s="2"/>
+      <c r="H1006" s="2"/>
+      <c r="I1006" s="2"/>
+      <c r="J1006" s="2"/>
+      <c r="K1006" s="2"/>
+      <c r="L1006" s="2"/>
+      <c r="M1006" s="2"/>
+      <c r="N1006" s="2"/>
+      <c r="O1006" s="2"/>
+      <c r="P1006" s="2"/>
+      <c r="Q1006" s="2"/>
+      <c r="R1006" s="2"/>
+      <c r="S1006" s="2"/>
+      <c r="T1006" s="2"/>
+      <c r="U1006" s="2"/>
+      <c r="V1006" s="2"/>
+      <c r="W1006" s="2"/>
+      <c r="X1006" s="2"/>
+      <c r="Y1006" s="2"/>
+      <c r="Z1006" s="2"/>
+    </row>
+    <row r="1007" ht="15.75" customHeight="1">
+      <c r="A1007" s="2"/>
+      <c r="B1007" s="2"/>
+      <c r="C1007" s="2"/>
+      <c r="D1007" s="2"/>
+      <c r="E1007" s="2"/>
+      <c r="F1007" s="2"/>
+      <c r="G1007" s="2"/>
+      <c r="H1007" s="2"/>
+      <c r="I1007" s="2"/>
+      <c r="J1007" s="2"/>
+      <c r="K1007" s="2"/>
+      <c r="L1007" s="2"/>
+      <c r="M1007" s="2"/>
+      <c r="N1007" s="2"/>
+      <c r="O1007" s="2"/>
+      <c r="P1007" s="2"/>
+      <c r="Q1007" s="2"/>
+      <c r="R1007" s="2"/>
+      <c r="S1007" s="2"/>
+      <c r="T1007" s="2"/>
+      <c r="U1007" s="2"/>
+      <c r="V1007" s="2"/>
+      <c r="W1007" s="2"/>
+      <c r="X1007" s="2"/>
+      <c r="Y1007" s="2"/>
+      <c r="Z1007" s="2"/>
+    </row>
+    <row r="1008" ht="15.75" customHeight="1">
+      <c r="A1008" s="2"/>
+      <c r="B1008" s="2"/>
+      <c r="C1008" s="2"/>
+      <c r="D1008" s="2"/>
+      <c r="E1008" s="2"/>
+      <c r="F1008" s="2"/>
+      <c r="G1008" s="2"/>
+      <c r="H1008" s="2"/>
+      <c r="I1008" s="2"/>
+      <c r="J1008" s="2"/>
+      <c r="K1008" s="2"/>
+      <c r="L1008" s="2"/>
+      <c r="M1008" s="2"/>
+      <c r="N1008" s="2"/>
+      <c r="O1008" s="2"/>
+      <c r="P1008" s="2"/>
+      <c r="Q1008" s="2"/>
+      <c r="R1008" s="2"/>
+      <c r="S1008" s="2"/>
+      <c r="T1008" s="2"/>
+      <c r="U1008" s="2"/>
+      <c r="V1008" s="2"/>
+      <c r="W1008" s="2"/>
+      <c r="X1008" s="2"/>
+      <c r="Y1008" s="2"/>
+      <c r="Z1008" s="2"/>
+    </row>
+    <row r="1009" ht="15.75" customHeight="1">
+      <c r="A1009" s="2"/>
+      <c r="B1009" s="2"/>
+      <c r="C1009" s="2"/>
+      <c r="D1009" s="2"/>
+      <c r="E1009" s="2"/>
+      <c r="F1009" s="2"/>
+      <c r="G1009" s="2"/>
+      <c r="H1009" s="2"/>
+      <c r="I1009" s="2"/>
+      <c r="J1009" s="2"/>
+      <c r="K1009" s="2"/>
+      <c r="L1009" s="2"/>
+      <c r="M1009" s="2"/>
+      <c r="N1009" s="2"/>
+      <c r="O1009" s="2"/>
+      <c r="P1009" s="2"/>
+      <c r="Q1009" s="2"/>
+      <c r="R1009" s="2"/>
+      <c r="S1009" s="2"/>
+      <c r="T1009" s="2"/>
+      <c r="U1009" s="2"/>
+      <c r="V1009" s="2"/>
+      <c r="W1009" s="2"/>
+      <c r="X1009" s="2"/>
+      <c r="Y1009" s="2"/>
+      <c r="Z1009" s="2"/>
+    </row>
+    <row r="1010" ht="15.75" customHeight="1">
+      <c r="A1010" s="2"/>
+      <c r="B1010" s="2"/>
+      <c r="C1010" s="2"/>
+      <c r="D1010" s="2"/>
+      <c r="E1010" s="2"/>
+      <c r="F1010" s="2"/>
+      <c r="G1010" s="2"/>
+      <c r="H1010" s="2"/>
+      <c r="I1010" s="2"/>
+      <c r="J1010" s="2"/>
+      <c r="K1010" s="2"/>
+      <c r="L1010" s="2"/>
+      <c r="M1010" s="2"/>
+      <c r="N1010" s="2"/>
+      <c r="O1010" s="2"/>
+      <c r="P1010" s="2"/>
+      <c r="Q1010" s="2"/>
+      <c r="R1010" s="2"/>
+      <c r="S1010" s="2"/>
+      <c r="T1010" s="2"/>
+      <c r="U1010" s="2"/>
+      <c r="V1010" s="2"/>
+      <c r="W1010" s="2"/>
+      <c r="X1010" s="2"/>
+      <c r="Y1010" s="2"/>
+      <c r="Z1010" s="2"/>
+    </row>
+    <row r="1011" ht="15.75" customHeight="1">
+      <c r="A1011" s="2"/>
+      <c r="B1011" s="2"/>
+      <c r="C1011" s="2"/>
+      <c r="D1011" s="2"/>
+      <c r="E1011" s="2"/>
+      <c r="F1011" s="2"/>
+      <c r="G1011" s="2"/>
+      <c r="H1011" s="2"/>
+      <c r="I1011" s="2"/>
+      <c r="J1011" s="2"/>
+      <c r="K1011" s="2"/>
+      <c r="L1011" s="2"/>
+      <c r="M1011" s="2"/>
+      <c r="N1011" s="2"/>
+      <c r="O1011" s="2"/>
+      <c r="P1011" s="2"/>
+      <c r="Q1011" s="2"/>
+      <c r="R1011" s="2"/>
+      <c r="S1011" s="2"/>
+      <c r="T1011" s="2"/>
+      <c r="U1011" s="2"/>
+      <c r="V1011" s="2"/>
+      <c r="W1011" s="2"/>
+      <c r="X1011" s="2"/>
+      <c r="Y1011" s="2"/>
+      <c r="Z1011" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="191">
   <si>
     <t>ID</t>
   </si>
@@ -340,6 +340,30 @@
     <t>You have failed to logout</t>
   </si>
   <si>
+    <t>COMMON_LOAD_SUCCESS_MSG</t>
+  </si>
+  <si>
+    <t>공용 로드 성공 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황을 로드했습니다.</t>
+  </si>
+  <si>
+    <t>You have successfully loaded progress.</t>
+  </si>
+  <si>
+    <t>COMMON_LOAD_FAIL_MSG</t>
+  </si>
+  <si>
+    <t>공용 로드 실패 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황 로드에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>You have failed to load progress.</t>
+  </si>
+  <si>
     <t>COMMON_SAVE_SUCCESS_MSG</t>
   </si>
   <si>
@@ -362,30 +386,6 @@
   </si>
   <si>
     <t>You have failed to save progress.</t>
-  </si>
-  <si>
-    <t>COMMON_LOAD_SUCCESS_MSG</t>
-  </si>
-  <si>
-    <t>공용 로드 성공 메세지</t>
-  </si>
-  <si>
-    <t>진행 상황을 로드했습니다.</t>
-  </si>
-  <si>
-    <t>You have successfully loaded progress.</t>
-  </si>
-  <si>
-    <t>COMMON_LOAD_FAIL_MSG</t>
-  </si>
-  <si>
-    <t>공용 로드 실패 메세지</t>
-  </si>
-  <si>
-    <t>진행 상황 로드에 실패했습니다.</t>
-  </si>
-  <si>
-    <t>You have failed to load progress.</t>
   </si>
   <si>
     <t>COMMON_PURCHASE_SUCCESS_MSG</t>
@@ -434,6 +434,48 @@
   </si>
   <si>
     <t>Failed to restore the product.</t>
+  </si>
+  <si>
+    <t>COMMON_GET_TEXT</t>
+  </si>
+  <si>
+    <t>공용 획득 텍스트</t>
+  </si>
+  <si>
+    <t>획득</t>
+  </si>
+  <si>
+    <t>Get</t>
+  </si>
+  <si>
+    <t>COMMON_NEXT_TEXT</t>
+  </si>
+  <si>
+    <t>공용 다음 텍스트</t>
+  </si>
+  <si>
+    <t>COMMON_LEAVE_TEXT</t>
+  </si>
+  <si>
+    <t>공용 나가기 텍스트</t>
+  </si>
+  <si>
+    <t>나가기</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>COMMON_WATCH_ADS_TEXT</t>
+  </si>
+  <si>
+    <t>공용 광고 시청 텍스트</t>
+  </si>
+  <si>
+    <t>광고 시청</t>
+  </si>
+  <si>
+    <t>Watch Ads</t>
   </si>
   <si>
     <t>COMMON_LEVEL_TEXT</t>
@@ -644,7 +686,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -662,6 +704,9 @@
     </xf>
     <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -676,8 +721,6 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -696,6 +739,8 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1876,952 +1921,992 @@
       <c r="Z25" s="9"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="12">
         <v>0.0</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="9"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="13"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="15">
         <v>0.0</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="14"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="16"/>
+      <c r="Z27" s="17"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="19">
         <v>0.0</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="18"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="21"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="19">
         <v>0.0</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="18"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="21"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="19">
         <v>0.0</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="19"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="19"/>
-      <c r="Z30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="21"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="19">
         <v>0.0</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="21"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="19">
         <v>0.0</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="21"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="19">
         <v>0.0</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="21"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="19">
         <v>0.0</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="19"/>
-      <c r="Z34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="21"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="23">
         <v>0.0</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="20"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
+      <c r="X35" s="23"/>
+      <c r="Y35" s="23"/>
+      <c r="Z35" s="21"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="23">
         <v>0.0</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
-      <c r="W36" s="22"/>
-      <c r="X36" s="22"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="20"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="23"/>
+      <c r="X36" s="23"/>
+      <c r="Y36" s="23"/>
+      <c r="Z36" s="21"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="23">
         <v>0.0</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="26"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="26"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="20"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="21"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <v>0.0</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D38" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="20"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="27"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="21"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="19">
         <v>0.0</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="19"/>
-      <c r="Z39" s="20"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="29"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="19">
         <v>0.0</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="29"/>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="B41" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="19"/>
-      <c r="X40" s="19"/>
-      <c r="Y40" s="19"/>
-      <c r="Z40" s="20"/>
-    </row>
-    <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="15" t="s">
+      <c r="D41" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="16">
+      <c r="E41" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
+      <c r="V41" s="28"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="28"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="29"/>
+    </row>
+    <row r="42" ht="15.0" customHeight="1">
+      <c r="A42" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="19">
         <v>0.0</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" s="16" t="s">
+      <c r="C42" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="19"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="19"/>
-      <c r="Z41" s="20"/>
-    </row>
-    <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="15" t="s">
+      <c r="D42" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="16">
+      <c r="E42" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="29"/>
+    </row>
+    <row r="43" ht="15.0" customHeight="1">
+      <c r="A43" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="19">
         <v>0.0</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="16" t="s">
+      <c r="C43" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="19"/>
-      <c r="T42" s="19"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="19"/>
-      <c r="W42" s="19"/>
-      <c r="X42" s="19"/>
-      <c r="Y42" s="19"/>
-      <c r="Z42" s="20"/>
-    </row>
-    <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="15" t="s">
+      <c r="D43" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B43" s="16">
+      <c r="E43" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="20"/>
+      <c r="W43" s="20"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="21"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" s="19">
         <v>0.0</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" s="16" t="s">
+      <c r="C44" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="19"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="19"/>
-      <c r="W43" s="19"/>
-      <c r="X43" s="19"/>
-      <c r="Y43" s="19"/>
-      <c r="Z43" s="20"/>
-    </row>
-    <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="15" t="s">
+      <c r="D44" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="16">
+      <c r="E44" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="21"/>
+    </row>
+    <row r="45" ht="15.0" customHeight="1">
+      <c r="A45" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" s="19">
         <v>0.0</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E44" s="16" t="s">
+      <c r="C45" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
-      <c r="S44" s="19"/>
-      <c r="T44" s="19"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="19"/>
-      <c r="W44" s="19"/>
-      <c r="X44" s="19"/>
-      <c r="Y44" s="19"/>
-      <c r="Z44" s="20"/>
-    </row>
-    <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="21" t="s">
+      <c r="D45" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="B45" s="22">
+      <c r="E45" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+      <c r="V45" s="20"/>
+      <c r="W45" s="20"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="21"/>
+    </row>
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="A46" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="19">
         <v>0.0</v>
       </c>
-      <c r="C45" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E45" s="23" t="s">
+      <c r="C46" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="22"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="22"/>
-      <c r="S45" s="22"/>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="22"/>
-      <c r="W45" s="22"/>
-      <c r="X45" s="22"/>
-      <c r="Y45" s="22"/>
-      <c r="Z45" s="20"/>
-    </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="21" t="s">
+      <c r="D46" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="B46" s="22">
+      <c r="E46" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="21"/>
+    </row>
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="A47" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B47" s="19">
         <v>0.0</v>
       </c>
-      <c r="C46" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E46" s="23" t="s">
+      <c r="C47" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="22"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="20"/>
-    </row>
-    <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="27" t="s">
+      <c r="D47" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="B47" s="28">
+      <c r="E47" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
+      <c r="U47" s="20"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="21"/>
+    </row>
+    <row r="48" ht="15.0" customHeight="1">
+      <c r="A48" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B48" s="19">
         <v>0.0</v>
       </c>
-      <c r="C47" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="E47" s="29" t="s">
+      <c r="C48" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-      <c r="N47" s="28"/>
-      <c r="O47" s="28"/>
-      <c r="P47" s="28"/>
-      <c r="Q47" s="28"/>
-      <c r="R47" s="28"/>
-      <c r="S47" s="28"/>
-      <c r="T47" s="28"/>
-      <c r="U47" s="28"/>
-      <c r="V47" s="28"/>
-      <c r="W47" s="28"/>
-      <c r="X47" s="28"/>
-      <c r="Y47" s="28"/>
-      <c r="Z47" s="30"/>
-    </row>
-    <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="2"/>
-      <c r="X48" s="2"/>
-      <c r="Y48" s="2"/>
-      <c r="Z48" s="2"/>
+      <c r="D48" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="20"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="21"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
+      <c r="A49" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="B49" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="23"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="23"/>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="23"/>
+      <c r="S49" s="23"/>
+      <c r="T49" s="23"/>
+      <c r="U49" s="23"/>
+      <c r="V49" s="23"/>
+      <c r="W49" s="23"/>
+      <c r="X49" s="23"/>
+      <c r="Y49" s="23"/>
+      <c r="Z49" s="21"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
+      <c r="A50" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="23"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="23"/>
+      <c r="M50" s="23"/>
+      <c r="N50" s="23"/>
+      <c r="O50" s="23"/>
+      <c r="P50" s="23"/>
+      <c r="Q50" s="23"/>
+      <c r="R50" s="23"/>
+      <c r="S50" s="23"/>
+      <c r="T50" s="23"/>
+      <c r="U50" s="23"/>
+      <c r="V50" s="23"/>
+      <c r="W50" s="23"/>
+      <c r="X50" s="23"/>
+      <c r="Y50" s="23"/>
+      <c r="Z50" s="21"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
+      <c r="A51" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="31"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="31"/>
+      <c r="W51" s="31"/>
+      <c r="X51" s="31"/>
+      <c r="Y51" s="31"/>
+      <c r="Z51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="2"/>
@@ -2879,7 +2964,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" ht="15.0" customHeight="1">
+    <row r="54">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2907,7 +2992,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" ht="15.0" customHeight="1">
+    <row r="55">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -8059,7 +8144,7 @@
       <c r="Y238" s="2"/>
       <c r="Z238" s="2"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" ht="15.0" customHeight="1">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -8087,7 +8172,7 @@
       <c r="Y239" s="2"/>
       <c r="Z239" s="2"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" ht="15.0" customHeight="1">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -8115,7 +8200,7 @@
       <c r="Y240" s="2"/>
       <c r="Z240" s="2"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" ht="15.0" customHeight="1">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -8143,7 +8228,7 @@
       <c r="Y241" s="2"/>
       <c r="Z241" s="2"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" ht="15.0" customHeight="1">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -29703,6 +29788,118 @@
       <c r="Y1011" s="2"/>
       <c r="Z1011" s="2"/>
     </row>
+    <row r="1012" ht="15.75" customHeight="1">
+      <c r="A1012" s="2"/>
+      <c r="B1012" s="2"/>
+      <c r="C1012" s="2"/>
+      <c r="D1012" s="2"/>
+      <c r="E1012" s="2"/>
+      <c r="F1012" s="2"/>
+      <c r="G1012" s="2"/>
+      <c r="H1012" s="2"/>
+      <c r="I1012" s="2"/>
+      <c r="J1012" s="2"/>
+      <c r="K1012" s="2"/>
+      <c r="L1012" s="2"/>
+      <c r="M1012" s="2"/>
+      <c r="N1012" s="2"/>
+      <c r="O1012" s="2"/>
+      <c r="P1012" s="2"/>
+      <c r="Q1012" s="2"/>
+      <c r="R1012" s="2"/>
+      <c r="S1012" s="2"/>
+      <c r="T1012" s="2"/>
+      <c r="U1012" s="2"/>
+      <c r="V1012" s="2"/>
+      <c r="W1012" s="2"/>
+      <c r="X1012" s="2"/>
+      <c r="Y1012" s="2"/>
+      <c r="Z1012" s="2"/>
+    </row>
+    <row r="1013" ht="15.75" customHeight="1">
+      <c r="A1013" s="2"/>
+      <c r="B1013" s="2"/>
+      <c r="C1013" s="2"/>
+      <c r="D1013" s="2"/>
+      <c r="E1013" s="2"/>
+      <c r="F1013" s="2"/>
+      <c r="G1013" s="2"/>
+      <c r="H1013" s="2"/>
+      <c r="I1013" s="2"/>
+      <c r="J1013" s="2"/>
+      <c r="K1013" s="2"/>
+      <c r="L1013" s="2"/>
+      <c r="M1013" s="2"/>
+      <c r="N1013" s="2"/>
+      <c r="O1013" s="2"/>
+      <c r="P1013" s="2"/>
+      <c r="Q1013" s="2"/>
+      <c r="R1013" s="2"/>
+      <c r="S1013" s="2"/>
+      <c r="T1013" s="2"/>
+      <c r="U1013" s="2"/>
+      <c r="V1013" s="2"/>
+      <c r="W1013" s="2"/>
+      <c r="X1013" s="2"/>
+      <c r="Y1013" s="2"/>
+      <c r="Z1013" s="2"/>
+    </row>
+    <row r="1014" ht="15.75" customHeight="1">
+      <c r="A1014" s="2"/>
+      <c r="B1014" s="2"/>
+      <c r="C1014" s="2"/>
+      <c r="D1014" s="2"/>
+      <c r="E1014" s="2"/>
+      <c r="F1014" s="2"/>
+      <c r="G1014" s="2"/>
+      <c r="H1014" s="2"/>
+      <c r="I1014" s="2"/>
+      <c r="J1014" s="2"/>
+      <c r="K1014" s="2"/>
+      <c r="L1014" s="2"/>
+      <c r="M1014" s="2"/>
+      <c r="N1014" s="2"/>
+      <c r="O1014" s="2"/>
+      <c r="P1014" s="2"/>
+      <c r="Q1014" s="2"/>
+      <c r="R1014" s="2"/>
+      <c r="S1014" s="2"/>
+      <c r="T1014" s="2"/>
+      <c r="U1014" s="2"/>
+      <c r="V1014" s="2"/>
+      <c r="W1014" s="2"/>
+      <c r="X1014" s="2"/>
+      <c r="Y1014" s="2"/>
+      <c r="Z1014" s="2"/>
+    </row>
+    <row r="1015" ht="15.75" customHeight="1">
+      <c r="A1015" s="2"/>
+      <c r="B1015" s="2"/>
+      <c r="C1015" s="2"/>
+      <c r="D1015" s="2"/>
+      <c r="E1015" s="2"/>
+      <c r="F1015" s="2"/>
+      <c r="G1015" s="2"/>
+      <c r="H1015" s="2"/>
+      <c r="I1015" s="2"/>
+      <c r="J1015" s="2"/>
+      <c r="K1015" s="2"/>
+      <c r="L1015" s="2"/>
+      <c r="M1015" s="2"/>
+      <c r="N1015" s="2"/>
+      <c r="O1015" s="2"/>
+      <c r="P1015" s="2"/>
+      <c r="Q1015" s="2"/>
+      <c r="R1015" s="2"/>
+      <c r="S1015" s="2"/>
+      <c r="T1015" s="2"/>
+      <c r="U1015" s="2"/>
+      <c r="V1015" s="2"/>
+      <c r="W1015" s="2"/>
+      <c r="X1015" s="2"/>
+      <c r="Y1015" s="2"/>
+      <c r="Z1015" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -686,15 +686,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -702,34 +702,28 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -739,8 +733,9 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -748,7 +743,7 @@
     <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2263,155 +2258,155 @@
       <c r="Z34" s="21"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <v>0.0</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="23"/>
-      <c r="Y35" s="23"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="22"/>
       <c r="Z35" s="21"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="22">
         <v>0.0</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
-      <c r="S36" s="23"/>
-      <c r="T36" s="23"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
-      <c r="W36" s="23"/>
-      <c r="X36" s="23"/>
-      <c r="Y36" s="23"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="22"/>
+      <c r="X36" s="22"/>
+      <c r="Y36" s="22"/>
       <c r="Z36" s="21"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="22">
         <v>0.0</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E37" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
       <c r="Z37" s="21"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="22">
         <v>0.0</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="E38" s="27" t="s">
+      <c r="E38" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
       <c r="Z38" s="21"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
@@ -2430,27 +2425,27 @@
       <c r="E39" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="29"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="21"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="18" t="s">
@@ -2468,27 +2463,27 @@
       <c r="E40" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="29"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="21"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="18" t="s">
@@ -2506,27 +2501,27 @@
       <c r="E41" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="28"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="28"/>
-      <c r="X41" s="28"/>
-      <c r="Y41" s="28"/>
-      <c r="Z41" s="29"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="21"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="18" t="s">
@@ -2541,30 +2536,30 @@
       <c r="D42" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="28"/>
-      <c r="X42" s="28"/>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="29"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="20"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="21"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="18" t="s">
@@ -2795,118 +2790,118 @@
       <c r="Z48" s="21"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B49" s="22">
         <v>0.0</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="D49" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
-      <c r="S49" s="23"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="23"/>
-      <c r="V49" s="23"/>
-      <c r="W49" s="23"/>
-      <c r="X49" s="23"/>
-      <c r="Y49" s="23"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22"/>
+      <c r="R49" s="22"/>
+      <c r="S49" s="22"/>
+      <c r="T49" s="22"/>
+      <c r="U49" s="22"/>
+      <c r="V49" s="22"/>
+      <c r="W49" s="22"/>
+      <c r="X49" s="22"/>
+      <c r="Y49" s="22"/>
       <c r="Z49" s="21"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B50" s="22">
         <v>0.0</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D50" s="24" t="s">
+      <c r="D50" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
-      <c r="S50" s="23"/>
-      <c r="T50" s="23"/>
-      <c r="U50" s="23"/>
-      <c r="V50" s="23"/>
-      <c r="W50" s="23"/>
-      <c r="X50" s="23"/>
-      <c r="Y50" s="23"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22"/>
+      <c r="R50" s="22"/>
+      <c r="S50" s="22"/>
+      <c r="T50" s="22"/>
+      <c r="U50" s="22"/>
+      <c r="V50" s="22"/>
+      <c r="W50" s="22"/>
+      <c r="X50" s="22"/>
+      <c r="Y50" s="22"/>
       <c r="Z50" s="21"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="28">
         <v>0.0</v>
       </c>
-      <c r="C51" s="32" t="s">
+      <c r="C51" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="E51" s="32" t="s">
+      <c r="E51" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="31"/>
-      <c r="P51" s="31"/>
-      <c r="Q51" s="31"/>
-      <c r="R51" s="31"/>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
-      <c r="X51" s="31"/>
-      <c r="Y51" s="31"/>
-      <c r="Z51" s="33"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="2"/>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -196,16 +196,16 @@
     <t>and</t>
   </si>
   <si>
-    <t>AGREE_P_SERVICES_URL_TEXT</t>
+    <t>AGREE_P_SERVICES_BTN_TEXT</t>
   </si>
   <si>
-    <t>약관 동의 팝업 서비스 URL 텍스트</t>
+    <t>약관 동의 팝업 서비스 버튼 텍스트</t>
   </si>
   <si>
-    <t>AGREE_P_PRIVACY_URL_TEXT</t>
+    <t>AGREE_P_PRIVACY_BTN_TEXT</t>
   </si>
   <si>
-    <t>약관 동의 팝업 개인 정보 URL 텍스트</t>
+    <t>약관 동의 팝업 개인 정보 버튼 텍스트</t>
   </si>
   <si>
     <t>AGREE_P_OK_BTN_TEXT</t>
@@ -959,7 +959,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="37.71"/>
     <col customWidth="1" min="2" max="2" width="14.43"/>
-    <col customWidth="1" min="3" max="3" width="29.57"/>
+    <col customWidth="1" min="3" max="3" width="29.0"/>
     <col customWidth="1" min="4" max="4" width="59.14"/>
     <col customWidth="1" min="5" max="5" width="54.71"/>
     <col customWidth="1" min="6" max="6" width="14.43"/>
@@ -1574,13 +1574,13 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B17" s="7">
         <v>0.0</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D17" s="7" t="s">
@@ -1612,13 +1612,13 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B18" s="7">
         <v>0.0</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="7" t="s">

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="263">
   <si>
     <t>ID</t>
   </si>
@@ -466,6 +466,24 @@
     <t>Leave</t>
   </si>
   <si>
+    <t>COMMON_SYNC_TEXT</t>
+  </si>
+  <si>
+    <t>공용 동기화 텍스트</t>
+  </si>
+  <si>
+    <t>동기화</t>
+  </si>
+  <si>
+    <t>Sync</t>
+  </si>
+  <si>
+    <t>COMMON_NOTICE_TEXT</t>
+  </si>
+  <si>
+    <t>공용 알림 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_WATCH_ADS_TEXT</t>
   </si>
   <si>
@@ -585,12 +603,210 @@
   <si>
     <t>Chapters : {0}</t>
   </si>
+  <si>
+    <t>STORE_P_TITLE</t>
+  </si>
+  <si>
+    <t>상점 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>상점</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>STORE_P_RESTORE_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>상점 팝업 복원 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>결제 복원</t>
+  </si>
+  <si>
+    <t>Restore Payment</t>
+  </si>
+  <si>
+    <t>SETTINGS_P_TITLE</t>
+  </si>
+  <si>
+    <t>설정 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>설정</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>SETTINGS_P_BG_SND_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>설정 팝업 배경음 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>배경음</t>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
+  <si>
+    <t>SETTINGS_P_FX_SNDS_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>설정 팝업 효과음 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>효과음</t>
+  </si>
+  <si>
+    <t>SFX</t>
+  </si>
+  <si>
+    <t>SETTINGS_P_NOTI_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>설정 팝업 알림 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>SETTINGS_P_REVIEW_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>설정 팝업 평가 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>평가</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>SETTINGS_P_SUPPORTS_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>설정 팝업 지원 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>문의</t>
+  </si>
+  <si>
+    <t>Supports</t>
+  </si>
+  <si>
+    <t>SYNC_P_TITLE</t>
+  </si>
+  <si>
+    <t>동기화 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>SYNC_P_LOGIN_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>동기화 팝업 로그인 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>로그인</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>SYNC_P_LOGOUT_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>동기화 팝업 로그아웃 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>로그아웃</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>DAILY_MP_TITLE</t>
+  </si>
+  <si>
+    <t>일일 미션 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>일일 미션</t>
+  </si>
+  <si>
+    <t>Daily Mission</t>
+  </si>
+  <si>
+    <t>FREE_RP_TITLE</t>
+  </si>
+  <si>
+    <t>무료 보상 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>무료 보상</t>
+  </si>
+  <si>
+    <t>Free Reward</t>
+  </si>
+  <si>
+    <t>FREE_RP_ADS_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>무료 보상 팝업 광고 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>DAILY_RP_TITLE</t>
+  </si>
+  <si>
+    <t>일일 보상 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>일일 보상</t>
+  </si>
+  <si>
+    <t>Daily Reward</t>
+  </si>
+  <si>
+    <t>DAILY_RP_ADS_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>일일 보상 팝업 광고 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>DAILY_RP_ACQUIRE_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>일일 보상 팝업 획득 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>CHANGES_P_TITLE</t>
+  </si>
+  <si>
+    <t>잔돈 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>잔돈</t>
+  </si>
+  <si>
+    <t>Changes</t>
+  </si>
+  <si>
+    <t>CHANGES_P_OK_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>잔돈 팝업 확인 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>REWARD_AP_ACQUIRE_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>보상 획득 팝업 획득 버튼 텍스트</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -601,8 +817,15 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,6 +848,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF4CCCC"/>
         <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -686,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="51">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -736,14 +965,62 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2486,172 +2763,172 @@
       <c r="Z40" s="21"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="26">
         <v>0.0</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="21"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="27"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="27"/>
+      <c r="W41" s="27"/>
+      <c r="X41" s="27"/>
+      <c r="Y41" s="27"/>
+      <c r="Z41" s="27"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="29">
         <v>0.0</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E42" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
-      <c r="T42" s="20"/>
-      <c r="U42" s="20"/>
-      <c r="V42" s="20"/>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="21"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
+      <c r="X42" s="30"/>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="26">
         <v>0.0</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="27"/>
+      <c r="P43" s="27"/>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="27"/>
+      <c r="S43" s="27"/>
+      <c r="T43" s="27"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="27"/>
+      <c r="W43" s="27"/>
+      <c r="X43" s="27"/>
+      <c r="Y43" s="27"/>
+      <c r="Z43" s="27"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="B44" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
-      <c r="Y43" s="20"/>
-      <c r="Z43" s="21"/>
-    </row>
-    <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="18" t="s">
+      <c r="D44" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C44" s="19" t="s">
+      <c r="E44" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="D44" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
-      <c r="U44" s="20"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="20"/>
-      <c r="X44" s="20"/>
-      <c r="Y44" s="20"/>
-      <c r="Z44" s="21"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="27"/>
+      <c r="S44" s="27"/>
+      <c r="T44" s="27"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="27"/>
+      <c r="W44" s="27"/>
+      <c r="X44" s="27"/>
+      <c r="Y44" s="27"/>
+      <c r="Z44" s="27"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B45" s="19">
         <v>0.0</v>
       </c>
       <c r="C45" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>166</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
@@ -2677,19 +2954,19 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B46" s="19">
         <v>0.0</v>
       </c>
       <c r="C46" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E46" s="19" t="s">
         <v>168</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>170</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
@@ -2715,19 +2992,19 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B47" s="19">
         <v>0.0</v>
       </c>
       <c r="C47" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="19" t="s">
         <v>172</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>174</v>
       </c>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
@@ -2753,19 +3030,19 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B48" s="19">
         <v>0.0</v>
       </c>
       <c r="C48" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E48" s="19" t="s">
         <v>176</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>178</v>
       </c>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
@@ -2791,733 +3068,953 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B49" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="C49" s="19" t="s">
+      <c r="E49" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="22"/>
-      <c r="O49" s="22"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="22"/>
-      <c r="S49" s="22"/>
-      <c r="T49" s="22"/>
-      <c r="U49" s="22"/>
-      <c r="V49" s="22"/>
-      <c r="W49" s="22"/>
-      <c r="X49" s="22"/>
-      <c r="Y49" s="22"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="20"/>
+      <c r="S49" s="20"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="20"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
       <c r="Z49" s="21"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D50" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B50" s="22">
+      <c r="E50" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="20"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="20"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="21"/>
+    </row>
+    <row r="51" ht="15.0" customHeight="1">
+      <c r="A51" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="22">
         <v>0.0</v>
       </c>
-      <c r="C50" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="19" t="s">
+      <c r="C51" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="22"/>
-      <c r="L50" s="22"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="22"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="22"/>
-      <c r="S50" s="22"/>
-      <c r="T50" s="22"/>
-      <c r="U50" s="22"/>
-      <c r="V50" s="22"/>
-      <c r="W50" s="22"/>
-      <c r="X50" s="22"/>
-      <c r="Y50" s="22"/>
-      <c r="Z50" s="21"/>
-    </row>
-    <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="27" t="s">
+      <c r="D51" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="B51" s="28">
+      <c r="E51" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22"/>
+      <c r="R51" s="22"/>
+      <c r="S51" s="22"/>
+      <c r="T51" s="22"/>
+      <c r="U51" s="22"/>
+      <c r="V51" s="22"/>
+      <c r="W51" s="22"/>
+      <c r="X51" s="22"/>
+      <c r="Y51" s="22"/>
+      <c r="Z51" s="21"/>
+    </row>
+    <row r="52" ht="15.0" customHeight="1">
+      <c r="A52" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" s="22">
         <v>0.0</v>
       </c>
-      <c r="C51" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="E51" s="29" t="s">
+      <c r="C52" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="28"/>
-      <c r="S51" s="28"/>
-      <c r="T51" s="28"/>
-      <c r="U51" s="28"/>
-      <c r="V51" s="28"/>
-      <c r="W51" s="28"/>
-      <c r="X51" s="28"/>
-      <c r="Y51" s="28"/>
-      <c r="Z51" s="30"/>
-    </row>
-    <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="2"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="2"/>
-      <c r="X52" s="2"/>
-      <c r="Y52" s="2"/>
-      <c r="Z52" s="2"/>
+      <c r="D52" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22"/>
+      <c r="R52" s="22"/>
+      <c r="S52" s="22"/>
+      <c r="T52" s="22"/>
+      <c r="U52" s="22"/>
+      <c r="V52" s="22"/>
+      <c r="W52" s="22"/>
+      <c r="X52" s="22"/>
+      <c r="Y52" s="22"/>
+      <c r="Z52" s="21"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-      <c r="Z53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="2"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="2"/>
-      <c r="T54" s="2"/>
-      <c r="U54" s="2"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="2"/>
-      <c r="X54" s="2"/>
-      <c r="Y54" s="2"/>
-      <c r="Z54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-      <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
-      <c r="Y55" s="2"/>
-      <c r="Z55" s="2"/>
+      <c r="A53" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22"/>
+      <c r="R53" s="22"/>
+      <c r="S53" s="22"/>
+      <c r="T53" s="22"/>
+      <c r="U53" s="22"/>
+      <c r="V53" s="22"/>
+      <c r="W53" s="22"/>
+      <c r="X53" s="22"/>
+      <c r="Y53" s="22"/>
+      <c r="Z53" s="32"/>
+    </row>
+    <row r="54" ht="15.0" customHeight="1">
+      <c r="A54" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B54" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+      <c r="U54" s="35"/>
+      <c r="V54" s="35"/>
+      <c r="W54" s="35"/>
+      <c r="X54" s="35"/>
+      <c r="Y54" s="35"/>
+      <c r="Z54" s="36"/>
+    </row>
+    <row r="55" ht="15.0" customHeight="1">
+      <c r="A55" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39"/>
+      <c r="K55" s="39"/>
+      <c r="L55" s="39"/>
+      <c r="M55" s="39"/>
+      <c r="N55" s="39"/>
+      <c r="O55" s="39"/>
+      <c r="P55" s="39"/>
+      <c r="Q55" s="39"/>
+      <c r="R55" s="39"/>
+      <c r="S55" s="39"/>
+      <c r="T55" s="39"/>
+      <c r="U55" s="39"/>
+      <c r="V55" s="39"/>
+      <c r="W55" s="39"/>
+      <c r="X55" s="39"/>
+      <c r="Y55" s="39"/>
+      <c r="Z55" s="40"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="2"/>
-      <c r="T56" s="2"/>
-      <c r="U56" s="2"/>
-      <c r="V56" s="2"/>
-      <c r="W56" s="2"/>
-      <c r="X56" s="2"/>
-      <c r="Y56" s="2"/>
-      <c r="Z56" s="2"/>
+      <c r="A56" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
+      <c r="N56" s="39"/>
+      <c r="O56" s="39"/>
+      <c r="P56" s="39"/>
+      <c r="Q56" s="39"/>
+      <c r="R56" s="39"/>
+      <c r="S56" s="39"/>
+      <c r="T56" s="39"/>
+      <c r="U56" s="39"/>
+      <c r="V56" s="39"/>
+      <c r="W56" s="39"/>
+      <c r="X56" s="39"/>
+      <c r="Y56" s="39"/>
+      <c r="Z56" s="40"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
-      <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="2"/>
-      <c r="W57" s="2"/>
-      <c r="X57" s="2"/>
-      <c r="Y57" s="2"/>
-      <c r="Z57" s="2"/>
+      <c r="A57" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="44"/>
+      <c r="M57" s="44"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="44"/>
+      <c r="P57" s="44"/>
+      <c r="Q57" s="44"/>
+      <c r="R57" s="44"/>
+      <c r="S57" s="44"/>
+      <c r="T57" s="44"/>
+      <c r="U57" s="44"/>
+      <c r="V57" s="44"/>
+      <c r="W57" s="44"/>
+      <c r="X57" s="44"/>
+      <c r="Y57" s="44"/>
+      <c r="Z57" s="45"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-      <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
-      <c r="Z58" s="2"/>
+      <c r="A58" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="C58" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="44"/>
+      <c r="M58" s="44"/>
+      <c r="N58" s="44"/>
+      <c r="O58" s="44"/>
+      <c r="P58" s="44"/>
+      <c r="Q58" s="44"/>
+      <c r="R58" s="44"/>
+      <c r="S58" s="44"/>
+      <c r="T58" s="44"/>
+      <c r="U58" s="44"/>
+      <c r="V58" s="44"/>
+      <c r="W58" s="44"/>
+      <c r="X58" s="44"/>
+      <c r="Y58" s="44"/>
+      <c r="Z58" s="45"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2"/>
+      <c r="A59" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="B59" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="C59" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="44"/>
+      <c r="J59" s="44"/>
+      <c r="K59" s="44"/>
+      <c r="L59" s="44"/>
+      <c r="M59" s="44"/>
+      <c r="N59" s="44"/>
+      <c r="O59" s="44"/>
+      <c r="P59" s="44"/>
+      <c r="Q59" s="44"/>
+      <c r="R59" s="44"/>
+      <c r="S59" s="44"/>
+      <c r="T59" s="44"/>
+      <c r="U59" s="44"/>
+      <c r="V59" s="44"/>
+      <c r="W59" s="44"/>
+      <c r="X59" s="44"/>
+      <c r="Y59" s="44"/>
+      <c r="Z59" s="45"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="2"/>
-      <c r="V60" s="2"/>
-      <c r="W60" s="2"/>
-      <c r="X60" s="2"/>
-      <c r="Y60" s="2"/>
-      <c r="Z60" s="2"/>
+      <c r="A60" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="C60" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="D60" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="E60" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+      <c r="L60" s="44"/>
+      <c r="M60" s="44"/>
+      <c r="N60" s="44"/>
+      <c r="O60" s="44"/>
+      <c r="P60" s="44"/>
+      <c r="Q60" s="44"/>
+      <c r="R60" s="44"/>
+      <c r="S60" s="44"/>
+      <c r="T60" s="44"/>
+      <c r="U60" s="44"/>
+      <c r="V60" s="44"/>
+      <c r="W60" s="44"/>
+      <c r="X60" s="44"/>
+      <c r="Y60" s="44"/>
+      <c r="Z60" s="45"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="2"/>
-      <c r="T61" s="2"/>
-      <c r="U61" s="2"/>
-      <c r="V61" s="2"/>
-      <c r="W61" s="2"/>
-      <c r="X61" s="2"/>
-      <c r="Y61" s="2"/>
-      <c r="Z61" s="2"/>
-    </row>
-    <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
-      <c r="T62" s="2"/>
-      <c r="U62" s="2"/>
-      <c r="V62" s="2"/>
-      <c r="W62" s="2"/>
-      <c r="X62" s="2"/>
-      <c r="Y62" s="2"/>
-      <c r="Z62" s="2"/>
-    </row>
-    <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
-      <c r="Y63" s="2"/>
-      <c r="Z63" s="2"/>
-    </row>
-    <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
-      <c r="T64" s="2"/>
-      <c r="U64" s="2"/>
-      <c r="V64" s="2"/>
-      <c r="W64" s="2"/>
-      <c r="X64" s="2"/>
-      <c r="Y64" s="2"/>
-      <c r="Z64" s="2"/>
-    </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
-      <c r="T65" s="2"/>
-      <c r="U65" s="2"/>
-      <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
-      <c r="X65" s="2"/>
-      <c r="Y65" s="2"/>
-      <c r="Z65" s="2"/>
+      <c r="A61" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B61" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="44"/>
+      <c r="L61" s="44"/>
+      <c r="M61" s="44"/>
+      <c r="N61" s="44"/>
+      <c r="O61" s="44"/>
+      <c r="P61" s="44"/>
+      <c r="Q61" s="44"/>
+      <c r="R61" s="44"/>
+      <c r="S61" s="44"/>
+      <c r="T61" s="44"/>
+      <c r="U61" s="44"/>
+      <c r="V61" s="44"/>
+      <c r="W61" s="44"/>
+      <c r="X61" s="44"/>
+      <c r="Y61" s="44"/>
+      <c r="Z61" s="45"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E62" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
+      <c r="N62" s="39"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="39"/>
+      <c r="Q62" s="39"/>
+      <c r="R62" s="39"/>
+      <c r="S62" s="39"/>
+      <c r="T62" s="39"/>
+      <c r="U62" s="39"/>
+      <c r="V62" s="39"/>
+      <c r="W62" s="39"/>
+      <c r="X62" s="39"/>
+      <c r="Y62" s="39"/>
+      <c r="Z62" s="40"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C63" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="D63" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="E63" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="39"/>
+      <c r="K63" s="39"/>
+      <c r="L63" s="39"/>
+      <c r="M63" s="39"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="39"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="39"/>
+      <c r="T63" s="39"/>
+      <c r="U63" s="39"/>
+      <c r="V63" s="39"/>
+      <c r="W63" s="39"/>
+      <c r="X63" s="39"/>
+      <c r="Y63" s="39"/>
+      <c r="Z63" s="40"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="B64" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="39"/>
+      <c r="K64" s="39"/>
+      <c r="L64" s="39"/>
+      <c r="M64" s="39"/>
+      <c r="N64" s="39"/>
+      <c r="O64" s="39"/>
+      <c r="P64" s="39"/>
+      <c r="Q64" s="39"/>
+      <c r="R64" s="39"/>
+      <c r="S64" s="39"/>
+      <c r="T64" s="39"/>
+      <c r="U64" s="39"/>
+      <c r="V64" s="39"/>
+      <c r="W64" s="39"/>
+      <c r="X64" s="39"/>
+      <c r="Y64" s="39"/>
+      <c r="Z64" s="40"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="B65" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C65" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="E65" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
+      <c r="L65" s="39"/>
+      <c r="M65" s="39"/>
+      <c r="N65" s="39"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="39"/>
+      <c r="Q65" s="39"/>
+      <c r="R65" s="39"/>
+      <c r="S65" s="39"/>
+      <c r="T65" s="39"/>
+      <c r="U65" s="39"/>
+      <c r="V65" s="39"/>
+      <c r="W65" s="39"/>
+      <c r="X65" s="39"/>
+      <c r="Y65" s="39"/>
+      <c r="Z65" s="40"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
-      <c r="Y66" s="2"/>
-      <c r="Z66" s="2"/>
+      <c r="A66" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="B66" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C66" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D66" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
+      <c r="Q66" s="39"/>
+      <c r="R66" s="39"/>
+      <c r="S66" s="39"/>
+      <c r="T66" s="39"/>
+      <c r="U66" s="39"/>
+      <c r="V66" s="39"/>
+      <c r="W66" s="39"/>
+      <c r="X66" s="39"/>
+      <c r="Y66" s="39"/>
+      <c r="Z66" s="40"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
-      <c r="Y67" s="2"/>
-      <c r="Z67" s="2"/>
+      <c r="A67" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="B67" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C67" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="D67" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E67" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="39"/>
+      <c r="L67" s="39"/>
+      <c r="M67" s="39"/>
+      <c r="N67" s="39"/>
+      <c r="O67" s="39"/>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
+      <c r="R67" s="39"/>
+      <c r="S67" s="39"/>
+      <c r="T67" s="39"/>
+      <c r="U67" s="39"/>
+      <c r="V67" s="39"/>
+      <c r="W67" s="39"/>
+      <c r="X67" s="39"/>
+      <c r="Y67" s="39"/>
+      <c r="Z67" s="40"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
-      <c r="Y68" s="2"/>
-      <c r="Z68" s="2"/>
+      <c r="A68" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="B68" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C68" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="D68" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39"/>
+      <c r="K68" s="39"/>
+      <c r="L68" s="39"/>
+      <c r="M68" s="39"/>
+      <c r="N68" s="39"/>
+      <c r="O68" s="39"/>
+      <c r="P68" s="39"/>
+      <c r="Q68" s="39"/>
+      <c r="R68" s="39"/>
+      <c r="S68" s="39"/>
+      <c r="T68" s="39"/>
+      <c r="U68" s="39"/>
+      <c r="V68" s="39"/>
+      <c r="W68" s="39"/>
+      <c r="X68" s="39"/>
+      <c r="Y68" s="39"/>
+      <c r="Z68" s="40"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
-      <c r="T69" s="2"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
-      <c r="Y69" s="2"/>
-      <c r="Z69" s="2"/>
+      <c r="A69" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="B69" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C69" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="D69" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E69" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39"/>
+      <c r="K69" s="39"/>
+      <c r="L69" s="39"/>
+      <c r="M69" s="39"/>
+      <c r="N69" s="39"/>
+      <c r="O69" s="39"/>
+      <c r="P69" s="39"/>
+      <c r="Q69" s="39"/>
+      <c r="R69" s="39"/>
+      <c r="S69" s="39"/>
+      <c r="T69" s="39"/>
+      <c r="U69" s="39"/>
+      <c r="V69" s="39"/>
+      <c r="W69" s="39"/>
+      <c r="X69" s="39"/>
+      <c r="Y69" s="39"/>
+      <c r="Z69" s="40"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="2"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="2"/>
-      <c r="W70" s="2"/>
-      <c r="X70" s="2"/>
-      <c r="Y70" s="2"/>
-      <c r="Z70" s="2"/>
+      <c r="A70" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="B70" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C70" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="D70" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E70" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39"/>
+      <c r="K70" s="39"/>
+      <c r="L70" s="39"/>
+      <c r="M70" s="39"/>
+      <c r="N70" s="39"/>
+      <c r="O70" s="39"/>
+      <c r="P70" s="39"/>
+      <c r="Q70" s="39"/>
+      <c r="R70" s="39"/>
+      <c r="S70" s="39"/>
+      <c r="T70" s="39"/>
+      <c r="U70" s="39"/>
+      <c r="V70" s="39"/>
+      <c r="W70" s="39"/>
+      <c r="X70" s="39"/>
+      <c r="Y70" s="39"/>
+      <c r="Z70" s="40"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
-      <c r="Y71" s="2"/>
-      <c r="Z71" s="2"/>
+      <c r="A71" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C71" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="D71" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="E71" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="39"/>
+      <c r="K71" s="39"/>
+      <c r="L71" s="39"/>
+      <c r="M71" s="39"/>
+      <c r="N71" s="39"/>
+      <c r="O71" s="39"/>
+      <c r="P71" s="39"/>
+      <c r="Q71" s="39"/>
+      <c r="R71" s="39"/>
+      <c r="S71" s="39"/>
+      <c r="T71" s="39"/>
+      <c r="U71" s="39"/>
+      <c r="V71" s="39"/>
+      <c r="W71" s="39"/>
+      <c r="X71" s="39"/>
+      <c r="Y71" s="39"/>
+      <c r="Z71" s="40"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
-      <c r="Y72" s="2"/>
-      <c r="Z72" s="2"/>
+      <c r="A72" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="B72" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="C72" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="D72" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="39"/>
+      <c r="K72" s="39"/>
+      <c r="L72" s="39"/>
+      <c r="M72" s="39"/>
+      <c r="N72" s="39"/>
+      <c r="O72" s="39"/>
+      <c r="P72" s="39"/>
+      <c r="Q72" s="39"/>
+      <c r="R72" s="39"/>
+      <c r="S72" s="39"/>
+      <c r="T72" s="39"/>
+      <c r="U72" s="39"/>
+      <c r="V72" s="39"/>
+      <c r="W72" s="39"/>
+      <c r="X72" s="39"/>
+      <c r="Y72" s="39"/>
+      <c r="Z72" s="40"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
-      <c r="T73" s="2"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
-      <c r="Z73" s="2"/>
+      <c r="A73" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="B73" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="C73" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="D73" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="E73" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="49"/>
+      <c r="N73" s="49"/>
+      <c r="O73" s="49"/>
+      <c r="P73" s="49"/>
+      <c r="Q73" s="49"/>
+      <c r="R73" s="49"/>
+      <c r="S73" s="49"/>
+      <c r="T73" s="49"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="49"/>
+      <c r="W73" s="49"/>
+      <c r="X73" s="49"/>
+      <c r="Y73" s="49"/>
+      <c r="Z73" s="50"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="2"/>
@@ -8251,7 +8748,7 @@
       <c r="Y242" s="2"/>
       <c r="Z242" s="2"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" ht="15.0" customHeight="1">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -8279,7 +8776,7 @@
       <c r="Y243" s="2"/>
       <c r="Z243" s="2"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" ht="15.0" customHeight="1">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -8307,7 +8804,7 @@
       <c r="Y244" s="2"/>
       <c r="Z244" s="2"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" ht="15.0" customHeight="1">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -8335,7 +8832,7 @@
       <c r="Y245" s="2"/>
       <c r="Z245" s="2"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" ht="15.0" customHeight="1">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -8363,7 +8860,7 @@
       <c r="Y246" s="2"/>
       <c r="Z246" s="2"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" ht="15.0" customHeight="1">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -8391,7 +8888,7 @@
       <c r="Y247" s="2"/>
       <c r="Z247" s="2"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" ht="15.0" customHeight="1">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -8419,7 +8916,7 @@
       <c r="Y248" s="2"/>
       <c r="Z248" s="2"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" ht="15.0" customHeight="1">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -8447,7 +8944,7 @@
       <c r="Y249" s="2"/>
       <c r="Z249" s="2"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" ht="15.0" customHeight="1">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -8475,7 +8972,7 @@
       <c r="Y250" s="2"/>
       <c r="Z250" s="2"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" ht="15.0" customHeight="1">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -8503,7 +9000,7 @@
       <c r="Y251" s="2"/>
       <c r="Z251" s="2"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" ht="15.0" customHeight="1">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -8531,7 +9028,7 @@
       <c r="Y252" s="2"/>
       <c r="Z252" s="2"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" ht="15.0" customHeight="1">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -8559,7 +9056,7 @@
       <c r="Y253" s="2"/>
       <c r="Z253" s="2"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" ht="15.0" customHeight="1">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -8587,7 +9084,7 @@
       <c r="Y254" s="2"/>
       <c r="Z254" s="2"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" ht="15.0" customHeight="1">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -8615,7 +9112,7 @@
       <c r="Y255" s="2"/>
       <c r="Z255" s="2"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" ht="15.0" customHeight="1">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -8643,7 +9140,7 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" ht="15.0" customHeight="1">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -29895,6 +30392,426 @@
       <c r="Y1015" s="2"/>
       <c r="Z1015" s="2"/>
     </row>
+    <row r="1016" ht="15.75" customHeight="1">
+      <c r="A1016" s="2"/>
+      <c r="B1016" s="2"/>
+      <c r="C1016" s="2"/>
+      <c r="D1016" s="2"/>
+      <c r="E1016" s="2"/>
+      <c r="F1016" s="2"/>
+      <c r="G1016" s="2"/>
+      <c r="H1016" s="2"/>
+      <c r="I1016" s="2"/>
+      <c r="J1016" s="2"/>
+      <c r="K1016" s="2"/>
+      <c r="L1016" s="2"/>
+      <c r="M1016" s="2"/>
+      <c r="N1016" s="2"/>
+      <c r="O1016" s="2"/>
+      <c r="P1016" s="2"/>
+      <c r="Q1016" s="2"/>
+      <c r="R1016" s="2"/>
+      <c r="S1016" s="2"/>
+      <c r="T1016" s="2"/>
+      <c r="U1016" s="2"/>
+      <c r="V1016" s="2"/>
+      <c r="W1016" s="2"/>
+      <c r="X1016" s="2"/>
+      <c r="Y1016" s="2"/>
+      <c r="Z1016" s="2"/>
+    </row>
+    <row r="1017" ht="15.75" customHeight="1">
+      <c r="A1017" s="2"/>
+      <c r="B1017" s="2"/>
+      <c r="C1017" s="2"/>
+      <c r="D1017" s="2"/>
+      <c r="E1017" s="2"/>
+      <c r="F1017" s="2"/>
+      <c r="G1017" s="2"/>
+      <c r="H1017" s="2"/>
+      <c r="I1017" s="2"/>
+      <c r="J1017" s="2"/>
+      <c r="K1017" s="2"/>
+      <c r="L1017" s="2"/>
+      <c r="M1017" s="2"/>
+      <c r="N1017" s="2"/>
+      <c r="O1017" s="2"/>
+      <c r="P1017" s="2"/>
+      <c r="Q1017" s="2"/>
+      <c r="R1017" s="2"/>
+      <c r="S1017" s="2"/>
+      <c r="T1017" s="2"/>
+      <c r="U1017" s="2"/>
+      <c r="V1017" s="2"/>
+      <c r="W1017" s="2"/>
+      <c r="X1017" s="2"/>
+      <c r="Y1017" s="2"/>
+      <c r="Z1017" s="2"/>
+    </row>
+    <row r="1018" ht="15.75" customHeight="1">
+      <c r="A1018" s="2"/>
+      <c r="B1018" s="2"/>
+      <c r="C1018" s="2"/>
+      <c r="D1018" s="2"/>
+      <c r="E1018" s="2"/>
+      <c r="F1018" s="2"/>
+      <c r="G1018" s="2"/>
+      <c r="H1018" s="2"/>
+      <c r="I1018" s="2"/>
+      <c r="J1018" s="2"/>
+      <c r="K1018" s="2"/>
+      <c r="L1018" s="2"/>
+      <c r="M1018" s="2"/>
+      <c r="N1018" s="2"/>
+      <c r="O1018" s="2"/>
+      <c r="P1018" s="2"/>
+      <c r="Q1018" s="2"/>
+      <c r="R1018" s="2"/>
+      <c r="S1018" s="2"/>
+      <c r="T1018" s="2"/>
+      <c r="U1018" s="2"/>
+      <c r="V1018" s="2"/>
+      <c r="W1018" s="2"/>
+      <c r="X1018" s="2"/>
+      <c r="Y1018" s="2"/>
+      <c r="Z1018" s="2"/>
+    </row>
+    <row r="1019" ht="15.75" customHeight="1">
+      <c r="A1019" s="2"/>
+      <c r="B1019" s="2"/>
+      <c r="C1019" s="2"/>
+      <c r="D1019" s="2"/>
+      <c r="E1019" s="2"/>
+      <c r="F1019" s="2"/>
+      <c r="G1019" s="2"/>
+      <c r="H1019" s="2"/>
+      <c r="I1019" s="2"/>
+      <c r="J1019" s="2"/>
+      <c r="K1019" s="2"/>
+      <c r="L1019" s="2"/>
+      <c r="M1019" s="2"/>
+      <c r="N1019" s="2"/>
+      <c r="O1019" s="2"/>
+      <c r="P1019" s="2"/>
+      <c r="Q1019" s="2"/>
+      <c r="R1019" s="2"/>
+      <c r="S1019" s="2"/>
+      <c r="T1019" s="2"/>
+      <c r="U1019" s="2"/>
+      <c r="V1019" s="2"/>
+      <c r="W1019" s="2"/>
+      <c r="X1019" s="2"/>
+      <c r="Y1019" s="2"/>
+      <c r="Z1019" s="2"/>
+    </row>
+    <row r="1020" ht="15.75" customHeight="1">
+      <c r="A1020" s="2"/>
+      <c r="B1020" s="2"/>
+      <c r="C1020" s="2"/>
+      <c r="D1020" s="2"/>
+      <c r="E1020" s="2"/>
+      <c r="F1020" s="2"/>
+      <c r="G1020" s="2"/>
+      <c r="H1020" s="2"/>
+      <c r="I1020" s="2"/>
+      <c r="J1020" s="2"/>
+      <c r="K1020" s="2"/>
+      <c r="L1020" s="2"/>
+      <c r="M1020" s="2"/>
+      <c r="N1020" s="2"/>
+      <c r="O1020" s="2"/>
+      <c r="P1020" s="2"/>
+      <c r="Q1020" s="2"/>
+      <c r="R1020" s="2"/>
+      <c r="S1020" s="2"/>
+      <c r="T1020" s="2"/>
+      <c r="U1020" s="2"/>
+      <c r="V1020" s="2"/>
+      <c r="W1020" s="2"/>
+      <c r="X1020" s="2"/>
+      <c r="Y1020" s="2"/>
+      <c r="Z1020" s="2"/>
+    </row>
+    <row r="1021" ht="15.75" customHeight="1">
+      <c r="A1021" s="2"/>
+      <c r="B1021" s="2"/>
+      <c r="C1021" s="2"/>
+      <c r="D1021" s="2"/>
+      <c r="E1021" s="2"/>
+      <c r="F1021" s="2"/>
+      <c r="G1021" s="2"/>
+      <c r="H1021" s="2"/>
+      <c r="I1021" s="2"/>
+      <c r="J1021" s="2"/>
+      <c r="K1021" s="2"/>
+      <c r="L1021" s="2"/>
+      <c r="M1021" s="2"/>
+      <c r="N1021" s="2"/>
+      <c r="O1021" s="2"/>
+      <c r="P1021" s="2"/>
+      <c r="Q1021" s="2"/>
+      <c r="R1021" s="2"/>
+      <c r="S1021" s="2"/>
+      <c r="T1021" s="2"/>
+      <c r="U1021" s="2"/>
+      <c r="V1021" s="2"/>
+      <c r="W1021" s="2"/>
+      <c r="X1021" s="2"/>
+      <c r="Y1021" s="2"/>
+      <c r="Z1021" s="2"/>
+    </row>
+    <row r="1022" ht="15.75" customHeight="1">
+      <c r="A1022" s="2"/>
+      <c r="B1022" s="2"/>
+      <c r="C1022" s="2"/>
+      <c r="D1022" s="2"/>
+      <c r="E1022" s="2"/>
+      <c r="F1022" s="2"/>
+      <c r="G1022" s="2"/>
+      <c r="H1022" s="2"/>
+      <c r="I1022" s="2"/>
+      <c r="J1022" s="2"/>
+      <c r="K1022" s="2"/>
+      <c r="L1022" s="2"/>
+      <c r="M1022" s="2"/>
+      <c r="N1022" s="2"/>
+      <c r="O1022" s="2"/>
+      <c r="P1022" s="2"/>
+      <c r="Q1022" s="2"/>
+      <c r="R1022" s="2"/>
+      <c r="S1022" s="2"/>
+      <c r="T1022" s="2"/>
+      <c r="U1022" s="2"/>
+      <c r="V1022" s="2"/>
+      <c r="W1022" s="2"/>
+      <c r="X1022" s="2"/>
+      <c r="Y1022" s="2"/>
+      <c r="Z1022" s="2"/>
+    </row>
+    <row r="1023" ht="15.75" customHeight="1">
+      <c r="A1023" s="2"/>
+      <c r="B1023" s="2"/>
+      <c r="C1023" s="2"/>
+      <c r="D1023" s="2"/>
+      <c r="E1023" s="2"/>
+      <c r="F1023" s="2"/>
+      <c r="G1023" s="2"/>
+      <c r="H1023" s="2"/>
+      <c r="I1023" s="2"/>
+      <c r="J1023" s="2"/>
+      <c r="K1023" s="2"/>
+      <c r="L1023" s="2"/>
+      <c r="M1023" s="2"/>
+      <c r="N1023" s="2"/>
+      <c r="O1023" s="2"/>
+      <c r="P1023" s="2"/>
+      <c r="Q1023" s="2"/>
+      <c r="R1023" s="2"/>
+      <c r="S1023" s="2"/>
+      <c r="T1023" s="2"/>
+      <c r="U1023" s="2"/>
+      <c r="V1023" s="2"/>
+      <c r="W1023" s="2"/>
+      <c r="X1023" s="2"/>
+      <c r="Y1023" s="2"/>
+      <c r="Z1023" s="2"/>
+    </row>
+    <row r="1024" ht="15.75" customHeight="1">
+      <c r="A1024" s="2"/>
+      <c r="B1024" s="2"/>
+      <c r="C1024" s="2"/>
+      <c r="D1024" s="2"/>
+      <c r="E1024" s="2"/>
+      <c r="F1024" s="2"/>
+      <c r="G1024" s="2"/>
+      <c r="H1024" s="2"/>
+      <c r="I1024" s="2"/>
+      <c r="J1024" s="2"/>
+      <c r="K1024" s="2"/>
+      <c r="L1024" s="2"/>
+      <c r="M1024" s="2"/>
+      <c r="N1024" s="2"/>
+      <c r="O1024" s="2"/>
+      <c r="P1024" s="2"/>
+      <c r="Q1024" s="2"/>
+      <c r="R1024" s="2"/>
+      <c r="S1024" s="2"/>
+      <c r="T1024" s="2"/>
+      <c r="U1024" s="2"/>
+      <c r="V1024" s="2"/>
+      <c r="W1024" s="2"/>
+      <c r="X1024" s="2"/>
+      <c r="Y1024" s="2"/>
+      <c r="Z1024" s="2"/>
+    </row>
+    <row r="1025" ht="15.75" customHeight="1">
+      <c r="A1025" s="2"/>
+      <c r="B1025" s="2"/>
+      <c r="C1025" s="2"/>
+      <c r="D1025" s="2"/>
+      <c r="E1025" s="2"/>
+      <c r="F1025" s="2"/>
+      <c r="G1025" s="2"/>
+      <c r="H1025" s="2"/>
+      <c r="I1025" s="2"/>
+      <c r="J1025" s="2"/>
+      <c r="K1025" s="2"/>
+      <c r="L1025" s="2"/>
+      <c r="M1025" s="2"/>
+      <c r="N1025" s="2"/>
+      <c r="O1025" s="2"/>
+      <c r="P1025" s="2"/>
+      <c r="Q1025" s="2"/>
+      <c r="R1025" s="2"/>
+      <c r="S1025" s="2"/>
+      <c r="T1025" s="2"/>
+      <c r="U1025" s="2"/>
+      <c r="V1025" s="2"/>
+      <c r="W1025" s="2"/>
+      <c r="X1025" s="2"/>
+      <c r="Y1025" s="2"/>
+      <c r="Z1025" s="2"/>
+    </row>
+    <row r="1026" ht="15.75" customHeight="1">
+      <c r="A1026" s="2"/>
+      <c r="B1026" s="2"/>
+      <c r="C1026" s="2"/>
+      <c r="D1026" s="2"/>
+      <c r="E1026" s="2"/>
+      <c r="F1026" s="2"/>
+      <c r="G1026" s="2"/>
+      <c r="H1026" s="2"/>
+      <c r="I1026" s="2"/>
+      <c r="J1026" s="2"/>
+      <c r="K1026" s="2"/>
+      <c r="L1026" s="2"/>
+      <c r="M1026" s="2"/>
+      <c r="N1026" s="2"/>
+      <c r="O1026" s="2"/>
+      <c r="P1026" s="2"/>
+      <c r="Q1026" s="2"/>
+      <c r="R1026" s="2"/>
+      <c r="S1026" s="2"/>
+      <c r="T1026" s="2"/>
+      <c r="U1026" s="2"/>
+      <c r="V1026" s="2"/>
+      <c r="W1026" s="2"/>
+      <c r="X1026" s="2"/>
+      <c r="Y1026" s="2"/>
+      <c r="Z1026" s="2"/>
+    </row>
+    <row r="1027" ht="15.75" customHeight="1">
+      <c r="A1027" s="2"/>
+      <c r="B1027" s="2"/>
+      <c r="C1027" s="2"/>
+      <c r="D1027" s="2"/>
+      <c r="E1027" s="2"/>
+      <c r="F1027" s="2"/>
+      <c r="G1027" s="2"/>
+      <c r="H1027" s="2"/>
+      <c r="I1027" s="2"/>
+      <c r="J1027" s="2"/>
+      <c r="K1027" s="2"/>
+      <c r="L1027" s="2"/>
+      <c r="M1027" s="2"/>
+      <c r="N1027" s="2"/>
+      <c r="O1027" s="2"/>
+      <c r="P1027" s="2"/>
+      <c r="Q1027" s="2"/>
+      <c r="R1027" s="2"/>
+      <c r="S1027" s="2"/>
+      <c r="T1027" s="2"/>
+      <c r="U1027" s="2"/>
+      <c r="V1027" s="2"/>
+      <c r="W1027" s="2"/>
+      <c r="X1027" s="2"/>
+      <c r="Y1027" s="2"/>
+      <c r="Z1027" s="2"/>
+    </row>
+    <row r="1028" ht="15.75" customHeight="1">
+      <c r="A1028" s="2"/>
+      <c r="B1028" s="2"/>
+      <c r="C1028" s="2"/>
+      <c r="D1028" s="2"/>
+      <c r="E1028" s="2"/>
+      <c r="F1028" s="2"/>
+      <c r="G1028" s="2"/>
+      <c r="H1028" s="2"/>
+      <c r="I1028" s="2"/>
+      <c r="J1028" s="2"/>
+      <c r="K1028" s="2"/>
+      <c r="L1028" s="2"/>
+      <c r="M1028" s="2"/>
+      <c r="N1028" s="2"/>
+      <c r="O1028" s="2"/>
+      <c r="P1028" s="2"/>
+      <c r="Q1028" s="2"/>
+      <c r="R1028" s="2"/>
+      <c r="S1028" s="2"/>
+      <c r="T1028" s="2"/>
+      <c r="U1028" s="2"/>
+      <c r="V1028" s="2"/>
+      <c r="W1028" s="2"/>
+      <c r="X1028" s="2"/>
+      <c r="Y1028" s="2"/>
+      <c r="Z1028" s="2"/>
+    </row>
+    <row r="1029" ht="15.75" customHeight="1">
+      <c r="A1029" s="2"/>
+      <c r="B1029" s="2"/>
+      <c r="C1029" s="2"/>
+      <c r="D1029" s="2"/>
+      <c r="E1029" s="2"/>
+      <c r="F1029" s="2"/>
+      <c r="G1029" s="2"/>
+      <c r="H1029" s="2"/>
+      <c r="I1029" s="2"/>
+      <c r="J1029" s="2"/>
+      <c r="K1029" s="2"/>
+      <c r="L1029" s="2"/>
+      <c r="M1029" s="2"/>
+      <c r="N1029" s="2"/>
+      <c r="O1029" s="2"/>
+      <c r="P1029" s="2"/>
+      <c r="Q1029" s="2"/>
+      <c r="R1029" s="2"/>
+      <c r="S1029" s="2"/>
+      <c r="T1029" s="2"/>
+      <c r="U1029" s="2"/>
+      <c r="V1029" s="2"/>
+      <c r="W1029" s="2"/>
+      <c r="X1029" s="2"/>
+      <c r="Y1029" s="2"/>
+      <c r="Z1029" s="2"/>
+    </row>
+    <row r="1030" ht="15.75" customHeight="1">
+      <c r="A1030" s="2"/>
+      <c r="B1030" s="2"/>
+      <c r="C1030" s="2"/>
+      <c r="D1030" s="2"/>
+      <c r="E1030" s="2"/>
+      <c r="F1030" s="2"/>
+      <c r="G1030" s="2"/>
+      <c r="H1030" s="2"/>
+      <c r="I1030" s="2"/>
+      <c r="J1030" s="2"/>
+      <c r="K1030" s="2"/>
+      <c r="L1030" s="2"/>
+      <c r="M1030" s="2"/>
+      <c r="N1030" s="2"/>
+      <c r="O1030" s="2"/>
+      <c r="P1030" s="2"/>
+      <c r="Q1030" s="2"/>
+      <c r="R1030" s="2"/>
+      <c r="S1030" s="2"/>
+      <c r="T1030" s="2"/>
+      <c r="U1030" s="2"/>
+      <c r="V1030" s="2"/>
+      <c r="W1030" s="2"/>
+      <c r="X1030" s="2"/>
+      <c r="Y1030" s="2"/>
+      <c r="Z1030" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -778,22 +778,22 @@
     <t>일일 보상 팝업 획득 버튼 텍스트</t>
   </si>
   <si>
-    <t>CHANGES_P_TITLE</t>
+    <t>SALE_CP_TITLE</t>
   </si>
   <si>
-    <t>잔돈 팝업 타이틀</t>
+    <t>판매 코인 팝업 타이틀</t>
   </si>
   <si>
-    <t>잔돈</t>
+    <t>판매 코인</t>
   </si>
   <si>
-    <t>Changes</t>
+    <t>Sale Coins</t>
   </si>
   <si>
-    <t>CHANGES_P_OK_BTN_TEXT</t>
+    <t>SALE_CP_OK_BTN_TEXT</t>
   </si>
   <si>
-    <t>잔돈 팝업 확인 버튼 텍스트</t>
+    <t>판매 코인 팝업 확인 버튼 텍스트</t>
   </si>
   <si>
     <t>REWARD_AP_ACQUIRE_BTN_TEXT</t>
@@ -915,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -978,7 +978,6 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -3254,767 +3253,767 @@
       <c r="W53" s="22"/>
       <c r="X53" s="22"/>
       <c r="Y53" s="22"/>
-      <c r="Z53" s="32"/>
+      <c r="Z53" s="21"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="B54" s="34">
+      <c r="B54" s="33">
         <v>0.0</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="E54" s="34" t="s">
+      <c r="E54" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
-      <c r="L54" s="35"/>
-      <c r="M54" s="35"/>
-      <c r="N54" s="35"/>
-      <c r="O54" s="35"/>
-      <c r="P54" s="35"/>
-      <c r="Q54" s="35"/>
-      <c r="R54" s="35"/>
-      <c r="S54" s="35"/>
-      <c r="T54" s="35"/>
-      <c r="U54" s="35"/>
-      <c r="V54" s="35"/>
-      <c r="W54" s="35"/>
-      <c r="X54" s="35"/>
-      <c r="Y54" s="35"/>
-      <c r="Z54" s="36"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="34"/>
+      <c r="N54" s="34"/>
+      <c r="O54" s="34"/>
+      <c r="P54" s="34"/>
+      <c r="Q54" s="34"/>
+      <c r="R54" s="34"/>
+      <c r="S54" s="34"/>
+      <c r="T54" s="34"/>
+      <c r="U54" s="34"/>
+      <c r="V54" s="34"/>
+      <c r="W54" s="34"/>
+      <c r="X54" s="34"/>
+      <c r="Y54" s="34"/>
+      <c r="Z54" s="35"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="37" t="s">
+      <c r="A55" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="B55" s="38">
+      <c r="B55" s="37">
         <v>0.0</v>
       </c>
-      <c r="C55" s="38" t="s">
+      <c r="C55" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="D55" s="38" t="s">
+      <c r="D55" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="E55" s="38" t="s">
+      <c r="E55" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="39"/>
-      <c r="O55" s="39"/>
-      <c r="P55" s="39"/>
-      <c r="Q55" s="39"/>
-      <c r="R55" s="39"/>
-      <c r="S55" s="39"/>
-      <c r="T55" s="39"/>
-      <c r="U55" s="39"/>
-      <c r="V55" s="39"/>
-      <c r="W55" s="39"/>
-      <c r="X55" s="39"/>
-      <c r="Y55" s="39"/>
-      <c r="Z55" s="40"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="38"/>
+      <c r="S55" s="38"/>
+      <c r="T55" s="38"/>
+      <c r="U55" s="38"/>
+      <c r="V55" s="38"/>
+      <c r="W55" s="38"/>
+      <c r="X55" s="38"/>
+      <c r="Y55" s="38"/>
+      <c r="Z55" s="39"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="37" t="s">
+      <c r="A56" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="B56" s="38">
+      <c r="B56" s="37">
         <v>0.0</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="E56" s="38" t="s">
+      <c r="E56" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
-      <c r="N56" s="39"/>
-      <c r="O56" s="39"/>
-      <c r="P56" s="39"/>
-      <c r="Q56" s="39"/>
-      <c r="R56" s="39"/>
-      <c r="S56" s="39"/>
-      <c r="T56" s="39"/>
-      <c r="U56" s="39"/>
-      <c r="V56" s="39"/>
-      <c r="W56" s="39"/>
-      <c r="X56" s="39"/>
-      <c r="Y56" s="39"/>
-      <c r="Z56" s="40"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="38"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="38"/>
+      <c r="P56" s="38"/>
+      <c r="Q56" s="38"/>
+      <c r="R56" s="38"/>
+      <c r="S56" s="38"/>
+      <c r="T56" s="38"/>
+      <c r="U56" s="38"/>
+      <c r="V56" s="38"/>
+      <c r="W56" s="38"/>
+      <c r="X56" s="38"/>
+      <c r="Y56" s="38"/>
+      <c r="Z56" s="39"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="B57" s="42">
+      <c r="B57" s="41">
         <v>0.0</v>
       </c>
-      <c r="C57" s="43" t="s">
+      <c r="C57" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="D57" s="43" t="s">
+      <c r="D57" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="43" t="s">
+      <c r="E57" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="F57" s="44"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="44"/>
-      <c r="I57" s="44"/>
-      <c r="J57" s="44"/>
-      <c r="K57" s="44"/>
-      <c r="L57" s="44"/>
-      <c r="M57" s="44"/>
-      <c r="N57" s="44"/>
-      <c r="O57" s="44"/>
-      <c r="P57" s="44"/>
-      <c r="Q57" s="44"/>
-      <c r="R57" s="44"/>
-      <c r="S57" s="44"/>
-      <c r="T57" s="44"/>
-      <c r="U57" s="44"/>
-      <c r="V57" s="44"/>
-      <c r="W57" s="44"/>
-      <c r="X57" s="44"/>
-      <c r="Y57" s="44"/>
-      <c r="Z57" s="45"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+      <c r="L57" s="43"/>
+      <c r="M57" s="43"/>
+      <c r="N57" s="43"/>
+      <c r="O57" s="43"/>
+      <c r="P57" s="43"/>
+      <c r="Q57" s="43"/>
+      <c r="R57" s="43"/>
+      <c r="S57" s="43"/>
+      <c r="T57" s="43"/>
+      <c r="U57" s="43"/>
+      <c r="V57" s="43"/>
+      <c r="W57" s="43"/>
+      <c r="X57" s="43"/>
+      <c r="Y57" s="43"/>
+      <c r="Z57" s="44"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="B58" s="42">
+      <c r="B58" s="41">
         <v>0.0</v>
       </c>
-      <c r="C58" s="43" t="s">
+      <c r="C58" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="D58" s="43" t="s">
+      <c r="D58" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="E58" s="43" t="s">
+      <c r="E58" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="44"/>
-      <c r="L58" s="44"/>
-      <c r="M58" s="44"/>
-      <c r="N58" s="44"/>
-      <c r="O58" s="44"/>
-      <c r="P58" s="44"/>
-      <c r="Q58" s="44"/>
-      <c r="R58" s="44"/>
-      <c r="S58" s="44"/>
-      <c r="T58" s="44"/>
-      <c r="U58" s="44"/>
-      <c r="V58" s="44"/>
-      <c r="W58" s="44"/>
-      <c r="X58" s="44"/>
-      <c r="Y58" s="44"/>
-      <c r="Z58" s="45"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+      <c r="L58" s="43"/>
+      <c r="M58" s="43"/>
+      <c r="N58" s="43"/>
+      <c r="O58" s="43"/>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="43"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="43"/>
+      <c r="T58" s="43"/>
+      <c r="U58" s="43"/>
+      <c r="V58" s="43"/>
+      <c r="W58" s="43"/>
+      <c r="X58" s="43"/>
+      <c r="Y58" s="43"/>
+      <c r="Z58" s="44"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="B59" s="42">
+      <c r="B59" s="41">
         <v>0.0</v>
       </c>
-      <c r="C59" s="43" t="s">
+      <c r="C59" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="D59" s="43" t="s">
+      <c r="D59" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="43" t="s">
+      <c r="E59" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="44"/>
-      <c r="G59" s="44"/>
-      <c r="H59" s="44"/>
-      <c r="I59" s="44"/>
-      <c r="J59" s="44"/>
-      <c r="K59" s="44"/>
-      <c r="L59" s="44"/>
-      <c r="M59" s="44"/>
-      <c r="N59" s="44"/>
-      <c r="O59" s="44"/>
-      <c r="P59" s="44"/>
-      <c r="Q59" s="44"/>
-      <c r="R59" s="44"/>
-      <c r="S59" s="44"/>
-      <c r="T59" s="44"/>
-      <c r="U59" s="44"/>
-      <c r="V59" s="44"/>
-      <c r="W59" s="44"/>
-      <c r="X59" s="44"/>
-      <c r="Y59" s="44"/>
-      <c r="Z59" s="45"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+      <c r="L59" s="43"/>
+      <c r="M59" s="43"/>
+      <c r="N59" s="43"/>
+      <c r="O59" s="43"/>
+      <c r="P59" s="43"/>
+      <c r="Q59" s="43"/>
+      <c r="R59" s="43"/>
+      <c r="S59" s="43"/>
+      <c r="T59" s="43"/>
+      <c r="U59" s="43"/>
+      <c r="V59" s="43"/>
+      <c r="W59" s="43"/>
+      <c r="X59" s="43"/>
+      <c r="Y59" s="43"/>
+      <c r="Z59" s="44"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="B60" s="42">
+      <c r="B60" s="41">
         <v>0.0</v>
       </c>
-      <c r="C60" s="43" t="s">
+      <c r="C60" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="D60" s="43" t="s">
+      <c r="D60" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="E60" s="43" t="s">
+      <c r="E60" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="F60" s="44"/>
-      <c r="G60" s="44"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="44"/>
-      <c r="J60" s="44"/>
-      <c r="K60" s="44"/>
-      <c r="L60" s="44"/>
-      <c r="M60" s="44"/>
-      <c r="N60" s="44"/>
-      <c r="O60" s="44"/>
-      <c r="P60" s="44"/>
-      <c r="Q60" s="44"/>
-      <c r="R60" s="44"/>
-      <c r="S60" s="44"/>
-      <c r="T60" s="44"/>
-      <c r="U60" s="44"/>
-      <c r="V60" s="44"/>
-      <c r="W60" s="44"/>
-      <c r="X60" s="44"/>
-      <c r="Y60" s="44"/>
-      <c r="Z60" s="45"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="43"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="43"/>
+      <c r="L60" s="43"/>
+      <c r="M60" s="43"/>
+      <c r="N60" s="43"/>
+      <c r="O60" s="43"/>
+      <c r="P60" s="43"/>
+      <c r="Q60" s="43"/>
+      <c r="R60" s="43"/>
+      <c r="S60" s="43"/>
+      <c r="T60" s="43"/>
+      <c r="U60" s="43"/>
+      <c r="V60" s="43"/>
+      <c r="W60" s="43"/>
+      <c r="X60" s="43"/>
+      <c r="Y60" s="43"/>
+      <c r="Z60" s="44"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="41" t="s">
+      <c r="A61" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="B61" s="42">
+      <c r="B61" s="41">
         <v>0.0</v>
       </c>
-      <c r="C61" s="43" t="s">
+      <c r="C61" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="D61" s="43" t="s">
+      <c r="D61" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="E61" s="43" t="s">
+      <c r="E61" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="F61" s="44"/>
-      <c r="G61" s="44"/>
-      <c r="H61" s="44"/>
-      <c r="I61" s="44"/>
-      <c r="J61" s="44"/>
-      <c r="K61" s="44"/>
-      <c r="L61" s="44"/>
-      <c r="M61" s="44"/>
-      <c r="N61" s="44"/>
-      <c r="O61" s="44"/>
-      <c r="P61" s="44"/>
-      <c r="Q61" s="44"/>
-      <c r="R61" s="44"/>
-      <c r="S61" s="44"/>
-      <c r="T61" s="44"/>
-      <c r="U61" s="44"/>
-      <c r="V61" s="44"/>
-      <c r="W61" s="44"/>
-      <c r="X61" s="44"/>
-      <c r="Y61" s="44"/>
-      <c r="Z61" s="45"/>
+      <c r="F61" s="43"/>
+      <c r="G61" s="43"/>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+      <c r="L61" s="43"/>
+      <c r="M61" s="43"/>
+      <c r="N61" s="43"/>
+      <c r="O61" s="43"/>
+      <c r="P61" s="43"/>
+      <c r="Q61" s="43"/>
+      <c r="R61" s="43"/>
+      <c r="S61" s="43"/>
+      <c r="T61" s="43"/>
+      <c r="U61" s="43"/>
+      <c r="V61" s="43"/>
+      <c r="W61" s="43"/>
+      <c r="X61" s="43"/>
+      <c r="Y61" s="43"/>
+      <c r="Z61" s="44"/>
     </row>
     <row r="62">
-      <c r="A62" s="37" t="s">
+      <c r="A62" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="B62" s="38">
+      <c r="B62" s="37">
         <v>0.0</v>
       </c>
-      <c r="C62" s="38" t="s">
+      <c r="C62" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D62" s="38" t="s">
+      <c r="D62" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="E62" s="38" t="s">
+      <c r="E62" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
-      <c r="N62" s="39"/>
-      <c r="O62" s="39"/>
-      <c r="P62" s="39"/>
-      <c r="Q62" s="39"/>
-      <c r="R62" s="39"/>
-      <c r="S62" s="39"/>
-      <c r="T62" s="39"/>
-      <c r="U62" s="39"/>
-      <c r="V62" s="39"/>
-      <c r="W62" s="39"/>
-      <c r="X62" s="39"/>
-      <c r="Y62" s="39"/>
-      <c r="Z62" s="40"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="38"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="38"/>
+      <c r="P62" s="38"/>
+      <c r="Q62" s="38"/>
+      <c r="R62" s="38"/>
+      <c r="S62" s="38"/>
+      <c r="T62" s="38"/>
+      <c r="U62" s="38"/>
+      <c r="V62" s="38"/>
+      <c r="W62" s="38"/>
+      <c r="X62" s="38"/>
+      <c r="Y62" s="38"/>
+      <c r="Z62" s="39"/>
     </row>
     <row r="63">
-      <c r="A63" s="37" t="s">
+      <c r="A63" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="B63" s="38">
+      <c r="B63" s="37">
         <v>0.0</v>
       </c>
-      <c r="C63" s="38" t="s">
+      <c r="C63" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="D63" s="38" t="s">
+      <c r="D63" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="E63" s="38" t="s">
+      <c r="E63" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
-      <c r="J63" s="39"/>
-      <c r="K63" s="39"/>
-      <c r="L63" s="39"/>
-      <c r="M63" s="39"/>
-      <c r="N63" s="39"/>
-      <c r="O63" s="39"/>
-      <c r="P63" s="39"/>
-      <c r="Q63" s="39"/>
-      <c r="R63" s="39"/>
-      <c r="S63" s="39"/>
-      <c r="T63" s="39"/>
-      <c r="U63" s="39"/>
-      <c r="V63" s="39"/>
-      <c r="W63" s="39"/>
-      <c r="X63" s="39"/>
-      <c r="Y63" s="39"/>
-      <c r="Z63" s="40"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="38"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="38"/>
+      <c r="P63" s="38"/>
+      <c r="Q63" s="38"/>
+      <c r="R63" s="38"/>
+      <c r="S63" s="38"/>
+      <c r="T63" s="38"/>
+      <c r="U63" s="38"/>
+      <c r="V63" s="38"/>
+      <c r="W63" s="38"/>
+      <c r="X63" s="38"/>
+      <c r="Y63" s="38"/>
+      <c r="Z63" s="39"/>
     </row>
     <row r="64">
-      <c r="A64" s="37" t="s">
+      <c r="A64" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B64" s="38">
+      <c r="B64" s="37">
         <v>0.0</v>
       </c>
-      <c r="C64" s="38" t="s">
+      <c r="C64" s="37" t="s">
         <v>234</v>
       </c>
-      <c r="D64" s="38" t="s">
+      <c r="D64" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="E64" s="38" t="s">
+      <c r="E64" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
-      <c r="L64" s="39"/>
-      <c r="M64" s="39"/>
-      <c r="N64" s="39"/>
-      <c r="O64" s="39"/>
-      <c r="P64" s="39"/>
-      <c r="Q64" s="39"/>
-      <c r="R64" s="39"/>
-      <c r="S64" s="39"/>
-      <c r="T64" s="39"/>
-      <c r="U64" s="39"/>
-      <c r="V64" s="39"/>
-      <c r="W64" s="39"/>
-      <c r="X64" s="39"/>
-      <c r="Y64" s="39"/>
-      <c r="Z64" s="40"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
+      <c r="L64" s="38"/>
+      <c r="M64" s="38"/>
+      <c r="N64" s="38"/>
+      <c r="O64" s="38"/>
+      <c r="P64" s="38"/>
+      <c r="Q64" s="38"/>
+      <c r="R64" s="38"/>
+      <c r="S64" s="38"/>
+      <c r="T64" s="38"/>
+      <c r="U64" s="38"/>
+      <c r="V64" s="38"/>
+      <c r="W64" s="38"/>
+      <c r="X64" s="38"/>
+      <c r="Y64" s="38"/>
+      <c r="Z64" s="39"/>
     </row>
     <row r="65">
-      <c r="A65" s="37" t="s">
+      <c r="A65" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="B65" s="38">
+      <c r="B65" s="37">
         <v>0.0</v>
       </c>
-      <c r="C65" s="38" t="s">
+      <c r="C65" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D65" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E65" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
-      <c r="L65" s="39"/>
-      <c r="M65" s="39"/>
-      <c r="N65" s="39"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="39"/>
-      <c r="Q65" s="39"/>
-      <c r="R65" s="39"/>
-      <c r="S65" s="39"/>
-      <c r="T65" s="39"/>
-      <c r="U65" s="39"/>
-      <c r="V65" s="39"/>
-      <c r="W65" s="39"/>
-      <c r="X65" s="39"/>
-      <c r="Y65" s="39"/>
-      <c r="Z65" s="40"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
+      <c r="L65" s="38"/>
+      <c r="M65" s="38"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="38"/>
+      <c r="P65" s="38"/>
+      <c r="Q65" s="38"/>
+      <c r="R65" s="38"/>
+      <c r="S65" s="38"/>
+      <c r="T65" s="38"/>
+      <c r="U65" s="38"/>
+      <c r="V65" s="38"/>
+      <c r="W65" s="38"/>
+      <c r="X65" s="38"/>
+      <c r="Y65" s="38"/>
+      <c r="Z65" s="39"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="37" t="s">
+      <c r="A66" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="B66" s="38">
+      <c r="B66" s="37">
         <v>0.0</v>
       </c>
-      <c r="C66" s="38" t="s">
+      <c r="C66" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="D66" s="38" t="s">
+      <c r="D66" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="E66" s="38" t="s">
+      <c r="E66" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="39"/>
-      <c r="M66" s="39"/>
-      <c r="N66" s="39"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="39"/>
-      <c r="Q66" s="39"/>
-      <c r="R66" s="39"/>
-      <c r="S66" s="39"/>
-      <c r="T66" s="39"/>
-      <c r="U66" s="39"/>
-      <c r="V66" s="39"/>
-      <c r="W66" s="39"/>
-      <c r="X66" s="39"/>
-      <c r="Y66" s="39"/>
-      <c r="Z66" s="40"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="38"/>
+      <c r="L66" s="38"/>
+      <c r="M66" s="38"/>
+      <c r="N66" s="38"/>
+      <c r="O66" s="38"/>
+      <c r="P66" s="38"/>
+      <c r="Q66" s="38"/>
+      <c r="R66" s="38"/>
+      <c r="S66" s="38"/>
+      <c r="T66" s="38"/>
+      <c r="U66" s="38"/>
+      <c r="V66" s="38"/>
+      <c r="W66" s="38"/>
+      <c r="X66" s="38"/>
+      <c r="Y66" s="38"/>
+      <c r="Z66" s="39"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="37" t="s">
+      <c r="A67" s="36" t="s">
         <v>245</v>
       </c>
-      <c r="B67" s="38">
+      <c r="B67" s="37">
         <v>0.0</v>
       </c>
-      <c r="C67" s="38" t="s">
+      <c r="C67" s="37" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="38" t="s">
+      <c r="D67" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="E67" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
-      <c r="L67" s="39"/>
-      <c r="M67" s="39"/>
-      <c r="N67" s="39"/>
-      <c r="O67" s="39"/>
-      <c r="P67" s="39"/>
-      <c r="Q67" s="39"/>
-      <c r="R67" s="39"/>
-      <c r="S67" s="39"/>
-      <c r="T67" s="39"/>
-      <c r="U67" s="39"/>
-      <c r="V67" s="39"/>
-      <c r="W67" s="39"/>
-      <c r="X67" s="39"/>
-      <c r="Y67" s="39"/>
-      <c r="Z67" s="40"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="38"/>
+      <c r="L67" s="38"/>
+      <c r="M67" s="38"/>
+      <c r="N67" s="38"/>
+      <c r="O67" s="38"/>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="38"/>
+      <c r="R67" s="38"/>
+      <c r="S67" s="38"/>
+      <c r="T67" s="38"/>
+      <c r="U67" s="38"/>
+      <c r="V67" s="38"/>
+      <c r="W67" s="38"/>
+      <c r="X67" s="38"/>
+      <c r="Y67" s="38"/>
+      <c r="Z67" s="39"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="37" t="s">
+      <c r="A68" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="B68" s="38">
+      <c r="B68" s="37">
         <v>0.0</v>
       </c>
-      <c r="C68" s="38" t="s">
+      <c r="C68" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="D68" s="38" t="s">
+      <c r="D68" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="E68" s="38" t="s">
+      <c r="E68" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
-      <c r="L68" s="39"/>
-      <c r="M68" s="39"/>
-      <c r="N68" s="39"/>
-      <c r="O68" s="39"/>
-      <c r="P68" s="39"/>
-      <c r="Q68" s="39"/>
-      <c r="R68" s="39"/>
-      <c r="S68" s="39"/>
-      <c r="T68" s="39"/>
-      <c r="U68" s="39"/>
-      <c r="V68" s="39"/>
-      <c r="W68" s="39"/>
-      <c r="X68" s="39"/>
-      <c r="Y68" s="39"/>
-      <c r="Z68" s="40"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="38"/>
+      <c r="L68" s="38"/>
+      <c r="M68" s="38"/>
+      <c r="N68" s="38"/>
+      <c r="O68" s="38"/>
+      <c r="P68" s="38"/>
+      <c r="Q68" s="38"/>
+      <c r="R68" s="38"/>
+      <c r="S68" s="38"/>
+      <c r="T68" s="38"/>
+      <c r="U68" s="38"/>
+      <c r="V68" s="38"/>
+      <c r="W68" s="38"/>
+      <c r="X68" s="38"/>
+      <c r="Y68" s="38"/>
+      <c r="Z68" s="39"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="46" t="s">
+      <c r="A69" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="38">
+      <c r="B69" s="37">
         <v>0.0</v>
       </c>
-      <c r="C69" s="38" t="s">
+      <c r="C69" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="38" t="s">
+      <c r="D69" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E69" s="38" t="s">
+      <c r="E69" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="39"/>
-      <c r="J69" s="39"/>
-      <c r="K69" s="39"/>
-      <c r="L69" s="39"/>
-      <c r="M69" s="39"/>
-      <c r="N69" s="39"/>
-      <c r="O69" s="39"/>
-      <c r="P69" s="39"/>
-      <c r="Q69" s="39"/>
-      <c r="R69" s="39"/>
-      <c r="S69" s="39"/>
-      <c r="T69" s="39"/>
-      <c r="U69" s="39"/>
-      <c r="V69" s="39"/>
-      <c r="W69" s="39"/>
-      <c r="X69" s="39"/>
-      <c r="Y69" s="39"/>
-      <c r="Z69" s="40"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
+      <c r="L69" s="38"/>
+      <c r="M69" s="38"/>
+      <c r="N69" s="38"/>
+      <c r="O69" s="38"/>
+      <c r="P69" s="38"/>
+      <c r="Q69" s="38"/>
+      <c r="R69" s="38"/>
+      <c r="S69" s="38"/>
+      <c r="T69" s="38"/>
+      <c r="U69" s="38"/>
+      <c r="V69" s="38"/>
+      <c r="W69" s="38"/>
+      <c r="X69" s="38"/>
+      <c r="Y69" s="38"/>
+      <c r="Z69" s="39"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="37" t="s">
+      <c r="A70" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="B70" s="38">
+      <c r="B70" s="37">
         <v>0.0</v>
       </c>
-      <c r="C70" s="38" t="s">
+      <c r="C70" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="D70" s="38" t="s">
+      <c r="D70" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="E70" s="38" t="s">
+      <c r="E70" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
-      <c r="L70" s="39"/>
-      <c r="M70" s="39"/>
-      <c r="N70" s="39"/>
-      <c r="O70" s="39"/>
-      <c r="P70" s="39"/>
-      <c r="Q70" s="39"/>
-      <c r="R70" s="39"/>
-      <c r="S70" s="39"/>
-      <c r="T70" s="39"/>
-      <c r="U70" s="39"/>
-      <c r="V70" s="39"/>
-      <c r="W70" s="39"/>
-      <c r="X70" s="39"/>
-      <c r="Y70" s="39"/>
-      <c r="Z70" s="40"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="38"/>
+      <c r="L70" s="38"/>
+      <c r="M70" s="38"/>
+      <c r="N70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="P70" s="38"/>
+      <c r="Q70" s="38"/>
+      <c r="R70" s="38"/>
+      <c r="S70" s="38"/>
+      <c r="T70" s="38"/>
+      <c r="U70" s="38"/>
+      <c r="V70" s="38"/>
+      <c r="W70" s="38"/>
+      <c r="X70" s="38"/>
+      <c r="Y70" s="38"/>
+      <c r="Z70" s="39"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="37" t="s">
+      <c r="A71" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="B71" s="38">
+      <c r="B71" s="37">
         <v>0.0</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="C71" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="D71" s="38" t="s">
+      <c r="D71" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
-      <c r="H71" s="39"/>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39"/>
-      <c r="K71" s="39"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-      <c r="N71" s="39"/>
-      <c r="O71" s="39"/>
-      <c r="P71" s="39"/>
-      <c r="Q71" s="39"/>
-      <c r="R71" s="39"/>
-      <c r="S71" s="39"/>
-      <c r="T71" s="39"/>
-      <c r="U71" s="39"/>
-      <c r="V71" s="39"/>
-      <c r="W71" s="39"/>
-      <c r="X71" s="39"/>
-      <c r="Y71" s="39"/>
-      <c r="Z71" s="40"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
+      <c r="L71" s="38"/>
+      <c r="M71" s="38"/>
+      <c r="N71" s="38"/>
+      <c r="O71" s="38"/>
+      <c r="P71" s="38"/>
+      <c r="Q71" s="38"/>
+      <c r="R71" s="38"/>
+      <c r="S71" s="38"/>
+      <c r="T71" s="38"/>
+      <c r="U71" s="38"/>
+      <c r="V71" s="38"/>
+      <c r="W71" s="38"/>
+      <c r="X71" s="38"/>
+      <c r="Y71" s="38"/>
+      <c r="Z71" s="39"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="37" t="s">
+      <c r="A72" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="B72" s="38">
+      <c r="B72" s="37">
         <v>0.0</v>
       </c>
-      <c r="C72" s="38" t="s">
+      <c r="C72" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="D72" s="38" t="s">
+      <c r="D72" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="E72" s="38" t="s">
+      <c r="E72" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="39"/>
-      <c r="J72" s="39"/>
-      <c r="K72" s="39"/>
-      <c r="L72" s="39"/>
-      <c r="M72" s="39"/>
-      <c r="N72" s="39"/>
-      <c r="O72" s="39"/>
-      <c r="P72" s="39"/>
-      <c r="Q72" s="39"/>
-      <c r="R72" s="39"/>
-      <c r="S72" s="39"/>
-      <c r="T72" s="39"/>
-      <c r="U72" s="39"/>
-      <c r="V72" s="39"/>
-      <c r="W72" s="39"/>
-      <c r="X72" s="39"/>
-      <c r="Y72" s="39"/>
-      <c r="Z72" s="40"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
+      <c r="L72" s="38"/>
+      <c r="M72" s="38"/>
+      <c r="N72" s="38"/>
+      <c r="O72" s="38"/>
+      <c r="P72" s="38"/>
+      <c r="Q72" s="38"/>
+      <c r="R72" s="38"/>
+      <c r="S72" s="38"/>
+      <c r="T72" s="38"/>
+      <c r="U72" s="38"/>
+      <c r="V72" s="38"/>
+      <c r="W72" s="38"/>
+      <c r="X72" s="38"/>
+      <c r="Y72" s="38"/>
+      <c r="Z72" s="39"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="47" t="s">
+      <c r="A73" s="46" t="s">
         <v>261</v>
       </c>
-      <c r="B73" s="48">
+      <c r="B73" s="47">
         <v>0.0</v>
       </c>
-      <c r="C73" s="48" t="s">
+      <c r="C73" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="E73" s="48" t="s">
+      <c r="E73" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49"/>
-      <c r="J73" s="49"/>
-      <c r="K73" s="49"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="49"/>
-      <c r="N73" s="49"/>
-      <c r="O73" s="49"/>
-      <c r="P73" s="49"/>
-      <c r="Q73" s="49"/>
-      <c r="R73" s="49"/>
-      <c r="S73" s="49"/>
-      <c r="T73" s="49"/>
-      <c r="U73" s="49"/>
-      <c r="V73" s="49"/>
-      <c r="W73" s="49"/>
-      <c r="X73" s="49"/>
-      <c r="Y73" s="49"/>
-      <c r="Z73" s="50"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="48"/>
+      <c r="L73" s="48"/>
+      <c r="M73" s="48"/>
+      <c r="N73" s="48"/>
+      <c r="O73" s="48"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="48"/>
+      <c r="R73" s="48"/>
+      <c r="S73" s="48"/>
+      <c r="T73" s="48"/>
+      <c r="U73" s="48"/>
+      <c r="V73" s="48"/>
+      <c r="W73" s="48"/>
+      <c r="X73" s="48"/>
+      <c r="Y73" s="48"/>
+      <c r="Z73" s="49"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="2"/>

--- a/Templates/Tables/StringInfo/T_StrTable.xlsx
+++ b/Templates/Tables/StringInfo/T_StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="271">
   <si>
     <t>ID</t>
   </si>
@@ -724,6 +724,30 @@
     <t>Logout</t>
   </si>
   <si>
+    <t>SYNC_P_SAVE_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>동기화 팝업 저장 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>저장하기</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>SYNC_P_LOAD_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>동기화 팝업 로드 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>불러오기</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
     <t>DAILY_MP_TITLE</t>
   </si>
   <si>
@@ -915,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1009,6 +1033,8 @@
     <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -3689,29 +3715,29 @@
       <c r="E65" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
-      <c r="L65" s="38"/>
-      <c r="M65" s="38"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="38"/>
-      <c r="P65" s="38"/>
-      <c r="Q65" s="38"/>
-      <c r="R65" s="38"/>
-      <c r="S65" s="38"/>
-      <c r="T65" s="38"/>
-      <c r="U65" s="38"/>
-      <c r="V65" s="38"/>
-      <c r="W65" s="38"/>
-      <c r="X65" s="38"/>
-      <c r="Y65" s="38"/>
-      <c r="Z65" s="39"/>
-    </row>
-    <row r="66" ht="15.0" customHeight="1">
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="45"/>
+      <c r="N65" s="45"/>
+      <c r="O65" s="45"/>
+      <c r="P65" s="45"/>
+      <c r="Q65" s="45"/>
+      <c r="R65" s="45"/>
+      <c r="S65" s="45"/>
+      <c r="T65" s="45"/>
+      <c r="U65" s="45"/>
+      <c r="V65" s="45"/>
+      <c r="W65" s="45"/>
+      <c r="X65" s="45"/>
+      <c r="Y65" s="45"/>
+      <c r="Z65" s="46"/>
+    </row>
+    <row r="66">
       <c r="A66" s="36" t="s">
         <v>241</v>
       </c>
@@ -3727,29 +3753,29 @@
       <c r="E66" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
-      <c r="L66" s="38"/>
-      <c r="M66" s="38"/>
-      <c r="N66" s="38"/>
-      <c r="O66" s="38"/>
-      <c r="P66" s="38"/>
-      <c r="Q66" s="38"/>
-      <c r="R66" s="38"/>
-      <c r="S66" s="38"/>
-      <c r="T66" s="38"/>
-      <c r="U66" s="38"/>
-      <c r="V66" s="38"/>
-      <c r="W66" s="38"/>
-      <c r="X66" s="38"/>
-      <c r="Y66" s="38"/>
-      <c r="Z66" s="39"/>
-    </row>
-    <row r="67" ht="15.0" customHeight="1">
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="45"/>
+      <c r="N66" s="45"/>
+      <c r="O66" s="45"/>
+      <c r="P66" s="45"/>
+      <c r="Q66" s="45"/>
+      <c r="R66" s="45"/>
+      <c r="S66" s="45"/>
+      <c r="T66" s="45"/>
+      <c r="U66" s="45"/>
+      <c r="V66" s="45"/>
+      <c r="W66" s="45"/>
+      <c r="X66" s="45"/>
+      <c r="Y66" s="45"/>
+      <c r="Z66" s="46"/>
+    </row>
+    <row r="67">
       <c r="A67" s="36" t="s">
         <v>245</v>
       </c>
@@ -3760,10 +3786,10 @@
         <v>246</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="F67" s="38"/>
       <c r="G67" s="38"/>
@@ -3789,19 +3815,19 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="36" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B68" s="37">
         <v>0.0</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F68" s="38"/>
       <c r="G68" s="38"/>
@@ -3826,14 +3852,14 @@
       <c r="Z68" s="39"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="45" t="s">
-        <v>251</v>
+      <c r="A69" s="36" t="s">
+        <v>253</v>
       </c>
       <c r="B69" s="37">
         <v>0.0</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D69" s="37" t="s">
         <v>159</v>
@@ -3865,19 +3891,19 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="36" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B70" s="37">
         <v>0.0</v>
       </c>
       <c r="C70" s="37" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>144</v>
+        <v>258</v>
       </c>
       <c r="F70" s="38"/>
       <c r="G70" s="38"/>
@@ -3902,20 +3928,20 @@
       <c r="Z70" s="39"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="36" t="s">
-        <v>255</v>
+      <c r="A71" s="47" t="s">
+        <v>259</v>
       </c>
       <c r="B71" s="37">
         <v>0.0</v>
       </c>
       <c r="C71" s="37" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="F71" s="38"/>
       <c r="G71" s="38"/>
@@ -3941,19 +3967,19 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B72" s="37">
         <v>0.0</v>
       </c>
       <c r="C72" s="37" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="E72" s="37" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="F72" s="38"/>
       <c r="G72" s="38"/>
@@ -3978,98 +4004,118 @@
       <c r="Z72" s="39"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="B73" s="47">
+      <c r="A73" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B73" s="37">
         <v>0.0</v>
       </c>
-      <c r="C73" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="D73" s="47" t="s">
+      <c r="C73" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="38"/>
+      <c r="M73" s="38"/>
+      <c r="N73" s="38"/>
+      <c r="O73" s="38"/>
+      <c r="P73" s="38"/>
+      <c r="Q73" s="38"/>
+      <c r="R73" s="38"/>
+      <c r="S73" s="38"/>
+      <c r="T73" s="38"/>
+      <c r="U73" s="38"/>
+      <c r="V73" s="38"/>
+      <c r="W73" s="38"/>
+      <c r="X73" s="38"/>
+      <c r="Y73" s="38"/>
+      <c r="Z73" s="39"/>
+    </row>
+    <row r="74" ht="15.0" customHeight="1">
+      <c r="A74" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="B74" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="D74" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
+      <c r="L74" s="38"/>
+      <c r="M74" s="38"/>
+      <c r="N74" s="38"/>
+      <c r="O74" s="38"/>
+      <c r="P74" s="38"/>
+      <c r="Q74" s="38"/>
+      <c r="R74" s="38"/>
+      <c r="S74" s="38"/>
+      <c r="T74" s="38"/>
+      <c r="U74" s="38"/>
+      <c r="V74" s="38"/>
+      <c r="W74" s="38"/>
+      <c r="X74" s="38"/>
+      <c r="Y74" s="38"/>
+      <c r="Z74" s="39"/>
+    </row>
+    <row r="75" ht="15.0" customHeight="1">
+      <c r="A75" s="48" t="s">
+        <v>269</v>
+      </c>
+      <c r="B75" s="49">
+        <v>0.0</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="D75" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="E73" s="47" t="s">
+      <c r="E75" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="48"/>
-      <c r="L73" s="48"/>
-      <c r="M73" s="48"/>
-      <c r="N73" s="48"/>
-      <c r="O73" s="48"/>
-      <c r="P73" s="48"/>
-      <c r="Q73" s="48"/>
-      <c r="R73" s="48"/>
-      <c r="S73" s="48"/>
-      <c r="T73" s="48"/>
-      <c r="U73" s="48"/>
-      <c r="V73" s="48"/>
-      <c r="W73" s="48"/>
-      <c r="X73" s="48"/>
-      <c r="Y73" s="48"/>
-      <c r="Z73" s="49"/>
-    </row>
-    <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
-      <c r="T74" s="2"/>
-      <c r="U74" s="2"/>
-      <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
-      <c r="X74" s="2"/>
-      <c r="Y74" s="2"/>
-      <c r="Z74" s="2"/>
-    </row>
-    <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
-      <c r="X75" s="2"/>
-      <c r="Y75" s="2"/>
-      <c r="Z75" s="2"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
+      <c r="H75" s="50"/>
+      <c r="I75" s="50"/>
+      <c r="J75" s="50"/>
+      <c r="K75" s="50"/>
+      <c r="L75" s="50"/>
+      <c r="M75" s="50"/>
+      <c r="N75" s="50"/>
+      <c r="O75" s="50"/>
+      <c r="P75" s="50"/>
+      <c r="Q75" s="50"/>
+      <c r="R75" s="50"/>
+      <c r="S75" s="50"/>
+      <c r="T75" s="50"/>
+      <c r="U75" s="50"/>
+      <c r="V75" s="50"/>
+      <c r="W75" s="50"/>
+      <c r="X75" s="50"/>
+      <c r="Y75" s="50"/>
+      <c r="Z75" s="51"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="2"/>
@@ -9167,7 +9213,7 @@
       <c r="Y257" s="2"/>
       <c r="Z257" s="2"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" ht="15.0" customHeight="1">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -9195,7 +9241,7 @@
       <c r="Y258" s="2"/>
       <c r="Z258" s="2"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" ht="15.0" customHeight="1">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -30811,6 +30857,62 @@
       <c r="Y1030" s="2"/>
       <c r="Z1030" s="2"/>
     </row>
+    <row r="1031" ht="15.75" customHeight="1">
+      <c r="A1031" s="2"/>
+      <c r="B1031" s="2"/>
+      <c r="C1031" s="2"/>
+      <c r="D1031" s="2"/>
+      <c r="E1031" s="2"/>
+      <c r="F1031" s="2"/>
+      <c r="G1031" s="2"/>
+      <c r="H1031" s="2"/>
+      <c r="I1031" s="2"/>
+      <c r="J1031" s="2"/>
+      <c r="K1031" s="2"/>
+      <c r="L1031" s="2"/>
+      <c r="M1031" s="2"/>
+      <c r="N1031" s="2"/>
+      <c r="O1031" s="2"/>
+      <c r="P1031" s="2"/>
+      <c r="Q1031" s="2"/>
+      <c r="R1031" s="2"/>
+      <c r="S1031" s="2"/>
+      <c r="T1031" s="2"/>
+      <c r="U1031" s="2"/>
+      <c r="V1031" s="2"/>
+      <c r="W1031" s="2"/>
+      <c r="X1031" s="2"/>
+      <c r="Y1031" s="2"/>
+      <c r="Z1031" s="2"/>
+    </row>
+    <row r="1032" ht="15.75" customHeight="1">
+      <c r="A1032" s="2"/>
+      <c r="B1032" s="2"/>
+      <c r="C1032" s="2"/>
+      <c r="D1032" s="2"/>
+      <c r="E1032" s="2"/>
+      <c r="F1032" s="2"/>
+      <c r="G1032" s="2"/>
+      <c r="H1032" s="2"/>
+      <c r="I1032" s="2"/>
+      <c r="J1032" s="2"/>
+      <c r="K1032" s="2"/>
+      <c r="L1032" s="2"/>
+      <c r="M1032" s="2"/>
+      <c r="N1032" s="2"/>
+      <c r="O1032" s="2"/>
+      <c r="P1032" s="2"/>
+      <c r="Q1032" s="2"/>
+      <c r="R1032" s="2"/>
+      <c r="S1032" s="2"/>
+      <c r="T1032" s="2"/>
+      <c r="U1032" s="2"/>
+      <c r="V1032" s="2"/>
+      <c r="W1032" s="2"/>
+      <c r="X1032" s="2"/>
+      <c r="Y1032" s="2"/>
+      <c r="Z1032" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
